--- a/internal/lib/service/excel/templates/res-summary-filter.xlsx
+++ b/internal/lib/service/excel/templates/res-summary-filter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\go\srmt-prime\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\go\srmt-prime\internal\lib\service\excel\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8CD185-A294-4485-8B85-34495277F79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E252B51-6182-4E7A-92E8-5BA8A8829165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5445" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="16.12 (P)" sheetId="1" r:id="rId1"/>
@@ -192,7 +192,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="A18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -216,7 +216,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="A22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -240,7 +240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="F22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -264,7 +264,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="I22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="50">
   <si>
     <r>
       <t xml:space="preserve">Ўзбекгидроэнерго АЖ бошқарувидаги сув омборларнинг кунлик амалда ишлаши тўғрисида </t>
@@ -733,9 +733,6 @@
     <t>+1,78</t>
   </si>
   <si>
-    <t xml:space="preserve"> -2,10</t>
-  </si>
-  <si>
     <t>Чотқол</t>
   </si>
   <si>
@@ -800,7 +797,7 @@
     <numFmt numFmtId="176" formatCode="dd\-mm\-yyyy&quot; йил&quot;"/>
     <numFmt numFmtId="177" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="69" x14ac:knownFonts="1">
+  <fonts count="70" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1325,49 +1322,19 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1532,7 +1499,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -1545,64 +1512,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="hair">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="hair">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="hair">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="hair">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="hair">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="hair">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1664,19 +1573,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="hair">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="hair">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="hair">
         <color rgb="FF000000"/>
       </left>
@@ -1687,19 +1583,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom style="hair">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -2029,7 +1912,7 @@
     <xf numFmtId="166" fontId="48" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2237,26 +2120,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="4" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="5" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="4" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="5" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -2264,28 +2127,12 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="7" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="14" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="27" fillId="8" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="27" fillId="4" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="8" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="23" fillId="9" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="23" fillId="10" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="9" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="29" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2294,14 +2141,6 @@
     </xf>
     <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="13" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="6" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="30" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2313,10 +2152,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="23" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="11" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2335,15 +2170,15 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="34" fillId="14" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="34" fillId="8" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="14" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="19" fillId="8" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="14" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="19" fillId="8" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2368,15 +2203,15 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="27" fillId="8" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="27" fillId="4" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="9" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="14" fillId="5" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="10" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="14" fillId="6" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2413,7 +2248,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="27" fillId="12" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="27" fillId="7" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2429,11 +2264,11 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="27" fillId="0" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="27" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2449,7 +2284,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="26" fillId="15" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="26" fillId="9" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -2464,14 +2299,14 @@
     <xf numFmtId="165" fontId="45" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="16" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="168" fontId="20" fillId="10" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="169" fontId="1" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="16" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="20" fillId="10" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2488,7 +2323,7 @@
     <xf numFmtId="170" fontId="1" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="17" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="46" fillId="11" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2506,45 +2341,89 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="18" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="18" fillId="12" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="7" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="14" fillId="3" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="8" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="14" fillId="4" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="35" fillId="19" borderId="20" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="35" fillId="13" borderId="14" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="20" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="10" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="14" fillId="6" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="9" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="14" fillId="5" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="172" fontId="19" fillId="14" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="172" fontId="19" fillId="8" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="173" fontId="19" fillId="14" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="173" fontId="19" fillId="8" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="63" fillId="28" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="61" fillId="26" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="64" fillId="26" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="65" fillId="27" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="66" fillId="27" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="53" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="67" fillId="27" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="61" fillId="27" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="65" fillId="27" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="65" fillId="27" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="61" fillId="27" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="61" fillId="27" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="62" fillId="26" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="63" fillId="26" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="62" fillId="28" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2554,174 +2433,130 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="173" fontId="19" fillId="15" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="47" fillId="30" borderId="33" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="173" fontId="19" fillId="16" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="61" fillId="26" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="61" fillId="26" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="68" fillId="27" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="63" fillId="28" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="53" fillId="27" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="61" fillId="27" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="65" fillId="27" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="15" borderId="17" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="16" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="171" fontId="35" fillId="12" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="59" fillId="25" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="59" fillId="25" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="47" fillId="24" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="20" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="27" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="21" borderId="23" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="28" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="22" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="23" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="24" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="20" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="19" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="22" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="35" fillId="19" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="35" fillId="13" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="35" fillId="15" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="35" fillId="9" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="171" fontId="35" fillId="18" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="19" fillId="21" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="173" fontId="19" fillId="22" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="21" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="22" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="29" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="34" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="59" fillId="31" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="59" fillId="31" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="63" fillId="34" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="61" fillId="32" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="64" fillId="32" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="65" fillId="33" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="66" fillId="33" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="53" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="67" fillId="33" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="61" fillId="33" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="65" fillId="33" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="65" fillId="33" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="63" fillId="34" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="53" fillId="33" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="61" fillId="33" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="65" fillId="33" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="68" fillId="33" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="61" fillId="33" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="61" fillId="33" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="62" fillId="32" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="63" fillId="32" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="62" fillId="34" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="61" fillId="32" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="61" fillId="32" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2783,7 +2618,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA8AAAAAAAAA4wJ+AA8AAAAAAAAAHgOSAF8BAADDJgAAOAAAADAAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA8AAAAAAAAA4wJ+AA8AAAAAAAAAHgOSAF8BAADDJgAAOAAAADAAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2859,7 +2694,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAUAAAAAAAAAWAOGAAUAAAAAAAAAkwOaAHYBAAAADwAAOAAAADMAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAUAAAAAAAAAWAOGAAUAAAAAAAAAkwOaAHYBAAAADwAAOAAAADMAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -2935,7 +2770,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAsAAAAAAAAA5wKIAAsAAAAAAAAAIgObAHsBAAArHQAANQAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAsAAAAAAAAA5wKIAAsAAAAAAAAAIgObAHsBAAArHQAANQAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3011,7 +2846,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAUAAAAAAAAAbgKHAAUAAAAAAAAAqAKaAHkBAAA4DgAANQAAADIAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAUAAAAAAAAAbgKHAAUAAAAAAAAAqAKaAHkBAAA4DgAANQAAADIAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3087,7 +2922,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAYAAAAAAAAAUgDdAAYAAAAAAAAAywDwAGgCAACyDwAANQAAADIAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAYAAAAAAAAAUgDdAAYAAAAAAAAAywDwAGgCAACyDwAANQAAADIAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3163,7 +2998,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAcAAAAAAAAA5AKDAAcAAAAAAAAAHgOXAG0BAACMEwAAOAAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAcAAAAAAAAA5AKDAAcAAAAAAAAAHgOXAG0BAACMEwAAOAAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3239,7 +3074,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAcAAAAAAAAAxAOCAAcAAAAAAAAA/wOVAGsBAABBFAAANQAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAcAAAAAAAAAxAOCAAcAAAAAAAAA/wOVAGsBAABBFAAANQAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3315,7 +3150,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAgAAAAAAAAATgG1AAgAAAAAAAAAxQHIAPkBAAD1FAAANQAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAO0NAwAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAgAAAAAAAAATgG1AAgAAAAAAAAAxQHIAPkBAAD1FAAANQAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3391,7 +3226,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAkAAAAAAAAATQODAAkAAAAAAAAAiQOWAG0BAACvGAAANQAAADAAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAkAAAAAAAAATQODAAkAAAAAAAAAiQOWAG0BAACvGAAANQAAADAAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3467,7 +3302,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAoAAAAAAAAAfACCAAoAAAAAAAAA+ACVAGsBAABwGQAANQAAADEAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAoAAAAAAAAAfACCAAoAAAAAAAAA+ACVAGsBAABwGQAANQAAADEAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3543,7 +3378,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA0AAAAAAAAAywODAA4AAAAAAAAACACWAG0BAACwIgAANQAAAC4AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA0AAAAAAAAAywODAA4AAAAAAAAACACWAG0BAACwIgAANQAAAC4AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3619,7 +3454,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA4AAAAAAAAAOgG1AA4AAAAAAAAAsAHIAPkBAABXIwAANQAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA4AAAAAAAAAOgG1AA4AAAAAAAAAsAHIAPkBAABXIwAANQAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3695,7 +3530,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAI8MAQAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA8AAAAAAAAAxwOBAA8AAAAAAAAAAASUAGgBAAB7JwAANQAAAC4AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAI8MAQAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA8AAAAAAAAAxwOBAA8AAAAAAAAAAASUAGgBAAB7JwAANQAAAC4AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3771,7 +3606,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAABAAAAAAAAAAXQGxABAAAAAAAAAA1AHFAO4BAAAzKAAANwAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAABAAAAAAAAAAXQGxABAAAAAAAAAA1AHFAO4BAAAzKAAANwAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3847,7 +3682,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAsAAAAAAAAAvgOHAAsAAAAAAAAA+QObAHkBAADYHQAANwAAAC8AAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAsAAAAAAAAAvgOHAAsAAAAAAAAA+QObAHkBAADYHQAANwAAAC8AAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3923,7 +3758,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAwAAAAAAAAAPAG9AAwAAAAAAAAAtQHQAA8CAACKHgAANQAAADAAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAwAAAAAAAAAPAG9AAwAAAAAAAAAtQHQAA8CAACKHgAANQAAADAAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -3999,7 +3834,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA0AAAAAAAAA6gKAAA0AAAAAAAAAJgOUAGUBAAD7IQAAOAAAADAAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAA0AAAAAAAAA6gKAAA0AAAAAAAAAJgOUAGUBAAD7IQAAOAAAADAAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -4075,7 +3910,7 @@
         <xdr:cNvSpPr>
           <a:extLst>
             <a:ext uri="smNativeData">
-              <pm:smNativeData xmlns:pm="smNativeData" xmlns="" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAYAAAAAAAAADgLfAAYAAAAAAAAAhQLyAG4CAABqEAAANQAAADEAAAAAAAAA"/>
+              <pm:smNativeData xmlns="" xmlns:pm="smNativeData" val="SMDATA_13_KLpxaRMAAAAlAAAAagAAAI0AAAAAkAAAAEgAAACQAAAASAAAAAAAAAAAAAAAAAAAAAEAAABQAAAAAAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8AAAAAAADgPwAAAAAAAOA/AAAAAAAA4D8CAAAAjAAAAAEAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAZAAAAAEAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAFAAAADwAAAABAAAAAAAAAAAAAAAUAAAAAQAAABQAAAAUAAAAFAAAAAEAAAAAAAAAZAAAAGQAAAAAAAAAZAAAAGQAAAAVAAAAYAAAAAAAAAAAAAAADwAAACADAAAAAAAAAAAAAAEAAACgMgAAVgcAAKr4//8BAAAAf39/AAEAAABkAAAAAAAAABQAAABAHwAAAAAAACYAAAAAAAAAwOD//wAAAAAmAAAAZAAAABYAAABMAAAAAAAAAAAAAAAEAAAAAAAAAAEAAAB/f38AAAAAACgAAAAoAAAAZAAAAGQAAAAAAAAAzMzMAAAAAABQAAAAUAAAAGQAAABkAAAAAAAAABcAAAAUAAAAAAAAAAAAAAD/fwAA/38AAAAAAAAJAAAABAAAAAAAAAAeAAAAaAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAECcAABAnAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABQAAAAAAAAAwMD/AAAAAABkAAAAMgAAAAAAAABkAAAAAAAAAH9/fwAKAAAAIgAAABgAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAkAAAAJAAAAAAAAAAHAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAf39/ACUAAABYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA/AAAAAAAAAKCGAQAAAAAAAAAAAAAAAAAMAAAAAQAAAAAAAAAAAAAAAAAAACEAAAAwAAAALAAAAAYAAAAAAAAADgLfAAYAAAAAAAAAhQLyAG4CAABqEAAANQAAADEAAAAAAAAA"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvSpPr>
@@ -4413,56 +4248,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:204" ht="29.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="173" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="134"/>
-      <c r="Q1" s="134"/>
-      <c r="R1" s="134"/>
-      <c r="S1" s="134"/>
-      <c r="T1" s="134"/>
-      <c r="U1" s="134"/>
-      <c r="V1" s="134"/>
-      <c r="W1" s="133"/>
-      <c r="X1" s="133"/>
-      <c r="Y1" s="133"/>
-      <c r="Z1" s="133"/>
-      <c r="AA1" s="133"/>
-      <c r="AB1" s="133"/>
-      <c r="AC1" s="133"/>
-      <c r="AD1" s="133"/>
-      <c r="AE1" s="133"/>
-      <c r="AF1" s="133"/>
-      <c r="AG1" s="133"/>
-      <c r="AH1" s="133"/>
-      <c r="AI1" s="133"/>
-      <c r="AJ1" s="133"/>
-      <c r="AK1" s="133"/>
-      <c r="AL1" s="133"/>
-      <c r="AM1" s="133"/>
-      <c r="AN1" s="133"/>
-      <c r="AO1" s="133"/>
-      <c r="AP1" s="133"/>
-      <c r="AQ1" s="133"/>
-      <c r="AR1" s="133"/>
-      <c r="AS1" s="133"/>
-      <c r="AT1" s="133"/>
-      <c r="AU1" s="133"/>
-      <c r="AV1" s="133"/>
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="173"/>
+      <c r="H1" s="173"/>
+      <c r="I1" s="173"/>
+      <c r="J1" s="173"/>
+      <c r="K1" s="173"/>
+      <c r="L1" s="173"/>
+      <c r="M1" s="173"/>
+      <c r="N1" s="173"/>
+      <c r="O1" s="173"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="121"/>
+      <c r="AE1" s="121"/>
+      <c r="AF1" s="121"/>
+      <c r="AG1" s="121"/>
+      <c r="AH1" s="121"/>
+      <c r="AI1" s="121"/>
+      <c r="AJ1" s="121"/>
+      <c r="AK1" s="121"/>
+      <c r="AL1" s="121"/>
+      <c r="AM1" s="121"/>
+      <c r="AN1" s="121"/>
+      <c r="AO1" s="121"/>
+      <c r="AP1" s="121"/>
+      <c r="AQ1" s="121"/>
+      <c r="AR1" s="121"/>
+      <c r="AS1" s="121"/>
+      <c r="AT1" s="121"/>
+      <c r="AU1" s="121"/>
+      <c r="AV1" s="121"/>
       <c r="AW1" s="4"/>
       <c r="AX1" s="4"/>
       <c r="AY1" s="4"/>
@@ -4531,7 +4366,7 @@
       <c r="DJ1" s="4"/>
       <c r="DK1" s="4"/>
       <c r="DL1" s="4"/>
-      <c r="FZ1" s="125"/>
+      <c r="FZ1" s="113"/>
     </row>
     <row r="2" spans="1:204" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="4"/>
@@ -4545,29 +4380,29 @@
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
-      <c r="L2" s="151">
+      <c r="L2" s="174">
         <v>46007</v>
       </c>
-      <c r="M2" s="151"/>
-      <c r="N2" s="151"/>
-      <c r="O2" s="151"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="131"/>
-      <c r="R2" s="131"/>
-      <c r="W2" s="129"/>
-      <c r="X2" s="129"/>
-      <c r="Y2" s="129"/>
-      <c r="Z2" s="129"/>
-      <c r="AA2" s="130"/>
-      <c r="AB2" s="129"/>
-      <c r="AC2" s="129"/>
-      <c r="AD2" s="129"/>
-      <c r="AE2" s="129"/>
-      <c r="AF2" s="129"/>
-      <c r="AG2" s="129"/>
-      <c r="AH2" s="129"/>
-      <c r="AI2" s="129"/>
-      <c r="AJ2" s="129"/>
+      <c r="M2" s="174"/>
+      <c r="N2" s="174"/>
+      <c r="O2" s="174"/>
+      <c r="P2" s="120"/>
+      <c r="Q2" s="119"/>
+      <c r="R2" s="119"/>
+      <c r="W2" s="117"/>
+      <c r="X2" s="117"/>
+      <c r="Y2" s="117"/>
+      <c r="Z2" s="117"/>
+      <c r="AA2" s="118"/>
+      <c r="AB2" s="117"/>
+      <c r="AC2" s="117"/>
+      <c r="AD2" s="117"/>
+      <c r="AE2" s="117"/>
+      <c r="AF2" s="117"/>
+      <c r="AG2" s="117"/>
+      <c r="AH2" s="117"/>
+      <c r="AI2" s="117"/>
+      <c r="AJ2" s="117"/>
       <c r="AK2" s="4"/>
       <c r="AL2" s="4"/>
       <c r="AM2" s="4"/>
@@ -4648,38 +4483,38 @@
       <c r="DJ2" s="4"/>
       <c r="DK2" s="4"/>
       <c r="DL2" s="4"/>
-      <c r="FZ2" s="125"/>
+      <c r="FZ2" s="113"/>
     </row>
     <row r="3" spans="1:204" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="159" t="s">
+      <c r="A3" s="182" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="142" t="s">
+      <c r="B3" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="152" t="s">
+      <c r="C3" s="175" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="153"/>
-      <c r="E3" s="153"/>
-      <c r="F3" s="152" t="s">
+      <c r="D3" s="176"/>
+      <c r="E3" s="176"/>
+      <c r="F3" s="175" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="153"/>
-      <c r="H3" s="154"/>
-      <c r="I3" s="152" t="s">
+      <c r="G3" s="176"/>
+      <c r="H3" s="177"/>
+      <c r="I3" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="153"/>
-      <c r="K3" s="154"/>
-      <c r="L3" s="155" t="s">
+      <c r="J3" s="176"/>
+      <c r="K3" s="177"/>
+      <c r="L3" s="178" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="156"/>
-      <c r="N3" s="155" t="s">
+      <c r="M3" s="179"/>
+      <c r="N3" s="178" t="s">
         <v>7</v>
       </c>
-      <c r="O3" s="156"/>
+      <c r="O3" s="179"/>
       <c r="P3" s="24"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
@@ -4697,11 +4532,11 @@
       <c r="AD3" s="4"/>
       <c r="AE3" s="4"/>
       <c r="AF3" s="4"/>
-      <c r="AG3" s="128"/>
-      <c r="AH3" s="127"/>
-      <c r="AI3" s="126"/>
-      <c r="AJ3" s="126"/>
-      <c r="AK3" s="126"/>
+      <c r="AG3" s="116"/>
+      <c r="AH3" s="115"/>
+      <c r="AI3" s="114"/>
+      <c r="AJ3" s="114"/>
+      <c r="AK3" s="114"/>
       <c r="AL3" s="4"/>
       <c r="AM3" s="4"/>
       <c r="AN3" s="4"/>
@@ -4774,109 +4609,109 @@
       <c r="DC3" s="4"/>
       <c r="DD3" s="4"/>
       <c r="DE3" s="4"/>
-      <c r="FS3" s="125"/>
+      <c r="FS3" s="113"/>
     </row>
     <row r="4" spans="1:204" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="160"/>
-      <c r="B4" s="164">
+      <c r="A4" s="183"/>
+      <c r="B4" s="187">
         <f>L2</f>
         <v>46007</v>
       </c>
-      <c r="C4" s="166">
+      <c r="C4" s="170">
         <f>L2</f>
         <v>46007</v>
       </c>
-      <c r="D4" s="161" t="s">
+      <c r="D4" s="184" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="162"/>
-      <c r="F4" s="141">
+      <c r="E4" s="185"/>
+      <c r="F4" s="129">
         <f>L2</f>
         <v>46007</v>
       </c>
-      <c r="G4" s="161" t="s">
+      <c r="G4" s="184" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="162"/>
-      <c r="I4" s="166">
+      <c r="H4" s="185"/>
+      <c r="I4" s="170">
         <f>L2</f>
         <v>46007</v>
       </c>
-      <c r="J4" s="161" t="s">
+      <c r="J4" s="184" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="163"/>
-      <c r="L4" s="157"/>
-      <c r="M4" s="158"/>
-      <c r="N4" s="157"/>
-      <c r="O4" s="158"/>
-      <c r="P4" s="123"/>
-      <c r="Q4" s="123"/>
-      <c r="R4" s="123"/>
-      <c r="S4" s="124"/>
-      <c r="T4" s="135"/>
-      <c r="U4" s="135"/>
-      <c r="V4" s="135"/>
-      <c r="W4" s="135"/>
-      <c r="X4" s="135"/>
-      <c r="Y4" s="135"/>
-      <c r="Z4" s="135"/>
-      <c r="AA4" s="135"/>
-      <c r="AB4" s="135"/>
-      <c r="AC4" s="135"/>
-      <c r="AD4" s="135"/>
-      <c r="AE4" s="135"/>
-      <c r="AF4" s="135"/>
-      <c r="AG4" s="135"/>
-      <c r="AH4" s="135"/>
-      <c r="AI4" s="135"/>
-      <c r="AJ4" s="135"/>
-      <c r="AK4" s="135"/>
-      <c r="AL4" s="135"/>
-      <c r="AM4" s="135"/>
-      <c r="AN4" s="135"/>
-      <c r="AO4" s="135"/>
-      <c r="AP4" s="135"/>
-      <c r="AQ4" s="135"/>
-      <c r="AR4" s="135"/>
-      <c r="AS4" s="135"/>
-      <c r="AT4" s="135"/>
-      <c r="AU4" s="135"/>
-      <c r="AV4" s="135"/>
-      <c r="AW4" s="135"/>
-      <c r="AX4" s="135"/>
-      <c r="AY4" s="135"/>
-      <c r="AZ4" s="135"/>
-      <c r="BA4" s="135"/>
-      <c r="BB4" s="135"/>
-      <c r="BC4" s="135"/>
-      <c r="BD4" s="135"/>
-      <c r="BE4" s="135"/>
-      <c r="BF4" s="135"/>
-      <c r="BG4" s="135"/>
-      <c r="BH4" s="135"/>
-      <c r="BI4" s="135"/>
-      <c r="BJ4" s="135"/>
-      <c r="BK4" s="135"/>
-      <c r="BL4" s="135"/>
-      <c r="BM4" s="135"/>
-      <c r="BN4" s="135"/>
-      <c r="BO4" s="135"/>
-      <c r="BP4" s="135"/>
-      <c r="BQ4" s="135"/>
-      <c r="BR4" s="135"/>
-      <c r="BS4" s="135"/>
-      <c r="BT4" s="135"/>
-      <c r="BU4" s="135"/>
-      <c r="BV4" s="135"/>
-      <c r="BW4" s="135"/>
-      <c r="BX4" s="135"/>
-      <c r="BY4" s="135"/>
-      <c r="BZ4" s="135"/>
-      <c r="CA4" s="135"/>
-      <c r="CB4" s="135"/>
-      <c r="CC4" s="135"/>
-      <c r="CD4" s="135"/>
+      <c r="K4" s="186"/>
+      <c r="L4" s="180"/>
+      <c r="M4" s="181"/>
+      <c r="N4" s="180"/>
+      <c r="O4" s="181"/>
+      <c r="P4" s="111"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="123"/>
+      <c r="U4" s="123"/>
+      <c r="V4" s="123"/>
+      <c r="W4" s="123"/>
+      <c r="X4" s="123"/>
+      <c r="Y4" s="123"/>
+      <c r="Z4" s="123"/>
+      <c r="AA4" s="123"/>
+      <c r="AB4" s="123"/>
+      <c r="AC4" s="123"/>
+      <c r="AD4" s="123"/>
+      <c r="AE4" s="123"/>
+      <c r="AF4" s="123"/>
+      <c r="AG4" s="123"/>
+      <c r="AH4" s="123"/>
+      <c r="AI4" s="123"/>
+      <c r="AJ4" s="123"/>
+      <c r="AK4" s="123"/>
+      <c r="AL4" s="123"/>
+      <c r="AM4" s="123"/>
+      <c r="AN4" s="123"/>
+      <c r="AO4" s="123"/>
+      <c r="AP4" s="123"/>
+      <c r="AQ4" s="123"/>
+      <c r="AR4" s="123"/>
+      <c r="AS4" s="123"/>
+      <c r="AT4" s="123"/>
+      <c r="AU4" s="123"/>
+      <c r="AV4" s="123"/>
+      <c r="AW4" s="123"/>
+      <c r="AX4" s="123"/>
+      <c r="AY4" s="123"/>
+      <c r="AZ4" s="123"/>
+      <c r="BA4" s="123"/>
+      <c r="BB4" s="123"/>
+      <c r="BC4" s="123"/>
+      <c r="BD4" s="123"/>
+      <c r="BE4" s="123"/>
+      <c r="BF4" s="123"/>
+      <c r="BG4" s="123"/>
+      <c r="BH4" s="123"/>
+      <c r="BI4" s="123"/>
+      <c r="BJ4" s="123"/>
+      <c r="BK4" s="123"/>
+      <c r="BL4" s="123"/>
+      <c r="BM4" s="123"/>
+      <c r="BN4" s="123"/>
+      <c r="BO4" s="123"/>
+      <c r="BP4" s="123"/>
+      <c r="BQ4" s="123"/>
+      <c r="BR4" s="123"/>
+      <c r="BS4" s="123"/>
+      <c r="BT4" s="123"/>
+      <c r="BU4" s="123"/>
+      <c r="BV4" s="123"/>
+      <c r="BW4" s="123"/>
+      <c r="BX4" s="123"/>
+      <c r="BY4" s="123"/>
+      <c r="BZ4" s="123"/>
+      <c r="CA4" s="123"/>
+      <c r="CB4" s="123"/>
+      <c r="CC4" s="123"/>
+      <c r="CD4" s="123"/>
       <c r="CE4" s="4"/>
       <c r="CF4" s="4"/>
       <c r="CG4" s="4"/>
@@ -4906,50 +4741,50 @@
       <c r="DE4" s="4"/>
     </row>
     <row r="5" spans="1:204" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="160"/>
-      <c r="B5" s="165"/>
-      <c r="C5" s="166"/>
-      <c r="D5" s="138">
+      <c r="A5" s="183"/>
+      <c r="B5" s="188"/>
+      <c r="C5" s="170"/>
+      <c r="D5" s="126">
         <f>YEAR($L$2)-1</f>
         <v>2024</v>
       </c>
-      <c r="E5" s="138">
+      <c r="E5" s="126">
         <f>YEAR($L$2)-2</f>
         <v>2023</v>
       </c>
-      <c r="F5" s="122" t="s">
+      <c r="F5" s="110" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="138">
+      <c r="G5" s="126">
         <f>YEAR($L$2)-1</f>
         <v>2024</v>
       </c>
-      <c r="H5" s="138">
+      <c r="H5" s="126">
         <f>YEAR($L$2)-2</f>
         <v>2023</v>
       </c>
-      <c r="I5" s="166"/>
-      <c r="J5" s="138">
+      <c r="I5" s="170"/>
+      <c r="J5" s="126">
         <f>YEAR($L$2)-1</f>
         <v>2024</v>
       </c>
-      <c r="K5" s="138">
+      <c r="K5" s="126">
         <f>YEAR($L$2)-2</f>
         <v>2023</v>
       </c>
-      <c r="L5" s="138">
+      <c r="L5" s="126">
         <f>YEAR($L$2)</f>
         <v>2025</v>
       </c>
-      <c r="M5" s="138">
+      <c r="M5" s="126">
         <f>YEAR($L$2)-1</f>
         <v>2024</v>
       </c>
-      <c r="N5" s="138">
+      <c r="N5" s="126">
         <f>YEAR($L$2)</f>
         <v>2025</v>
       </c>
-      <c r="O5" s="138">
+      <c r="O5" s="126">
         <f>YEAR($L$2)-1</f>
         <v>2024</v>
       </c>
@@ -4957,3910 +4792,3954 @@
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
-      <c r="T5" s="121"/>
-      <c r="U5" s="121"/>
-      <c r="V5" s="121"/>
-      <c r="W5" s="121"/>
-      <c r="X5" s="121"/>
-      <c r="Y5" s="121"/>
-      <c r="Z5" s="121"/>
-      <c r="AA5" s="121"/>
-      <c r="AB5" s="119"/>
-      <c r="AC5" s="119"/>
-      <c r="AD5" s="119"/>
-      <c r="AE5" s="119"/>
-      <c r="AF5" s="119"/>
-      <c r="AG5" s="119"/>
-      <c r="AH5" s="119"/>
-      <c r="AI5" s="119"/>
-      <c r="AJ5" s="119"/>
-      <c r="AK5" s="119"/>
-      <c r="AL5" s="119"/>
-      <c r="AM5" s="119"/>
-      <c r="AN5" s="119"/>
-      <c r="AO5" s="119"/>
-      <c r="AP5" s="119"/>
-      <c r="AQ5" s="119"/>
-      <c r="AR5" s="119"/>
-      <c r="AS5" s="119"/>
-      <c r="AT5" s="119"/>
-      <c r="AU5" s="119"/>
-      <c r="AV5" s="119"/>
-      <c r="AW5" s="119"/>
-      <c r="AX5" s="119"/>
-      <c r="AY5" s="119"/>
-      <c r="AZ5" s="119"/>
-      <c r="BA5" s="119"/>
-      <c r="BB5" s="119"/>
-      <c r="BC5" s="119"/>
-      <c r="BD5" s="119"/>
-      <c r="BE5" s="119"/>
-      <c r="BF5" s="120"/>
-      <c r="BG5" s="120"/>
-      <c r="BH5" s="120"/>
-      <c r="BI5" s="120"/>
-      <c r="BJ5" s="120"/>
-      <c r="BK5" s="120"/>
-      <c r="BL5" s="120"/>
-      <c r="BM5" s="120"/>
-      <c r="BN5" s="120"/>
-      <c r="BO5" s="120"/>
-      <c r="BP5" s="120"/>
-      <c r="BQ5" s="120"/>
-      <c r="BR5" s="120"/>
-      <c r="BS5" s="120"/>
-      <c r="BT5" s="120"/>
-      <c r="BU5" s="120"/>
-      <c r="BV5" s="120"/>
-      <c r="BW5" s="120"/>
-      <c r="BX5" s="120"/>
-      <c r="BY5" s="120"/>
-      <c r="BZ5" s="120"/>
-      <c r="CA5" s="120"/>
-      <c r="CB5" s="120"/>
-      <c r="CC5" s="120"/>
-      <c r="CD5" s="120"/>
-      <c r="CE5" s="120"/>
-      <c r="CF5" s="120"/>
-      <c r="CG5" s="120"/>
-      <c r="CH5" s="120"/>
-      <c r="CI5" s="120"/>
-      <c r="CJ5" s="120"/>
-      <c r="CK5" s="120"/>
-      <c r="CL5" s="120"/>
-      <c r="CM5" s="120"/>
-      <c r="CN5" s="120"/>
-      <c r="CO5" s="120"/>
-      <c r="CP5" s="120"/>
-      <c r="CQ5" s="120"/>
-      <c r="CR5" s="120"/>
-      <c r="CS5" s="120"/>
-      <c r="CT5" s="120"/>
-      <c r="CU5" s="120"/>
-      <c r="CV5" s="120"/>
-      <c r="CW5" s="120"/>
-      <c r="CX5" s="120"/>
-      <c r="CY5" s="120"/>
-      <c r="CZ5" s="120"/>
-      <c r="DA5" s="120"/>
-      <c r="DB5" s="120"/>
-      <c r="DC5" s="120"/>
-      <c r="DD5" s="120"/>
-      <c r="DE5" s="120"/>
-      <c r="DF5" s="120"/>
-      <c r="DG5" s="120"/>
-      <c r="DH5" s="120"/>
-      <c r="DI5" s="120"/>
-      <c r="DJ5" s="120"/>
-      <c r="DK5" s="120"/>
-      <c r="DL5" s="120"/>
-      <c r="DM5" s="120"/>
-      <c r="DN5" s="120"/>
-      <c r="DO5" s="120"/>
-      <c r="DP5" s="120"/>
-      <c r="DQ5" s="120"/>
-      <c r="DR5" s="120"/>
-      <c r="DS5" s="120"/>
-      <c r="DT5" s="120"/>
-      <c r="DU5" s="120"/>
-      <c r="DV5" s="120"/>
-      <c r="DW5" s="120"/>
-      <c r="DX5" s="120"/>
-      <c r="DY5" s="120"/>
-      <c r="DZ5" s="120"/>
-      <c r="EA5" s="120"/>
-      <c r="EB5" s="120"/>
-      <c r="EC5" s="120"/>
-      <c r="ED5" s="120"/>
-      <c r="EE5" s="120"/>
-      <c r="EF5" s="120"/>
-      <c r="EG5" s="120"/>
-      <c r="EH5" s="119"/>
-      <c r="EI5" s="119"/>
-      <c r="EJ5" s="119"/>
-      <c r="EK5" s="119"/>
-      <c r="EL5" s="119"/>
-      <c r="EM5" s="119"/>
-      <c r="EN5" s="119"/>
-      <c r="EO5" s="119"/>
-      <c r="EP5" s="119"/>
-      <c r="EQ5" s="119"/>
-      <c r="ER5" s="119"/>
-      <c r="ES5" s="119"/>
-      <c r="ET5" s="119"/>
-      <c r="EU5" s="119"/>
-      <c r="EV5" s="119"/>
-      <c r="EW5" s="119"/>
-      <c r="EX5" s="119"/>
-      <c r="EY5" s="119"/>
-      <c r="EZ5" s="119"/>
-      <c r="FA5" s="119"/>
-      <c r="FB5" s="119"/>
-      <c r="FC5" s="119"/>
-      <c r="FD5" s="119"/>
-      <c r="FE5" s="119"/>
-      <c r="FF5" s="119"/>
-      <c r="FG5" s="119"/>
-      <c r="FH5" s="119"/>
-      <c r="FI5" s="119"/>
-      <c r="FJ5" s="119"/>
-      <c r="FK5" s="119"/>
-      <c r="FL5" s="119"/>
-      <c r="FM5" s="119"/>
-      <c r="FN5" s="119"/>
-      <c r="FO5" s="119"/>
-      <c r="FP5" s="119"/>
-      <c r="FQ5" s="119"/>
-      <c r="FR5" s="119"/>
-      <c r="FS5" s="119"/>
-      <c r="FT5" s="119"/>
-      <c r="FU5" s="119"/>
-      <c r="FV5" s="119"/>
-      <c r="FW5" s="119"/>
-      <c r="FX5" s="119"/>
-      <c r="FY5" s="119"/>
-      <c r="FZ5" s="119"/>
-      <c r="GA5" s="119"/>
-      <c r="GB5" s="119"/>
-      <c r="GC5" s="119"/>
-      <c r="GD5" s="119"/>
-      <c r="GE5" s="119"/>
-      <c r="GF5" s="119"/>
-      <c r="GG5" s="119"/>
-      <c r="GH5" s="119"/>
-      <c r="GI5" s="119"/>
-      <c r="GJ5" s="119"/>
-      <c r="GK5" s="119"/>
-      <c r="GL5" s="119"/>
-      <c r="GM5" s="119"/>
-      <c r="GN5" s="119"/>
-      <c r="GO5" s="119"/>
-      <c r="GP5" s="119"/>
-      <c r="GQ5" s="119"/>
-      <c r="GR5" s="119"/>
-      <c r="GS5" s="119"/>
-      <c r="GT5" s="119"/>
-      <c r="GU5" s="119"/>
-      <c r="GV5" s="119"/>
-    </row>
-    <row r="6" spans="1:204" s="95" customFormat="1" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="167" t="s">
+      <c r="T5" s="109"/>
+      <c r="U5" s="109"/>
+      <c r="V5" s="109"/>
+      <c r="W5" s="109"/>
+      <c r="X5" s="109"/>
+      <c r="Y5" s="109"/>
+      <c r="Z5" s="109"/>
+      <c r="AA5" s="109"/>
+      <c r="AB5" s="107"/>
+      <c r="AC5" s="107"/>
+      <c r="AD5" s="107"/>
+      <c r="AE5" s="107"/>
+      <c r="AF5" s="107"/>
+      <c r="AG5" s="107"/>
+      <c r="AH5" s="107"/>
+      <c r="AI5" s="107"/>
+      <c r="AJ5" s="107"/>
+      <c r="AK5" s="107"/>
+      <c r="AL5" s="107"/>
+      <c r="AM5" s="107"/>
+      <c r="AN5" s="107"/>
+      <c r="AO5" s="107"/>
+      <c r="AP5" s="107"/>
+      <c r="AQ5" s="107"/>
+      <c r="AR5" s="107"/>
+      <c r="AS5" s="107"/>
+      <c r="AT5" s="107"/>
+      <c r="AU5" s="107"/>
+      <c r="AV5" s="107"/>
+      <c r="AW5" s="107"/>
+      <c r="AX5" s="107"/>
+      <c r="AY5" s="107"/>
+      <c r="AZ5" s="107"/>
+      <c r="BA5" s="107"/>
+      <c r="BB5" s="107"/>
+      <c r="BC5" s="107"/>
+      <c r="BD5" s="107"/>
+      <c r="BE5" s="107"/>
+      <c r="BF5" s="108"/>
+      <c r="BG5" s="108"/>
+      <c r="BH5" s="108"/>
+      <c r="BI5" s="108"/>
+      <c r="BJ5" s="108"/>
+      <c r="BK5" s="108"/>
+      <c r="BL5" s="108"/>
+      <c r="BM5" s="108"/>
+      <c r="BN5" s="108"/>
+      <c r="BO5" s="108"/>
+      <c r="BP5" s="108"/>
+      <c r="BQ5" s="108"/>
+      <c r="BR5" s="108"/>
+      <c r="BS5" s="108"/>
+      <c r="BT5" s="108"/>
+      <c r="BU5" s="108"/>
+      <c r="BV5" s="108"/>
+      <c r="BW5" s="108"/>
+      <c r="BX5" s="108"/>
+      <c r="BY5" s="108"/>
+      <c r="BZ5" s="108"/>
+      <c r="CA5" s="108"/>
+      <c r="CB5" s="108"/>
+      <c r="CC5" s="108"/>
+      <c r="CD5" s="108"/>
+      <c r="CE5" s="108"/>
+      <c r="CF5" s="108"/>
+      <c r="CG5" s="108"/>
+      <c r="CH5" s="108"/>
+      <c r="CI5" s="108"/>
+      <c r="CJ5" s="108"/>
+      <c r="CK5" s="108"/>
+      <c r="CL5" s="108"/>
+      <c r="CM5" s="108"/>
+      <c r="CN5" s="108"/>
+      <c r="CO5" s="108"/>
+      <c r="CP5" s="108"/>
+      <c r="CQ5" s="108"/>
+      <c r="CR5" s="108"/>
+      <c r="CS5" s="108"/>
+      <c r="CT5" s="108"/>
+      <c r="CU5" s="108"/>
+      <c r="CV5" s="108"/>
+      <c r="CW5" s="108"/>
+      <c r="CX5" s="108"/>
+      <c r="CY5" s="108"/>
+      <c r="CZ5" s="108"/>
+      <c r="DA5" s="108"/>
+      <c r="DB5" s="108"/>
+      <c r="DC5" s="108"/>
+      <c r="DD5" s="108"/>
+      <c r="DE5" s="108"/>
+      <c r="DF5" s="108"/>
+      <c r="DG5" s="108"/>
+      <c r="DH5" s="108"/>
+      <c r="DI5" s="108"/>
+      <c r="DJ5" s="108"/>
+      <c r="DK5" s="108"/>
+      <c r="DL5" s="108"/>
+      <c r="DM5" s="108"/>
+      <c r="DN5" s="108"/>
+      <c r="DO5" s="108"/>
+      <c r="DP5" s="108"/>
+      <c r="DQ5" s="108"/>
+      <c r="DR5" s="108"/>
+      <c r="DS5" s="108"/>
+      <c r="DT5" s="108"/>
+      <c r="DU5" s="108"/>
+      <c r="DV5" s="108"/>
+      <c r="DW5" s="108"/>
+      <c r="DX5" s="108"/>
+      <c r="DY5" s="108"/>
+      <c r="DZ5" s="108"/>
+      <c r="EA5" s="108"/>
+      <c r="EB5" s="108"/>
+      <c r="EC5" s="108"/>
+      <c r="ED5" s="108"/>
+      <c r="EE5" s="108"/>
+      <c r="EF5" s="108"/>
+      <c r="EG5" s="108"/>
+      <c r="EH5" s="107"/>
+      <c r="EI5" s="107"/>
+      <c r="EJ5" s="107"/>
+      <c r="EK5" s="107"/>
+      <c r="EL5" s="107"/>
+      <c r="EM5" s="107"/>
+      <c r="EN5" s="107"/>
+      <c r="EO5" s="107"/>
+      <c r="EP5" s="107"/>
+      <c r="EQ5" s="107"/>
+      <c r="ER5" s="107"/>
+      <c r="ES5" s="107"/>
+      <c r="ET5" s="107"/>
+      <c r="EU5" s="107"/>
+      <c r="EV5" s="107"/>
+      <c r="EW5" s="107"/>
+      <c r="EX5" s="107"/>
+      <c r="EY5" s="107"/>
+      <c r="EZ5" s="107"/>
+      <c r="FA5" s="107"/>
+      <c r="FB5" s="107"/>
+      <c r="FC5" s="107"/>
+      <c r="FD5" s="107"/>
+      <c r="FE5" s="107"/>
+      <c r="FF5" s="107"/>
+      <c r="FG5" s="107"/>
+      <c r="FH5" s="107"/>
+      <c r="FI5" s="107"/>
+      <c r="FJ5" s="107"/>
+      <c r="FK5" s="107"/>
+      <c r="FL5" s="107"/>
+      <c r="FM5" s="107"/>
+      <c r="FN5" s="107"/>
+      <c r="FO5" s="107"/>
+      <c r="FP5" s="107"/>
+      <c r="FQ5" s="107"/>
+      <c r="FR5" s="107"/>
+      <c r="FS5" s="107"/>
+      <c r="FT5" s="107"/>
+      <c r="FU5" s="107"/>
+      <c r="FV5" s="107"/>
+      <c r="FW5" s="107"/>
+      <c r="FX5" s="107"/>
+      <c r="FY5" s="107"/>
+      <c r="FZ5" s="107"/>
+      <c r="GA5" s="107"/>
+      <c r="GB5" s="107"/>
+      <c r="GC5" s="107"/>
+      <c r="GD5" s="107"/>
+      <c r="GE5" s="107"/>
+      <c r="GF5" s="107"/>
+      <c r="GG5" s="107"/>
+      <c r="GH5" s="107"/>
+      <c r="GI5" s="107"/>
+      <c r="GJ5" s="107"/>
+      <c r="GK5" s="107"/>
+      <c r="GL5" s="107"/>
+      <c r="GM5" s="107"/>
+      <c r="GN5" s="107"/>
+      <c r="GO5" s="107"/>
+      <c r="GP5" s="107"/>
+      <c r="GQ5" s="107"/>
+      <c r="GR5" s="107"/>
+      <c r="GS5" s="107"/>
+      <c r="GT5" s="107"/>
+      <c r="GU5" s="107"/>
+      <c r="GV5" s="107"/>
+    </row>
+    <row r="6" spans="1:204" s="83" customFormat="1" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="166" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="101">
+      <c r="B6" s="89">
         <v>1</v>
       </c>
-      <c r="C6" s="101">
+      <c r="C6" s="89">
         <v>1</v>
       </c>
-      <c r="D6" s="143">
+      <c r="D6" s="131">
         <v>1</v>
       </c>
-      <c r="E6" s="144">
+      <c r="E6" s="132">
         <v>1</v>
       </c>
-      <c r="F6" s="72">
+      <c r="F6" s="67">
         <v>1</v>
       </c>
-      <c r="G6" s="103">
+      <c r="G6" s="91">
         <v>1</v>
       </c>
-      <c r="H6" s="102">
+      <c r="H6" s="90">
         <v>1</v>
       </c>
-      <c r="I6" s="72">
+      <c r="I6" s="67">
         <v>1</v>
       </c>
-      <c r="J6" s="103">
+      <c r="J6" s="91">
         <v>1</v>
       </c>
-      <c r="K6" s="102">
+      <c r="K6" s="90">
         <v>1</v>
       </c>
-      <c r="L6" s="118">
+      <c r="L6" s="106">
         <v>1</v>
       </c>
-      <c r="M6" s="117">
+      <c r="M6" s="105">
         <v>1</v>
       </c>
-      <c r="N6" s="72">
+      <c r="N6" s="67">
         <v>1</v>
       </c>
-      <c r="O6" s="71">
+      <c r="O6" s="66">
         <v>1</v>
       </c>
-      <c r="P6" s="112"/>
-      <c r="Q6" s="112"/>
-      <c r="R6" s="114"/>
-      <c r="S6" s="99"/>
-      <c r="T6" s="110"/>
-      <c r="U6" s="110"/>
-      <c r="V6" s="110"/>
-      <c r="W6" s="110"/>
-      <c r="X6" s="110"/>
-      <c r="Y6" s="110"/>
-      <c r="Z6" s="110"/>
-      <c r="AA6" s="110"/>
-      <c r="AB6" s="110"/>
-      <c r="AC6" s="110"/>
-      <c r="AD6" s="110"/>
-      <c r="AE6" s="110"/>
-      <c r="AF6" s="110"/>
-      <c r="AG6" s="110"/>
-      <c r="AH6" s="110"/>
-      <c r="AI6" s="110"/>
-      <c r="AJ6" s="110"/>
-      <c r="AK6" s="110"/>
-      <c r="AL6" s="110"/>
-      <c r="AM6" s="110"/>
-      <c r="AN6" s="110"/>
-      <c r="AO6" s="110"/>
-      <c r="AP6" s="110"/>
-      <c r="AQ6" s="110"/>
-      <c r="AR6" s="110"/>
-      <c r="AS6" s="110"/>
-      <c r="AT6" s="108"/>
-      <c r="AU6" s="108"/>
-      <c r="AV6" s="108"/>
-      <c r="AW6" s="108"/>
-      <c r="AX6" s="108"/>
-      <c r="AY6" s="108"/>
-      <c r="AZ6" s="108"/>
-      <c r="BA6" s="108"/>
-      <c r="BB6" s="108"/>
-      <c r="BC6" s="108"/>
-      <c r="BD6" s="108"/>
-      <c r="BE6" s="108"/>
-      <c r="BF6" s="109"/>
-      <c r="BG6" s="109"/>
-      <c r="BH6" s="109"/>
-      <c r="BI6" s="109"/>
-      <c r="BJ6" s="109"/>
-      <c r="BK6" s="109"/>
-      <c r="BL6" s="109"/>
-      <c r="BM6" s="109"/>
-      <c r="BN6" s="109"/>
-      <c r="BO6" s="109"/>
-      <c r="BP6" s="109"/>
-      <c r="BQ6" s="109"/>
-      <c r="BR6" s="109"/>
-      <c r="BS6" s="109"/>
-      <c r="BT6" s="109"/>
-      <c r="BU6" s="109"/>
-      <c r="BV6" s="109"/>
-      <c r="BW6" s="109"/>
-      <c r="BX6" s="109"/>
-      <c r="BY6" s="109"/>
-      <c r="BZ6" s="109"/>
-      <c r="CA6" s="109"/>
-      <c r="CB6" s="109"/>
-      <c r="CC6" s="109"/>
-      <c r="CD6" s="109"/>
-      <c r="CE6" s="109"/>
-      <c r="CF6" s="109"/>
-      <c r="CG6" s="109"/>
-      <c r="CH6" s="109"/>
-      <c r="CI6" s="109"/>
-      <c r="CJ6" s="109"/>
-      <c r="CK6" s="109"/>
-      <c r="CL6" s="109"/>
-      <c r="CM6" s="109"/>
-      <c r="CN6" s="109"/>
-      <c r="CO6" s="109"/>
-      <c r="CP6" s="109"/>
-      <c r="CQ6" s="109"/>
-      <c r="CR6" s="109"/>
-      <c r="CS6" s="109"/>
-      <c r="CT6" s="109"/>
-      <c r="CU6" s="109"/>
-      <c r="CV6" s="109"/>
-      <c r="CW6" s="109"/>
-      <c r="CX6" s="109"/>
-      <c r="CY6" s="109"/>
-      <c r="CZ6" s="109"/>
-      <c r="DA6" s="109"/>
-      <c r="DB6" s="109"/>
-      <c r="DC6" s="109"/>
-      <c r="DD6" s="109"/>
-      <c r="DE6" s="109"/>
-      <c r="DF6" s="109"/>
-      <c r="DG6" s="109"/>
-      <c r="DH6" s="109"/>
-      <c r="DI6" s="109"/>
-      <c r="DJ6" s="109"/>
-      <c r="DK6" s="109"/>
-      <c r="DL6" s="109"/>
-      <c r="DM6" s="109"/>
-      <c r="DN6" s="109"/>
-      <c r="DO6" s="109"/>
-      <c r="DP6" s="109"/>
-      <c r="DQ6" s="109"/>
-      <c r="DR6" s="109"/>
-      <c r="DS6" s="109"/>
-      <c r="DT6" s="109"/>
-      <c r="DU6" s="109"/>
-      <c r="DV6" s="109"/>
-      <c r="DW6" s="109"/>
-      <c r="DX6" s="109"/>
-      <c r="DY6" s="109"/>
-      <c r="DZ6" s="109"/>
-      <c r="EA6" s="109"/>
-      <c r="EB6" s="109"/>
-      <c r="EC6" s="109"/>
-      <c r="ED6" s="109"/>
-      <c r="EE6" s="109"/>
-      <c r="EF6" s="109"/>
-      <c r="EG6" s="109"/>
-      <c r="EH6" s="108"/>
-      <c r="EI6" s="108"/>
-      <c r="EJ6" s="108"/>
-      <c r="EK6" s="108"/>
-      <c r="EL6" s="108"/>
-      <c r="EM6" s="108"/>
-      <c r="EN6" s="108"/>
-      <c r="EO6" s="108"/>
-      <c r="EP6" s="108"/>
-      <c r="EQ6" s="108"/>
-      <c r="ER6" s="108"/>
-      <c r="ES6" s="108"/>
-      <c r="ET6" s="108"/>
-      <c r="EU6" s="108"/>
-      <c r="EV6" s="108"/>
-      <c r="EW6" s="108"/>
-      <c r="EX6" s="108"/>
-      <c r="EY6" s="108"/>
-      <c r="EZ6" s="108"/>
-      <c r="FA6" s="108"/>
-      <c r="FB6" s="108"/>
-      <c r="FC6" s="108"/>
-      <c r="FD6" s="108"/>
-      <c r="FE6" s="108"/>
-      <c r="FF6" s="108"/>
-      <c r="FG6" s="108"/>
-      <c r="FH6" s="108"/>
-      <c r="FI6" s="108"/>
-      <c r="FJ6" s="108"/>
-      <c r="FK6" s="108"/>
-      <c r="FL6" s="108"/>
-      <c r="FM6" s="108"/>
-      <c r="FN6" s="108"/>
-      <c r="FO6" s="108"/>
-      <c r="FP6" s="108"/>
-      <c r="FQ6" s="108"/>
-      <c r="FR6" s="108"/>
-      <c r="FS6" s="108"/>
-      <c r="FT6" s="108"/>
-      <c r="FU6" s="108"/>
-      <c r="FV6" s="108"/>
-      <c r="FW6" s="108"/>
-      <c r="FX6" s="108"/>
-      <c r="FY6" s="108"/>
-      <c r="FZ6" s="108"/>
-      <c r="GA6" s="108"/>
-      <c r="GB6" s="108"/>
-      <c r="GC6" s="108"/>
-      <c r="GD6" s="108"/>
-      <c r="GE6" s="108"/>
-      <c r="GF6" s="108"/>
-      <c r="GG6" s="108"/>
-      <c r="GH6" s="108"/>
-      <c r="GI6" s="108"/>
-      <c r="GJ6" s="108"/>
-      <c r="GK6" s="108"/>
-      <c r="GL6" s="108"/>
-      <c r="GM6" s="108"/>
-      <c r="GN6" s="108"/>
-      <c r="GO6" s="108"/>
-      <c r="GP6" s="108"/>
-      <c r="GQ6" s="108"/>
-      <c r="GR6" s="108"/>
-      <c r="GS6" s="108"/>
-      <c r="GT6" s="108"/>
-      <c r="GU6" s="108"/>
-      <c r="GV6" s="108"/>
+      <c r="P6" s="100"/>
+      <c r="Q6" s="100"/>
+      <c r="R6" s="102"/>
+      <c r="S6" s="87"/>
+      <c r="T6" s="98"/>
+      <c r="U6" s="98"/>
+      <c r="V6" s="98"/>
+      <c r="W6" s="98"/>
+      <c r="X6" s="98"/>
+      <c r="Y6" s="98"/>
+      <c r="Z6" s="98"/>
+      <c r="AA6" s="98"/>
+      <c r="AB6" s="98"/>
+      <c r="AC6" s="98"/>
+      <c r="AD6" s="98"/>
+      <c r="AE6" s="98"/>
+      <c r="AF6" s="98"/>
+      <c r="AG6" s="98"/>
+      <c r="AH6" s="98"/>
+      <c r="AI6" s="98"/>
+      <c r="AJ6" s="98"/>
+      <c r="AK6" s="98"/>
+      <c r="AL6" s="98"/>
+      <c r="AM6" s="98"/>
+      <c r="AN6" s="98"/>
+      <c r="AO6" s="98"/>
+      <c r="AP6" s="98"/>
+      <c r="AQ6" s="98"/>
+      <c r="AR6" s="98"/>
+      <c r="AS6" s="98"/>
+      <c r="AT6" s="96"/>
+      <c r="AU6" s="96"/>
+      <c r="AV6" s="96"/>
+      <c r="AW6" s="96"/>
+      <c r="AX6" s="96"/>
+      <c r="AY6" s="96"/>
+      <c r="AZ6" s="96"/>
+      <c r="BA6" s="96"/>
+      <c r="BB6" s="96"/>
+      <c r="BC6" s="96"/>
+      <c r="BD6" s="96"/>
+      <c r="BE6" s="96"/>
+      <c r="BF6" s="97"/>
+      <c r="BG6" s="97"/>
+      <c r="BH6" s="97"/>
+      <c r="BI6" s="97"/>
+      <c r="BJ6" s="97"/>
+      <c r="BK6" s="97"/>
+      <c r="BL6" s="97"/>
+      <c r="BM6" s="97"/>
+      <c r="BN6" s="97"/>
+      <c r="BO6" s="97"/>
+      <c r="BP6" s="97"/>
+      <c r="BQ6" s="97"/>
+      <c r="BR6" s="97"/>
+      <c r="BS6" s="97"/>
+      <c r="BT6" s="97"/>
+      <c r="BU6" s="97"/>
+      <c r="BV6" s="97"/>
+      <c r="BW6" s="97"/>
+      <c r="BX6" s="97"/>
+      <c r="BY6" s="97"/>
+      <c r="BZ6" s="97"/>
+      <c r="CA6" s="97"/>
+      <c r="CB6" s="97"/>
+      <c r="CC6" s="97"/>
+      <c r="CD6" s="97"/>
+      <c r="CE6" s="97"/>
+      <c r="CF6" s="97"/>
+      <c r="CG6" s="97"/>
+      <c r="CH6" s="97"/>
+      <c r="CI6" s="97"/>
+      <c r="CJ6" s="97"/>
+      <c r="CK6" s="97"/>
+      <c r="CL6" s="97"/>
+      <c r="CM6" s="97"/>
+      <c r="CN6" s="97"/>
+      <c r="CO6" s="97"/>
+      <c r="CP6" s="97"/>
+      <c r="CQ6" s="97"/>
+      <c r="CR6" s="97"/>
+      <c r="CS6" s="97"/>
+      <c r="CT6" s="97"/>
+      <c r="CU6" s="97"/>
+      <c r="CV6" s="97"/>
+      <c r="CW6" s="97"/>
+      <c r="CX6" s="97"/>
+      <c r="CY6" s="97"/>
+      <c r="CZ6" s="97"/>
+      <c r="DA6" s="97"/>
+      <c r="DB6" s="97"/>
+      <c r="DC6" s="97"/>
+      <c r="DD6" s="97"/>
+      <c r="DE6" s="97"/>
+      <c r="DF6" s="97"/>
+      <c r="DG6" s="97"/>
+      <c r="DH6" s="97"/>
+      <c r="DI6" s="97"/>
+      <c r="DJ6" s="97"/>
+      <c r="DK6" s="97"/>
+      <c r="DL6" s="97"/>
+      <c r="DM6" s="97"/>
+      <c r="DN6" s="97"/>
+      <c r="DO6" s="97"/>
+      <c r="DP6" s="97"/>
+      <c r="DQ6" s="97"/>
+      <c r="DR6" s="97"/>
+      <c r="DS6" s="97"/>
+      <c r="DT6" s="97"/>
+      <c r="DU6" s="97"/>
+      <c r="DV6" s="97"/>
+      <c r="DW6" s="97"/>
+      <c r="DX6" s="97"/>
+      <c r="DY6" s="97"/>
+      <c r="DZ6" s="97"/>
+      <c r="EA6" s="97"/>
+      <c r="EB6" s="97"/>
+      <c r="EC6" s="97"/>
+      <c r="ED6" s="97"/>
+      <c r="EE6" s="97"/>
+      <c r="EF6" s="97"/>
+      <c r="EG6" s="97"/>
+      <c r="EH6" s="96"/>
+      <c r="EI6" s="96"/>
+      <c r="EJ6" s="96"/>
+      <c r="EK6" s="96"/>
+      <c r="EL6" s="96"/>
+      <c r="EM6" s="96"/>
+      <c r="EN6" s="96"/>
+      <c r="EO6" s="96"/>
+      <c r="EP6" s="96"/>
+      <c r="EQ6" s="96"/>
+      <c r="ER6" s="96"/>
+      <c r="ES6" s="96"/>
+      <c r="ET6" s="96"/>
+      <c r="EU6" s="96"/>
+      <c r="EV6" s="96"/>
+      <c r="EW6" s="96"/>
+      <c r="EX6" s="96"/>
+      <c r="EY6" s="96"/>
+      <c r="EZ6" s="96"/>
+      <c r="FA6" s="96"/>
+      <c r="FB6" s="96"/>
+      <c r="FC6" s="96"/>
+      <c r="FD6" s="96"/>
+      <c r="FE6" s="96"/>
+      <c r="FF6" s="96"/>
+      <c r="FG6" s="96"/>
+      <c r="FH6" s="96"/>
+      <c r="FI6" s="96"/>
+      <c r="FJ6" s="96"/>
+      <c r="FK6" s="96"/>
+      <c r="FL6" s="96"/>
+      <c r="FM6" s="96"/>
+      <c r="FN6" s="96"/>
+      <c r="FO6" s="96"/>
+      <c r="FP6" s="96"/>
+      <c r="FQ6" s="96"/>
+      <c r="FR6" s="96"/>
+      <c r="FS6" s="96"/>
+      <c r="FT6" s="96"/>
+      <c r="FU6" s="96"/>
+      <c r="FV6" s="96"/>
+      <c r="FW6" s="96"/>
+      <c r="FX6" s="96"/>
+      <c r="FY6" s="96"/>
+      <c r="FZ6" s="96"/>
+      <c r="GA6" s="96"/>
+      <c r="GB6" s="96"/>
+      <c r="GC6" s="96"/>
+      <c r="GD6" s="96"/>
+      <c r="GE6" s="96"/>
+      <c r="GF6" s="96"/>
+      <c r="GG6" s="96"/>
+      <c r="GH6" s="96"/>
+      <c r="GI6" s="96"/>
+      <c r="GJ6" s="96"/>
+      <c r="GK6" s="96"/>
+      <c r="GL6" s="96"/>
+      <c r="GM6" s="96"/>
+      <c r="GN6" s="96"/>
+      <c r="GO6" s="96"/>
+      <c r="GP6" s="96"/>
+      <c r="GQ6" s="96"/>
+      <c r="GR6" s="96"/>
+      <c r="GS6" s="96"/>
+      <c r="GT6" s="96"/>
+      <c r="GU6" s="96"/>
+      <c r="GV6" s="96"/>
     </row>
     <row r="7" spans="1:204" ht="21.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="167"/>
-      <c r="B7" s="145" t="s">
+      <c r="A7" s="166"/>
+      <c r="B7" s="133" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="145" t="s">
+      <c r="C7" s="133" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="145">
+      <c r="D7" s="133">
         <f>C6-D6</f>
         <v>0</v>
       </c>
-      <c r="E7" s="145">
+      <c r="E7" s="133">
         <f>C6-E6</f>
         <v>0</v>
       </c>
-      <c r="F7" s="146" t="s">
+      <c r="F7" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="146">
+      <c r="G7" s="134">
         <f>F6-G6</f>
         <v>0</v>
       </c>
-      <c r="H7" s="146">
+      <c r="H7" s="134">
         <f>F6-H6</f>
         <v>0</v>
       </c>
-      <c r="I7" s="146" t="s">
+      <c r="I7" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="J7" s="146">
+      <c r="J7" s="134">
         <f>I6-J6</f>
         <v>0</v>
       </c>
-      <c r="K7" s="146">
+      <c r="K7" s="134">
         <f>I6-K6</f>
         <v>0</v>
       </c>
-      <c r="L7" s="145">
+      <c r="L7" s="133">
         <f>L6-M6</f>
         <v>0</v>
       </c>
-      <c r="M7" s="94">
+      <c r="M7" s="82">
         <f>IFERROR(L6/M6, 0)</f>
         <v>1</v>
       </c>
-      <c r="N7" s="168">
+      <c r="N7" s="157">
         <f>N6-O6</f>
         <v>0</v>
       </c>
-      <c r="O7" s="169" t="str">
+      <c r="O7" s="158" t="str">
         <f>IF(TEXT(N6-O6,"+0,0; -0,0")="+0,0","0,0",TEXT(N6-O6,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
-      <c r="P7" s="91"/>
-      <c r="Q7" s="91"/>
-      <c r="R7" s="111"/>
-      <c r="S7" s="99"/>
-      <c r="T7" s="106"/>
-      <c r="U7" s="106"/>
-      <c r="V7" s="106"/>
-      <c r="W7" s="106"/>
-      <c r="X7" s="106"/>
-      <c r="Y7" s="106"/>
-      <c r="Z7" s="106"/>
-      <c r="AA7" s="106"/>
-      <c r="AB7" s="106"/>
-      <c r="AC7" s="106"/>
-      <c r="AD7" s="106"/>
-      <c r="AE7" s="106"/>
-      <c r="AF7" s="106"/>
-      <c r="AG7" s="106"/>
-      <c r="AH7" s="106"/>
-      <c r="AI7" s="116"/>
-      <c r="AJ7" s="116"/>
-      <c r="AK7" s="116"/>
-      <c r="AL7" s="116"/>
-      <c r="AM7" s="116"/>
-      <c r="AN7" s="116"/>
-      <c r="AO7" s="116"/>
-      <c r="AP7" s="116"/>
-      <c r="AQ7" s="116"/>
-      <c r="AR7" s="116"/>
-      <c r="AS7" s="116"/>
-      <c r="AT7" s="116"/>
-      <c r="AU7" s="116"/>
-      <c r="AV7" s="116"/>
-      <c r="AW7" s="116"/>
-      <c r="AX7" s="116"/>
-      <c r="AY7" s="116"/>
-      <c r="AZ7" s="116"/>
-      <c r="BA7" s="116"/>
-      <c r="BB7" s="116"/>
-      <c r="BC7" s="116"/>
-      <c r="BD7" s="116"/>
-      <c r="BE7" s="116"/>
-      <c r="BF7" s="116"/>
-      <c r="BG7" s="116"/>
-      <c r="BH7" s="116"/>
-      <c r="BI7" s="116"/>
-      <c r="BJ7" s="116"/>
-      <c r="BK7" s="116"/>
-      <c r="BL7" s="116"/>
-      <c r="BM7" s="116"/>
-      <c r="BN7" s="116"/>
-      <c r="BO7" s="116"/>
-      <c r="BP7" s="116"/>
-      <c r="BQ7" s="116"/>
-      <c r="BR7" s="116"/>
-      <c r="BS7" s="116"/>
-      <c r="BT7" s="116"/>
-      <c r="BU7" s="116"/>
-      <c r="BV7" s="116"/>
-      <c r="BW7" s="116"/>
-      <c r="BX7" s="116"/>
-      <c r="BY7" s="116"/>
-      <c r="BZ7" s="116"/>
-      <c r="CA7" s="116"/>
-      <c r="CB7" s="116"/>
-      <c r="CC7" s="116"/>
-      <c r="CD7" s="116"/>
-      <c r="CE7" s="116"/>
-      <c r="CF7" s="116"/>
-      <c r="CG7" s="116"/>
-      <c r="CH7" s="116"/>
-      <c r="CI7" s="116"/>
-      <c r="CJ7" s="116"/>
-      <c r="CK7" s="116"/>
-      <c r="CL7" s="116"/>
-      <c r="CM7" s="116"/>
-      <c r="CN7" s="116"/>
-      <c r="CO7" s="116"/>
-      <c r="CP7" s="116"/>
-      <c r="CQ7" s="116"/>
-      <c r="CR7" s="116"/>
-      <c r="CS7" s="116"/>
-      <c r="CT7" s="116"/>
-      <c r="CU7" s="116"/>
-      <c r="CV7" s="116"/>
-      <c r="CW7" s="116"/>
-      <c r="CX7" s="116"/>
-      <c r="CY7" s="116"/>
-      <c r="CZ7" s="116"/>
-      <c r="DA7" s="116"/>
-      <c r="DB7" s="116"/>
-      <c r="DC7" s="116"/>
-      <c r="DD7" s="116"/>
-      <c r="DE7" s="116"/>
-      <c r="DF7" s="116"/>
-      <c r="DG7" s="116"/>
-      <c r="DH7" s="116"/>
-      <c r="DI7" s="116"/>
-      <c r="DJ7" s="116"/>
-      <c r="DK7" s="116"/>
-      <c r="DL7" s="116"/>
-      <c r="DM7" s="116"/>
-      <c r="DN7" s="116"/>
-      <c r="DO7" s="116"/>
-      <c r="DP7" s="116"/>
-      <c r="DQ7" s="116"/>
-      <c r="DR7" s="116"/>
-      <c r="DS7" s="116"/>
-      <c r="DT7" s="116"/>
-      <c r="DU7" s="116"/>
-      <c r="DV7" s="116"/>
-      <c r="DW7" s="116"/>
-      <c r="DX7" s="116"/>
-      <c r="DY7" s="116"/>
-      <c r="DZ7" s="116"/>
-      <c r="EA7" s="116"/>
-      <c r="EB7" s="116"/>
-      <c r="EC7" s="116"/>
-      <c r="ED7" s="116"/>
-      <c r="EE7" s="116"/>
-      <c r="EF7" s="116"/>
-      <c r="EG7" s="116"/>
-      <c r="EH7" s="115"/>
-      <c r="EI7" s="115"/>
-      <c r="EJ7" s="115"/>
-      <c r="EK7" s="115"/>
-      <c r="EL7" s="115"/>
-      <c r="EM7" s="115"/>
-      <c r="EN7" s="115"/>
-      <c r="EO7" s="115"/>
-      <c r="EP7" s="115"/>
-      <c r="EQ7" s="115"/>
-      <c r="ER7" s="115"/>
-      <c r="ES7" s="115"/>
-      <c r="ET7" s="115"/>
-      <c r="EU7" s="115"/>
-      <c r="EV7" s="115"/>
-      <c r="EW7" s="115"/>
-      <c r="EX7" s="115"/>
-      <c r="EY7" s="115"/>
-      <c r="EZ7" s="115"/>
-      <c r="FA7" s="115"/>
-      <c r="FB7" s="115"/>
-      <c r="FC7" s="115"/>
-      <c r="FD7" s="115"/>
-      <c r="FE7" s="115"/>
-      <c r="FF7" s="115"/>
-      <c r="FG7" s="115"/>
-      <c r="FH7" s="115"/>
-      <c r="FI7" s="115"/>
-      <c r="FJ7" s="115"/>
-      <c r="FK7" s="115"/>
-      <c r="FL7" s="115"/>
-      <c r="FM7" s="115"/>
-      <c r="FN7" s="115"/>
-      <c r="FO7" s="115"/>
-      <c r="FP7" s="115"/>
-      <c r="FQ7" s="115"/>
-      <c r="FR7" s="115"/>
-      <c r="FS7" s="115"/>
-      <c r="FT7" s="115"/>
-      <c r="FU7" s="115"/>
-      <c r="FV7" s="115"/>
-      <c r="FW7" s="115"/>
-      <c r="FX7" s="115"/>
-      <c r="FY7" s="115"/>
-      <c r="FZ7" s="115"/>
-      <c r="GA7" s="115"/>
-      <c r="GB7" s="115"/>
-      <c r="GC7" s="115"/>
-      <c r="GD7" s="115"/>
-      <c r="GE7" s="115"/>
-      <c r="GF7" s="115"/>
-      <c r="GG7" s="115"/>
-      <c r="GH7" s="115"/>
-      <c r="GI7" s="115"/>
-      <c r="GJ7" s="115"/>
-      <c r="GK7" s="115"/>
-      <c r="GL7" s="115"/>
-      <c r="GM7" s="115"/>
-      <c r="GN7" s="115"/>
-      <c r="GO7" s="115"/>
-      <c r="GP7" s="115"/>
-      <c r="GQ7" s="115"/>
-      <c r="GR7" s="115"/>
-      <c r="GS7" s="115"/>
-      <c r="GT7" s="115"/>
-      <c r="GU7" s="115"/>
-      <c r="GV7" s="115"/>
-    </row>
-    <row r="8" spans="1:204" s="95" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="167" t="s">
+      <c r="P7" s="79"/>
+      <c r="Q7" s="79"/>
+      <c r="R7" s="99"/>
+      <c r="S7" s="87"/>
+      <c r="T7" s="94"/>
+      <c r="U7" s="94"/>
+      <c r="V7" s="94"/>
+      <c r="W7" s="94"/>
+      <c r="X7" s="94"/>
+      <c r="Y7" s="94"/>
+      <c r="Z7" s="94"/>
+      <c r="AA7" s="94"/>
+      <c r="AB7" s="94"/>
+      <c r="AC7" s="94"/>
+      <c r="AD7" s="94"/>
+      <c r="AE7" s="94"/>
+      <c r="AF7" s="94"/>
+      <c r="AG7" s="94"/>
+      <c r="AH7" s="94"/>
+      <c r="AI7" s="104"/>
+      <c r="AJ7" s="104"/>
+      <c r="AK7" s="104"/>
+      <c r="AL7" s="104"/>
+      <c r="AM7" s="104"/>
+      <c r="AN7" s="104"/>
+      <c r="AO7" s="104"/>
+      <c r="AP7" s="104"/>
+      <c r="AQ7" s="104"/>
+      <c r="AR7" s="104"/>
+      <c r="AS7" s="104"/>
+      <c r="AT7" s="104"/>
+      <c r="AU7" s="104"/>
+      <c r="AV7" s="104"/>
+      <c r="AW7" s="104"/>
+      <c r="AX7" s="104"/>
+      <c r="AY7" s="104"/>
+      <c r="AZ7" s="104"/>
+      <c r="BA7" s="104"/>
+      <c r="BB7" s="104"/>
+      <c r="BC7" s="104"/>
+      <c r="BD7" s="104"/>
+      <c r="BE7" s="104"/>
+      <c r="BF7" s="104"/>
+      <c r="BG7" s="104"/>
+      <c r="BH7" s="104"/>
+      <c r="BI7" s="104"/>
+      <c r="BJ7" s="104"/>
+      <c r="BK7" s="104"/>
+      <c r="BL7" s="104"/>
+      <c r="BM7" s="104"/>
+      <c r="BN7" s="104"/>
+      <c r="BO7" s="104"/>
+      <c r="BP7" s="104"/>
+      <c r="BQ7" s="104"/>
+      <c r="BR7" s="104"/>
+      <c r="BS7" s="104"/>
+      <c r="BT7" s="104"/>
+      <c r="BU7" s="104"/>
+      <c r="BV7" s="104"/>
+      <c r="BW7" s="104"/>
+      <c r="BX7" s="104"/>
+      <c r="BY7" s="104"/>
+      <c r="BZ7" s="104"/>
+      <c r="CA7" s="104"/>
+      <c r="CB7" s="104"/>
+      <c r="CC7" s="104"/>
+      <c r="CD7" s="104"/>
+      <c r="CE7" s="104"/>
+      <c r="CF7" s="104"/>
+      <c r="CG7" s="104"/>
+      <c r="CH7" s="104"/>
+      <c r="CI7" s="104"/>
+      <c r="CJ7" s="104"/>
+      <c r="CK7" s="104"/>
+      <c r="CL7" s="104"/>
+      <c r="CM7" s="104"/>
+      <c r="CN7" s="104"/>
+      <c r="CO7" s="104"/>
+      <c r="CP7" s="104"/>
+      <c r="CQ7" s="104"/>
+      <c r="CR7" s="104"/>
+      <c r="CS7" s="104"/>
+      <c r="CT7" s="104"/>
+      <c r="CU7" s="104"/>
+      <c r="CV7" s="104"/>
+      <c r="CW7" s="104"/>
+      <c r="CX7" s="104"/>
+      <c r="CY7" s="104"/>
+      <c r="CZ7" s="104"/>
+      <c r="DA7" s="104"/>
+      <c r="DB7" s="104"/>
+      <c r="DC7" s="104"/>
+      <c r="DD7" s="104"/>
+      <c r="DE7" s="104"/>
+      <c r="DF7" s="104"/>
+      <c r="DG7" s="104"/>
+      <c r="DH7" s="104"/>
+      <c r="DI7" s="104"/>
+      <c r="DJ7" s="104"/>
+      <c r="DK7" s="104"/>
+      <c r="DL7" s="104"/>
+      <c r="DM7" s="104"/>
+      <c r="DN7" s="104"/>
+      <c r="DO7" s="104"/>
+      <c r="DP7" s="104"/>
+      <c r="DQ7" s="104"/>
+      <c r="DR7" s="104"/>
+      <c r="DS7" s="104"/>
+      <c r="DT7" s="104"/>
+      <c r="DU7" s="104"/>
+      <c r="DV7" s="104"/>
+      <c r="DW7" s="104"/>
+      <c r="DX7" s="104"/>
+      <c r="DY7" s="104"/>
+      <c r="DZ7" s="104"/>
+      <c r="EA7" s="104"/>
+      <c r="EB7" s="104"/>
+      <c r="EC7" s="104"/>
+      <c r="ED7" s="104"/>
+      <c r="EE7" s="104"/>
+      <c r="EF7" s="104"/>
+      <c r="EG7" s="104"/>
+      <c r="EH7" s="103"/>
+      <c r="EI7" s="103"/>
+      <c r="EJ7" s="103"/>
+      <c r="EK7" s="103"/>
+      <c r="EL7" s="103"/>
+      <c r="EM7" s="103"/>
+      <c r="EN7" s="103"/>
+      <c r="EO7" s="103"/>
+      <c r="EP7" s="103"/>
+      <c r="EQ7" s="103"/>
+      <c r="ER7" s="103"/>
+      <c r="ES7" s="103"/>
+      <c r="ET7" s="103"/>
+      <c r="EU7" s="103"/>
+      <c r="EV7" s="103"/>
+      <c r="EW7" s="103"/>
+      <c r="EX7" s="103"/>
+      <c r="EY7" s="103"/>
+      <c r="EZ7" s="103"/>
+      <c r="FA7" s="103"/>
+      <c r="FB7" s="103"/>
+      <c r="FC7" s="103"/>
+      <c r="FD7" s="103"/>
+      <c r="FE7" s="103"/>
+      <c r="FF7" s="103"/>
+      <c r="FG7" s="103"/>
+      <c r="FH7" s="103"/>
+      <c r="FI7" s="103"/>
+      <c r="FJ7" s="103"/>
+      <c r="FK7" s="103"/>
+      <c r="FL7" s="103"/>
+      <c r="FM7" s="103"/>
+      <c r="FN7" s="103"/>
+      <c r="FO7" s="103"/>
+      <c r="FP7" s="103"/>
+      <c r="FQ7" s="103"/>
+      <c r="FR7" s="103"/>
+      <c r="FS7" s="103"/>
+      <c r="FT7" s="103"/>
+      <c r="FU7" s="103"/>
+      <c r="FV7" s="103"/>
+      <c r="FW7" s="103"/>
+      <c r="FX7" s="103"/>
+      <c r="FY7" s="103"/>
+      <c r="FZ7" s="103"/>
+      <c r="GA7" s="103"/>
+      <c r="GB7" s="103"/>
+      <c r="GC7" s="103"/>
+      <c r="GD7" s="103"/>
+      <c r="GE7" s="103"/>
+      <c r="GF7" s="103"/>
+      <c r="GG7" s="103"/>
+      <c r="GH7" s="103"/>
+      <c r="GI7" s="103"/>
+      <c r="GJ7" s="103"/>
+      <c r="GK7" s="103"/>
+      <c r="GL7" s="103"/>
+      <c r="GM7" s="103"/>
+      <c r="GN7" s="103"/>
+      <c r="GO7" s="103"/>
+      <c r="GP7" s="103"/>
+      <c r="GQ7" s="103"/>
+      <c r="GR7" s="103"/>
+      <c r="GS7" s="103"/>
+      <c r="GT7" s="103"/>
+      <c r="GU7" s="103"/>
+      <c r="GV7" s="103"/>
+    </row>
+    <row r="8" spans="1:204" s="83" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="166" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="101">
+      <c r="B8" s="89">
         <v>1</v>
       </c>
-      <c r="C8" s="101">
+      <c r="C8" s="89">
         <v>1</v>
       </c>
-      <c r="D8" s="143">
+      <c r="D8" s="131">
         <v>1</v>
       </c>
-      <c r="E8" s="144">
+      <c r="E8" s="132">
         <v>1</v>
       </c>
-      <c r="F8" s="72">
+      <c r="F8" s="67">
         <v>1</v>
       </c>
-      <c r="G8" s="103">
+      <c r="G8" s="91">
         <v>1</v>
       </c>
-      <c r="H8" s="102">
+      <c r="H8" s="90">
         <v>1</v>
       </c>
-      <c r="I8" s="72">
+      <c r="I8" s="67">
         <v>1</v>
       </c>
-      <c r="J8" s="103">
+      <c r="J8" s="91">
         <v>1</v>
       </c>
-      <c r="K8" s="102">
+      <c r="K8" s="90">
         <v>1</v>
       </c>
-      <c r="L8" s="101">
+      <c r="L8" s="89">
         <v>1</v>
       </c>
-      <c r="M8" s="139">
+      <c r="M8" s="127">
         <v>1</v>
       </c>
-      <c r="N8" s="72">
+      <c r="N8" s="67">
         <v>1</v>
       </c>
-      <c r="O8" s="71">
+      <c r="O8" s="66">
         <v>1</v>
       </c>
-      <c r="P8" s="112"/>
-      <c r="Q8" s="112"/>
-      <c r="R8" s="111"/>
-      <c r="S8" s="99"/>
-      <c r="T8" s="110"/>
-      <c r="U8" s="110"/>
-      <c r="V8" s="110"/>
-      <c r="W8" s="110"/>
-      <c r="X8" s="110"/>
-      <c r="Y8" s="110"/>
-      <c r="Z8" s="110"/>
-      <c r="AA8" s="110"/>
-      <c r="AB8" s="110"/>
-      <c r="AC8" s="110"/>
-      <c r="AD8" s="110"/>
-      <c r="AE8" s="110"/>
-      <c r="AF8" s="110"/>
-      <c r="AG8" s="110"/>
-      <c r="AH8" s="110"/>
-      <c r="AI8" s="110"/>
-      <c r="AJ8" s="110"/>
-      <c r="AK8" s="110"/>
-      <c r="AL8" s="110"/>
-      <c r="AM8" s="110"/>
-      <c r="AN8" s="110"/>
-      <c r="AO8" s="110"/>
-      <c r="AP8" s="110"/>
-      <c r="AQ8" s="110"/>
-      <c r="AR8" s="110"/>
-      <c r="AS8" s="110"/>
-      <c r="AT8" s="108"/>
-      <c r="AU8" s="108"/>
-      <c r="AV8" s="108"/>
-      <c r="AW8" s="108"/>
-      <c r="AX8" s="108"/>
-      <c r="AY8" s="108"/>
-      <c r="AZ8" s="108"/>
-      <c r="BA8" s="108"/>
-      <c r="BB8" s="108"/>
-      <c r="BC8" s="108"/>
-      <c r="BD8" s="108"/>
-      <c r="BE8" s="108"/>
-      <c r="BF8" s="109"/>
-      <c r="BG8" s="109"/>
-      <c r="BH8" s="109"/>
-      <c r="BI8" s="109"/>
-      <c r="BJ8" s="109"/>
-      <c r="BK8" s="109"/>
-      <c r="BL8" s="109"/>
-      <c r="BM8" s="109"/>
-      <c r="BN8" s="109"/>
-      <c r="BO8" s="109"/>
-      <c r="BP8" s="109"/>
-      <c r="BQ8" s="109"/>
-      <c r="BR8" s="109"/>
-      <c r="BS8" s="109"/>
-      <c r="BT8" s="109"/>
-      <c r="BU8" s="109"/>
-      <c r="BV8" s="109"/>
-      <c r="BW8" s="109"/>
-      <c r="BX8" s="109"/>
-      <c r="BY8" s="109"/>
-      <c r="BZ8" s="109"/>
-      <c r="CA8" s="109"/>
-      <c r="CB8" s="109"/>
-      <c r="CC8" s="109"/>
-      <c r="CD8" s="109"/>
-      <c r="CE8" s="109"/>
-      <c r="CF8" s="109"/>
-      <c r="CG8" s="109"/>
-      <c r="CH8" s="109"/>
-      <c r="CI8" s="109"/>
-      <c r="CJ8" s="109"/>
-      <c r="CK8" s="109"/>
-      <c r="CL8" s="109"/>
-      <c r="CM8" s="109"/>
-      <c r="CN8" s="109"/>
-      <c r="CO8" s="109"/>
-      <c r="CP8" s="109"/>
-      <c r="CQ8" s="109"/>
-      <c r="CR8" s="109"/>
-      <c r="CS8" s="109"/>
-      <c r="CT8" s="109"/>
-      <c r="CU8" s="109"/>
-      <c r="CV8" s="109"/>
-      <c r="CW8" s="109"/>
-      <c r="CX8" s="109"/>
-      <c r="CY8" s="109"/>
-      <c r="CZ8" s="109"/>
-      <c r="DA8" s="109"/>
-      <c r="DB8" s="109"/>
-      <c r="DC8" s="109"/>
-      <c r="DD8" s="109"/>
-      <c r="DE8" s="109"/>
-      <c r="DF8" s="109"/>
-      <c r="DG8" s="109"/>
-      <c r="DH8" s="109"/>
-      <c r="DI8" s="109"/>
-      <c r="DJ8" s="109"/>
-      <c r="DK8" s="109"/>
-      <c r="DL8" s="109"/>
-      <c r="DM8" s="109"/>
-      <c r="DN8" s="109"/>
-      <c r="DO8" s="109"/>
-      <c r="DP8" s="109"/>
-      <c r="DQ8" s="109"/>
-      <c r="DR8" s="109"/>
-      <c r="DS8" s="109"/>
-      <c r="DT8" s="109"/>
-      <c r="DU8" s="109"/>
-      <c r="DV8" s="109"/>
-      <c r="DW8" s="109"/>
-      <c r="DX8" s="109"/>
-      <c r="DY8" s="109"/>
-      <c r="DZ8" s="109"/>
-      <c r="EA8" s="109"/>
-      <c r="EB8" s="109"/>
-      <c r="EC8" s="109"/>
-      <c r="ED8" s="109"/>
-      <c r="EE8" s="109"/>
-      <c r="EF8" s="109"/>
-      <c r="EG8" s="109"/>
-      <c r="EH8" s="108"/>
-      <c r="EI8" s="108"/>
-      <c r="EJ8" s="108"/>
-      <c r="EK8" s="108"/>
-      <c r="EL8" s="108"/>
-      <c r="EM8" s="108"/>
-      <c r="EN8" s="108"/>
-      <c r="EO8" s="108"/>
-      <c r="EP8" s="108"/>
-      <c r="EQ8" s="108"/>
-      <c r="ER8" s="108"/>
-      <c r="ES8" s="108"/>
-      <c r="ET8" s="108"/>
-      <c r="EU8" s="108"/>
-      <c r="EV8" s="108"/>
-      <c r="EW8" s="108"/>
-      <c r="EX8" s="108"/>
-      <c r="EY8" s="108"/>
-      <c r="EZ8" s="108"/>
-      <c r="FA8" s="108"/>
-      <c r="FB8" s="108"/>
-      <c r="FC8" s="108"/>
-      <c r="FD8" s="108"/>
-      <c r="FE8" s="108"/>
-      <c r="FF8" s="108"/>
-      <c r="FG8" s="108"/>
-      <c r="FH8" s="108"/>
-      <c r="FI8" s="108"/>
-      <c r="FJ8" s="108"/>
-      <c r="FK8" s="108"/>
-      <c r="FL8" s="108"/>
-      <c r="FM8" s="108"/>
-      <c r="FN8" s="108"/>
-      <c r="FO8" s="108"/>
-      <c r="FP8" s="108"/>
-      <c r="FQ8" s="108"/>
-      <c r="FR8" s="108"/>
-      <c r="FS8" s="108"/>
-      <c r="FT8" s="108"/>
-      <c r="FU8" s="108"/>
-      <c r="FV8" s="108"/>
-      <c r="FW8" s="108"/>
-      <c r="FX8" s="108"/>
-      <c r="FY8" s="108"/>
-      <c r="FZ8" s="108"/>
-      <c r="GA8" s="108"/>
-      <c r="GB8" s="108"/>
-      <c r="GC8" s="108"/>
-      <c r="GD8" s="108"/>
-      <c r="GE8" s="108"/>
-      <c r="GF8" s="108"/>
-      <c r="GG8" s="108"/>
-      <c r="GH8" s="108"/>
-      <c r="GI8" s="108"/>
-      <c r="GJ8" s="108"/>
-      <c r="GK8" s="108"/>
-      <c r="GL8" s="108"/>
-      <c r="GM8" s="108"/>
-      <c r="GN8" s="108"/>
-      <c r="GO8" s="108"/>
-      <c r="GP8" s="108"/>
-      <c r="GQ8" s="108"/>
-      <c r="GR8" s="108"/>
-      <c r="GS8" s="108"/>
-      <c r="GT8" s="108"/>
-      <c r="GU8" s="108"/>
-      <c r="GV8" s="108"/>
+      <c r="P8" s="100"/>
+      <c r="Q8" s="100"/>
+      <c r="R8" s="99"/>
+      <c r="S8" s="87"/>
+      <c r="T8" s="98"/>
+      <c r="U8" s="98"/>
+      <c r="V8" s="98"/>
+      <c r="W8" s="98"/>
+      <c r="X8" s="98"/>
+      <c r="Y8" s="98"/>
+      <c r="Z8" s="98"/>
+      <c r="AA8" s="98"/>
+      <c r="AB8" s="98"/>
+      <c r="AC8" s="98"/>
+      <c r="AD8" s="98"/>
+      <c r="AE8" s="98"/>
+      <c r="AF8" s="98"/>
+      <c r="AG8" s="98"/>
+      <c r="AH8" s="98"/>
+      <c r="AI8" s="98"/>
+      <c r="AJ8" s="98"/>
+      <c r="AK8" s="98"/>
+      <c r="AL8" s="98"/>
+      <c r="AM8" s="98"/>
+      <c r="AN8" s="98"/>
+      <c r="AO8" s="98"/>
+      <c r="AP8" s="98"/>
+      <c r="AQ8" s="98"/>
+      <c r="AR8" s="98"/>
+      <c r="AS8" s="98"/>
+      <c r="AT8" s="96"/>
+      <c r="AU8" s="96"/>
+      <c r="AV8" s="96"/>
+      <c r="AW8" s="96"/>
+      <c r="AX8" s="96"/>
+      <c r="AY8" s="96"/>
+      <c r="AZ8" s="96"/>
+      <c r="BA8" s="96"/>
+      <c r="BB8" s="96"/>
+      <c r="BC8" s="96"/>
+      <c r="BD8" s="96"/>
+      <c r="BE8" s="96"/>
+      <c r="BF8" s="97"/>
+      <c r="BG8" s="97"/>
+      <c r="BH8" s="97"/>
+      <c r="BI8" s="97"/>
+      <c r="BJ8" s="97"/>
+      <c r="BK8" s="97"/>
+      <c r="BL8" s="97"/>
+      <c r="BM8" s="97"/>
+      <c r="BN8" s="97"/>
+      <c r="BO8" s="97"/>
+      <c r="BP8" s="97"/>
+      <c r="BQ8" s="97"/>
+      <c r="BR8" s="97"/>
+      <c r="BS8" s="97"/>
+      <c r="BT8" s="97"/>
+      <c r="BU8" s="97"/>
+      <c r="BV8" s="97"/>
+      <c r="BW8" s="97"/>
+      <c r="BX8" s="97"/>
+      <c r="BY8" s="97"/>
+      <c r="BZ8" s="97"/>
+      <c r="CA8" s="97"/>
+      <c r="CB8" s="97"/>
+      <c r="CC8" s="97"/>
+      <c r="CD8" s="97"/>
+      <c r="CE8" s="97"/>
+      <c r="CF8" s="97"/>
+      <c r="CG8" s="97"/>
+      <c r="CH8" s="97"/>
+      <c r="CI8" s="97"/>
+      <c r="CJ8" s="97"/>
+      <c r="CK8" s="97"/>
+      <c r="CL8" s="97"/>
+      <c r="CM8" s="97"/>
+      <c r="CN8" s="97"/>
+      <c r="CO8" s="97"/>
+      <c r="CP8" s="97"/>
+      <c r="CQ8" s="97"/>
+      <c r="CR8" s="97"/>
+      <c r="CS8" s="97"/>
+      <c r="CT8" s="97"/>
+      <c r="CU8" s="97"/>
+      <c r="CV8" s="97"/>
+      <c r="CW8" s="97"/>
+      <c r="CX8" s="97"/>
+      <c r="CY8" s="97"/>
+      <c r="CZ8" s="97"/>
+      <c r="DA8" s="97"/>
+      <c r="DB8" s="97"/>
+      <c r="DC8" s="97"/>
+      <c r="DD8" s="97"/>
+      <c r="DE8" s="97"/>
+      <c r="DF8" s="97"/>
+      <c r="DG8" s="97"/>
+      <c r="DH8" s="97"/>
+      <c r="DI8" s="97"/>
+      <c r="DJ8" s="97"/>
+      <c r="DK8" s="97"/>
+      <c r="DL8" s="97"/>
+      <c r="DM8" s="97"/>
+      <c r="DN8" s="97"/>
+      <c r="DO8" s="97"/>
+      <c r="DP8" s="97"/>
+      <c r="DQ8" s="97"/>
+      <c r="DR8" s="97"/>
+      <c r="DS8" s="97"/>
+      <c r="DT8" s="97"/>
+      <c r="DU8" s="97"/>
+      <c r="DV8" s="97"/>
+      <c r="DW8" s="97"/>
+      <c r="DX8" s="97"/>
+      <c r="DY8" s="97"/>
+      <c r="DZ8" s="97"/>
+      <c r="EA8" s="97"/>
+      <c r="EB8" s="97"/>
+      <c r="EC8" s="97"/>
+      <c r="ED8" s="97"/>
+      <c r="EE8" s="97"/>
+      <c r="EF8" s="97"/>
+      <c r="EG8" s="97"/>
+      <c r="EH8" s="96"/>
+      <c r="EI8" s="96"/>
+      <c r="EJ8" s="96"/>
+      <c r="EK8" s="96"/>
+      <c r="EL8" s="96"/>
+      <c r="EM8" s="96"/>
+      <c r="EN8" s="96"/>
+      <c r="EO8" s="96"/>
+      <c r="EP8" s="96"/>
+      <c r="EQ8" s="96"/>
+      <c r="ER8" s="96"/>
+      <c r="ES8" s="96"/>
+      <c r="ET8" s="96"/>
+      <c r="EU8" s="96"/>
+      <c r="EV8" s="96"/>
+      <c r="EW8" s="96"/>
+      <c r="EX8" s="96"/>
+      <c r="EY8" s="96"/>
+      <c r="EZ8" s="96"/>
+      <c r="FA8" s="96"/>
+      <c r="FB8" s="96"/>
+      <c r="FC8" s="96"/>
+      <c r="FD8" s="96"/>
+      <c r="FE8" s="96"/>
+      <c r="FF8" s="96"/>
+      <c r="FG8" s="96"/>
+      <c r="FH8" s="96"/>
+      <c r="FI8" s="96"/>
+      <c r="FJ8" s="96"/>
+      <c r="FK8" s="96"/>
+      <c r="FL8" s="96"/>
+      <c r="FM8" s="96"/>
+      <c r="FN8" s="96"/>
+      <c r="FO8" s="96"/>
+      <c r="FP8" s="96"/>
+      <c r="FQ8" s="96"/>
+      <c r="FR8" s="96"/>
+      <c r="FS8" s="96"/>
+      <c r="FT8" s="96"/>
+      <c r="FU8" s="96"/>
+      <c r="FV8" s="96"/>
+      <c r="FW8" s="96"/>
+      <c r="FX8" s="96"/>
+      <c r="FY8" s="96"/>
+      <c r="FZ8" s="96"/>
+      <c r="GA8" s="96"/>
+      <c r="GB8" s="96"/>
+      <c r="GC8" s="96"/>
+      <c r="GD8" s="96"/>
+      <c r="GE8" s="96"/>
+      <c r="GF8" s="96"/>
+      <c r="GG8" s="96"/>
+      <c r="GH8" s="96"/>
+      <c r="GI8" s="96"/>
+      <c r="GJ8" s="96"/>
+      <c r="GK8" s="96"/>
+      <c r="GL8" s="96"/>
+      <c r="GM8" s="96"/>
+      <c r="GN8" s="96"/>
+      <c r="GO8" s="96"/>
+      <c r="GP8" s="96"/>
+      <c r="GQ8" s="96"/>
+      <c r="GR8" s="96"/>
+      <c r="GS8" s="96"/>
+      <c r="GT8" s="96"/>
+      <c r="GU8" s="96"/>
+      <c r="GV8" s="96"/>
     </row>
     <row r="9" spans="1:204" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="167"/>
-      <c r="B9" s="145" t="s">
+      <c r="A9" s="166"/>
+      <c r="B9" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="145" t="s">
+      <c r="C9" s="133" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="145">
+      <c r="D9" s="133">
         <f>C8-D8</f>
         <v>0</v>
       </c>
-      <c r="E9" s="145">
+      <c r="E9" s="133">
         <f>C8-E8</f>
         <v>0</v>
       </c>
-      <c r="F9" s="146" t="s">
+      <c r="F9" s="134" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="146">
+      <c r="G9" s="134">
         <f>F8-G8</f>
         <v>0</v>
       </c>
-      <c r="H9" s="146">
+      <c r="H9" s="134">
         <f>F8-H8</f>
         <v>0</v>
       </c>
-      <c r="I9" s="146" t="s">
+      <c r="I9" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="146">
+      <c r="J9" s="134">
         <f>I8-J8</f>
         <v>0</v>
       </c>
-      <c r="K9" s="146">
+      <c r="K9" s="134">
         <f>I8-K8</f>
         <v>0</v>
       </c>
-      <c r="L9" s="145">
+      <c r="L9" s="133">
         <f>L8-M8</f>
         <v>0</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="82">
         <f>IFERROR(L8/M8, 0)</f>
         <v>1</v>
       </c>
-      <c r="N9" s="168">
+      <c r="N9" s="157">
         <f>N8-O8</f>
         <v>0</v>
       </c>
-      <c r="O9" s="169" t="str">
+      <c r="O9" s="158" t="str">
         <f>IF(TEXT(N8-O8,"+0,0; -0,0")="+0,0","0,0",TEXT(N8-O8,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
-      <c r="P9" s="91"/>
-      <c r="Q9" s="91"/>
-      <c r="R9" s="114"/>
-      <c r="S9" s="91"/>
-      <c r="T9" s="106"/>
-      <c r="U9" s="106"/>
-      <c r="V9" s="106"/>
-      <c r="W9" s="106"/>
-      <c r="X9" s="106"/>
-      <c r="Y9" s="106"/>
-      <c r="Z9" s="106"/>
-      <c r="AA9" s="106"/>
-      <c r="AB9" s="106"/>
-      <c r="AC9" s="106"/>
-      <c r="AD9" s="106"/>
-      <c r="AE9" s="106"/>
-      <c r="AF9" s="106"/>
-      <c r="AG9" s="106"/>
-      <c r="AH9" s="106"/>
-      <c r="AI9" s="105"/>
-      <c r="AJ9" s="105"/>
-      <c r="AK9" s="105"/>
-      <c r="AL9" s="105"/>
-      <c r="AM9" s="105"/>
-      <c r="AN9" s="105"/>
-      <c r="AO9" s="105"/>
-      <c r="AP9" s="105"/>
-      <c r="AQ9" s="105"/>
-      <c r="AR9" s="105"/>
-      <c r="AS9" s="105"/>
-      <c r="AT9" s="105"/>
-      <c r="AU9" s="105"/>
-      <c r="AV9" s="105"/>
-      <c r="AW9" s="105"/>
-      <c r="AX9" s="105"/>
-      <c r="AY9" s="105"/>
-      <c r="AZ9" s="105"/>
-      <c r="BA9" s="105"/>
-      <c r="BB9" s="105"/>
-      <c r="BC9" s="105"/>
-      <c r="BD9" s="105"/>
-      <c r="BE9" s="105"/>
-      <c r="BF9" s="105"/>
-      <c r="BG9" s="105"/>
-      <c r="BH9" s="105"/>
-      <c r="BI9" s="105"/>
-      <c r="BJ9" s="105"/>
-      <c r="BK9" s="105"/>
-      <c r="BL9" s="105"/>
-      <c r="BM9" s="105"/>
-      <c r="BN9" s="105"/>
-      <c r="BO9" s="105"/>
-      <c r="BP9" s="105"/>
-      <c r="BQ9" s="105"/>
-      <c r="BR9" s="105"/>
-      <c r="BS9" s="105"/>
-      <c r="BT9" s="105"/>
-      <c r="BU9" s="105"/>
-      <c r="BV9" s="105"/>
-      <c r="BW9" s="105"/>
-      <c r="BX9" s="105"/>
-      <c r="BY9" s="105"/>
-      <c r="BZ9" s="105"/>
-      <c r="CA9" s="105"/>
-      <c r="CB9" s="105"/>
-      <c r="CC9" s="105"/>
-      <c r="CD9" s="105"/>
-      <c r="CE9" s="105"/>
-      <c r="CF9" s="105"/>
-      <c r="CG9" s="105"/>
-      <c r="CH9" s="105"/>
-      <c r="CI9" s="105"/>
-      <c r="CJ9" s="105"/>
-      <c r="CK9" s="105"/>
-      <c r="CL9" s="105"/>
-      <c r="CM9" s="105"/>
-      <c r="CN9" s="105"/>
-      <c r="CO9" s="105"/>
-      <c r="CP9" s="105"/>
-      <c r="CQ9" s="105"/>
-      <c r="CR9" s="105"/>
-      <c r="CS9" s="105"/>
-      <c r="CT9" s="105"/>
-      <c r="CU9" s="105"/>
-      <c r="CV9" s="105"/>
-      <c r="CW9" s="105"/>
-      <c r="CX9" s="105"/>
-      <c r="CY9" s="105"/>
-      <c r="CZ9" s="105"/>
-      <c r="DA9" s="105"/>
-      <c r="DB9" s="105"/>
-      <c r="DC9" s="105"/>
-      <c r="DD9" s="105"/>
-      <c r="DE9" s="105"/>
-      <c r="DF9" s="105"/>
-      <c r="DG9" s="105"/>
-      <c r="DH9" s="105"/>
-      <c r="DI9" s="105"/>
-      <c r="DJ9" s="105"/>
-      <c r="DK9" s="105"/>
-      <c r="DL9" s="105"/>
-      <c r="DM9" s="105"/>
-      <c r="DN9" s="105"/>
-      <c r="DO9" s="105"/>
-      <c r="DP9" s="105"/>
-      <c r="DQ9" s="105"/>
-      <c r="DR9" s="105"/>
-      <c r="DS9" s="105"/>
-      <c r="DT9" s="105"/>
-      <c r="DU9" s="105"/>
-      <c r="DV9" s="105"/>
-      <c r="DW9" s="105"/>
-      <c r="DX9" s="105"/>
-      <c r="DY9" s="105"/>
-      <c r="DZ9" s="105"/>
-      <c r="EA9" s="105"/>
-      <c r="EB9" s="105"/>
-      <c r="EC9" s="105"/>
-      <c r="ED9" s="105"/>
-      <c r="EE9" s="105"/>
-      <c r="EF9" s="105"/>
-      <c r="EG9" s="105"/>
-      <c r="EH9" s="104"/>
-      <c r="EI9" s="104"/>
-      <c r="EJ9" s="104"/>
-      <c r="EK9" s="104"/>
-      <c r="EL9" s="104"/>
-      <c r="EM9" s="104"/>
-      <c r="EN9" s="104"/>
-      <c r="EO9" s="104"/>
-      <c r="EP9" s="104"/>
-      <c r="EQ9" s="104"/>
-      <c r="ER9" s="104"/>
-      <c r="ES9" s="104"/>
-      <c r="ET9" s="104"/>
-      <c r="EU9" s="104"/>
-      <c r="EV9" s="104"/>
-      <c r="EW9" s="104"/>
-      <c r="EX9" s="104"/>
-      <c r="EY9" s="104"/>
-      <c r="EZ9" s="104"/>
-      <c r="FA9" s="104"/>
-      <c r="FB9" s="104"/>
-      <c r="FC9" s="104"/>
-      <c r="FD9" s="104"/>
-      <c r="FE9" s="104"/>
-      <c r="FF9" s="104"/>
-      <c r="FG9" s="104"/>
-      <c r="FH9" s="104"/>
-      <c r="FI9" s="104"/>
-      <c r="FJ9" s="104"/>
-      <c r="FK9" s="104"/>
-      <c r="FL9" s="104"/>
-      <c r="FM9" s="104"/>
-      <c r="FN9" s="104"/>
-      <c r="FO9" s="104"/>
-      <c r="FP9" s="104"/>
-      <c r="FQ9" s="104"/>
-      <c r="FR9" s="104"/>
-      <c r="FS9" s="104"/>
-      <c r="FT9" s="104"/>
-      <c r="FU9" s="104"/>
-      <c r="FV9" s="104"/>
-      <c r="FW9" s="104"/>
-      <c r="FX9" s="104"/>
-      <c r="FY9" s="104"/>
-      <c r="FZ9" s="104"/>
-      <c r="GA9" s="104"/>
-      <c r="GB9" s="104"/>
-      <c r="GC9" s="104"/>
-      <c r="GD9" s="104"/>
-      <c r="GE9" s="104"/>
-      <c r="GF9" s="104"/>
-      <c r="GG9" s="104"/>
-      <c r="GH9" s="104"/>
-      <c r="GI9" s="104"/>
-      <c r="GJ9" s="104"/>
-      <c r="GK9" s="104"/>
-      <c r="GL9" s="104"/>
-      <c r="GM9" s="104"/>
-      <c r="GN9" s="104"/>
-      <c r="GO9" s="104"/>
-      <c r="GP9" s="104"/>
-      <c r="GQ9" s="104"/>
-      <c r="GR9" s="104"/>
-      <c r="GS9" s="104"/>
-      <c r="GT9" s="104"/>
-      <c r="GU9" s="104"/>
-      <c r="GV9" s="104"/>
-    </row>
-    <row r="10" spans="1:204" s="95" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="167" t="s">
+      <c r="P9" s="79"/>
+      <c r="Q9" s="79"/>
+      <c r="R9" s="102"/>
+      <c r="S9" s="79"/>
+      <c r="T9" s="94"/>
+      <c r="U9" s="94"/>
+      <c r="V9" s="94"/>
+      <c r="W9" s="94"/>
+      <c r="X9" s="94"/>
+      <c r="Y9" s="94"/>
+      <c r="Z9" s="94"/>
+      <c r="AA9" s="94"/>
+      <c r="AB9" s="94"/>
+      <c r="AC9" s="94"/>
+      <c r="AD9" s="94"/>
+      <c r="AE9" s="94"/>
+      <c r="AF9" s="94"/>
+      <c r="AG9" s="94"/>
+      <c r="AH9" s="94"/>
+      <c r="AI9" s="93"/>
+      <c r="AJ9" s="93"/>
+      <c r="AK9" s="93"/>
+      <c r="AL9" s="93"/>
+      <c r="AM9" s="93"/>
+      <c r="AN9" s="93"/>
+      <c r="AO9" s="93"/>
+      <c r="AP9" s="93"/>
+      <c r="AQ9" s="93"/>
+      <c r="AR9" s="93"/>
+      <c r="AS9" s="93"/>
+      <c r="AT9" s="93"/>
+      <c r="AU9" s="93"/>
+      <c r="AV9" s="93"/>
+      <c r="AW9" s="93"/>
+      <c r="AX9" s="93"/>
+      <c r="AY9" s="93"/>
+      <c r="AZ9" s="93"/>
+      <c r="BA9" s="93"/>
+      <c r="BB9" s="93"/>
+      <c r="BC9" s="93"/>
+      <c r="BD9" s="93"/>
+      <c r="BE9" s="93"/>
+      <c r="BF9" s="93"/>
+      <c r="BG9" s="93"/>
+      <c r="BH9" s="93"/>
+      <c r="BI9" s="93"/>
+      <c r="BJ9" s="93"/>
+      <c r="BK9" s="93"/>
+      <c r="BL9" s="93"/>
+      <c r="BM9" s="93"/>
+      <c r="BN9" s="93"/>
+      <c r="BO9" s="93"/>
+      <c r="BP9" s="93"/>
+      <c r="BQ9" s="93"/>
+      <c r="BR9" s="93"/>
+      <c r="BS9" s="93"/>
+      <c r="BT9" s="93"/>
+      <c r="BU9" s="93"/>
+      <c r="BV9" s="93"/>
+      <c r="BW9" s="93"/>
+      <c r="BX9" s="93"/>
+      <c r="BY9" s="93"/>
+      <c r="BZ9" s="93"/>
+      <c r="CA9" s="93"/>
+      <c r="CB9" s="93"/>
+      <c r="CC9" s="93"/>
+      <c r="CD9" s="93"/>
+      <c r="CE9" s="93"/>
+      <c r="CF9" s="93"/>
+      <c r="CG9" s="93"/>
+      <c r="CH9" s="93"/>
+      <c r="CI9" s="93"/>
+      <c r="CJ9" s="93"/>
+      <c r="CK9" s="93"/>
+      <c r="CL9" s="93"/>
+      <c r="CM9" s="93"/>
+      <c r="CN9" s="93"/>
+      <c r="CO9" s="93"/>
+      <c r="CP9" s="93"/>
+      <c r="CQ9" s="93"/>
+      <c r="CR9" s="93"/>
+      <c r="CS9" s="93"/>
+      <c r="CT9" s="93"/>
+      <c r="CU9" s="93"/>
+      <c r="CV9" s="93"/>
+      <c r="CW9" s="93"/>
+      <c r="CX9" s="93"/>
+      <c r="CY9" s="93"/>
+      <c r="CZ9" s="93"/>
+      <c r="DA9" s="93"/>
+      <c r="DB9" s="93"/>
+      <c r="DC9" s="93"/>
+      <c r="DD9" s="93"/>
+      <c r="DE9" s="93"/>
+      <c r="DF9" s="93"/>
+      <c r="DG9" s="93"/>
+      <c r="DH9" s="93"/>
+      <c r="DI9" s="93"/>
+      <c r="DJ9" s="93"/>
+      <c r="DK9" s="93"/>
+      <c r="DL9" s="93"/>
+      <c r="DM9" s="93"/>
+      <c r="DN9" s="93"/>
+      <c r="DO9" s="93"/>
+      <c r="DP9" s="93"/>
+      <c r="DQ9" s="93"/>
+      <c r="DR9" s="93"/>
+      <c r="DS9" s="93"/>
+      <c r="DT9" s="93"/>
+      <c r="DU9" s="93"/>
+      <c r="DV9" s="93"/>
+      <c r="DW9" s="93"/>
+      <c r="DX9" s="93"/>
+      <c r="DY9" s="93"/>
+      <c r="DZ9" s="93"/>
+      <c r="EA9" s="93"/>
+      <c r="EB9" s="93"/>
+      <c r="EC9" s="93"/>
+      <c r="ED9" s="93"/>
+      <c r="EE9" s="93"/>
+      <c r="EF9" s="93"/>
+      <c r="EG9" s="93"/>
+      <c r="EH9" s="92"/>
+      <c r="EI9" s="92"/>
+      <c r="EJ9" s="92"/>
+      <c r="EK9" s="92"/>
+      <c r="EL9" s="92"/>
+      <c r="EM9" s="92"/>
+      <c r="EN9" s="92"/>
+      <c r="EO9" s="92"/>
+      <c r="EP9" s="92"/>
+      <c r="EQ9" s="92"/>
+      <c r="ER9" s="92"/>
+      <c r="ES9" s="92"/>
+      <c r="ET9" s="92"/>
+      <c r="EU9" s="92"/>
+      <c r="EV9" s="92"/>
+      <c r="EW9" s="92"/>
+      <c r="EX9" s="92"/>
+      <c r="EY9" s="92"/>
+      <c r="EZ9" s="92"/>
+      <c r="FA9" s="92"/>
+      <c r="FB9" s="92"/>
+      <c r="FC9" s="92"/>
+      <c r="FD9" s="92"/>
+      <c r="FE9" s="92"/>
+      <c r="FF9" s="92"/>
+      <c r="FG9" s="92"/>
+      <c r="FH9" s="92"/>
+      <c r="FI9" s="92"/>
+      <c r="FJ9" s="92"/>
+      <c r="FK9" s="92"/>
+      <c r="FL9" s="92"/>
+      <c r="FM9" s="92"/>
+      <c r="FN9" s="92"/>
+      <c r="FO9" s="92"/>
+      <c r="FP9" s="92"/>
+      <c r="FQ9" s="92"/>
+      <c r="FR9" s="92"/>
+      <c r="FS9" s="92"/>
+      <c r="FT9" s="92"/>
+      <c r="FU9" s="92"/>
+      <c r="FV9" s="92"/>
+      <c r="FW9" s="92"/>
+      <c r="FX9" s="92"/>
+      <c r="FY9" s="92"/>
+      <c r="FZ9" s="92"/>
+      <c r="GA9" s="92"/>
+      <c r="GB9" s="92"/>
+      <c r="GC9" s="92"/>
+      <c r="GD9" s="92"/>
+      <c r="GE9" s="92"/>
+      <c r="GF9" s="92"/>
+      <c r="GG9" s="92"/>
+      <c r="GH9" s="92"/>
+      <c r="GI9" s="92"/>
+      <c r="GJ9" s="92"/>
+      <c r="GK9" s="92"/>
+      <c r="GL9" s="92"/>
+      <c r="GM9" s="92"/>
+      <c r="GN9" s="92"/>
+      <c r="GO9" s="92"/>
+      <c r="GP9" s="92"/>
+      <c r="GQ9" s="92"/>
+      <c r="GR9" s="92"/>
+      <c r="GS9" s="92"/>
+      <c r="GT9" s="92"/>
+      <c r="GU9" s="92"/>
+      <c r="GV9" s="92"/>
+    </row>
+    <row r="10" spans="1:204" s="83" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="166" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="101">
+      <c r="B10" s="89">
         <v>1</v>
       </c>
-      <c r="C10" s="101">
+      <c r="C10" s="89">
         <v>1</v>
       </c>
-      <c r="D10" s="143">
+      <c r="D10" s="131">
         <v>1</v>
       </c>
-      <c r="E10" s="144">
+      <c r="E10" s="132">
         <v>1</v>
       </c>
-      <c r="F10" s="72">
+      <c r="F10" s="67">
         <v>1</v>
       </c>
-      <c r="G10" s="103">
+      <c r="G10" s="91">
         <v>1</v>
       </c>
-      <c r="H10" s="102">
+      <c r="H10" s="90">
         <v>1</v>
       </c>
-      <c r="I10" s="72">
+      <c r="I10" s="67">
         <v>1</v>
       </c>
-      <c r="J10" s="103">
+      <c r="J10" s="91">
         <v>1</v>
       </c>
-      <c r="K10" s="102">
+      <c r="K10" s="90">
         <v>1</v>
       </c>
-      <c r="L10" s="101">
+      <c r="L10" s="89">
         <v>1</v>
       </c>
-      <c r="M10" s="139">
+      <c r="M10" s="127">
         <v>1</v>
       </c>
-      <c r="N10" s="72"/>
-      <c r="O10" s="71"/>
-      <c r="P10" s="112"/>
-      <c r="Q10" s="112"/>
-      <c r="R10" s="111"/>
-      <c r="S10" s="99"/>
-      <c r="T10" s="110"/>
-      <c r="U10" s="110"/>
-      <c r="V10" s="110"/>
-      <c r="W10" s="110"/>
-      <c r="X10" s="110"/>
-      <c r="Y10" s="110"/>
-      <c r="Z10" s="110"/>
-      <c r="AA10" s="110"/>
-      <c r="AB10" s="110"/>
-      <c r="AC10" s="110"/>
-      <c r="AD10" s="110"/>
-      <c r="AE10" s="110"/>
-      <c r="AF10" s="110"/>
-      <c r="AG10" s="110"/>
-      <c r="AH10" s="110"/>
-      <c r="AI10" s="110"/>
-      <c r="AJ10" s="110"/>
-      <c r="AK10" s="110"/>
-      <c r="AL10" s="110"/>
-      <c r="AM10" s="110"/>
-      <c r="AN10" s="110"/>
-      <c r="AO10" s="110"/>
-      <c r="AP10" s="110"/>
-      <c r="AQ10" s="110"/>
-      <c r="AR10" s="110"/>
-      <c r="AS10" s="110"/>
-      <c r="AT10" s="108"/>
-      <c r="AU10" s="108"/>
-      <c r="AV10" s="108"/>
-      <c r="AW10" s="108"/>
-      <c r="AX10" s="108"/>
-      <c r="AY10" s="108"/>
-      <c r="AZ10" s="108"/>
-      <c r="BA10" s="108"/>
-      <c r="BB10" s="108"/>
-      <c r="BC10" s="108"/>
-      <c r="BD10" s="108"/>
-      <c r="BE10" s="108"/>
-      <c r="BF10" s="109"/>
-      <c r="BG10" s="109"/>
-      <c r="BH10" s="109"/>
-      <c r="BI10" s="109"/>
-      <c r="BJ10" s="109"/>
-      <c r="BK10" s="109"/>
-      <c r="BL10" s="109"/>
-      <c r="BM10" s="109"/>
-      <c r="BN10" s="109"/>
-      <c r="BO10" s="109"/>
-      <c r="BP10" s="109"/>
-      <c r="BQ10" s="109"/>
-      <c r="BR10" s="109"/>
-      <c r="BS10" s="109"/>
-      <c r="BT10" s="109"/>
-      <c r="BU10" s="109"/>
-      <c r="BV10" s="109"/>
-      <c r="BW10" s="109"/>
-      <c r="BX10" s="109"/>
-      <c r="BY10" s="109"/>
-      <c r="BZ10" s="109"/>
-      <c r="CA10" s="109"/>
-      <c r="CB10" s="109"/>
-      <c r="CC10" s="109"/>
-      <c r="CD10" s="109"/>
-      <c r="CE10" s="109"/>
-      <c r="CF10" s="109"/>
-      <c r="CG10" s="109"/>
-      <c r="CH10" s="109"/>
-      <c r="CI10" s="109"/>
-      <c r="CJ10" s="109"/>
-      <c r="CK10" s="109"/>
-      <c r="CL10" s="109"/>
-      <c r="CM10" s="109"/>
-      <c r="CN10" s="109"/>
-      <c r="CO10" s="109"/>
-      <c r="CP10" s="109"/>
-      <c r="CQ10" s="109"/>
-      <c r="CR10" s="109"/>
-      <c r="CS10" s="109"/>
-      <c r="CT10" s="109"/>
-      <c r="CU10" s="109"/>
-      <c r="CV10" s="109"/>
-      <c r="CW10" s="109"/>
-      <c r="CX10" s="109"/>
-      <c r="CY10" s="109"/>
-      <c r="CZ10" s="109"/>
-      <c r="DA10" s="109"/>
-      <c r="DB10" s="109"/>
-      <c r="DC10" s="109"/>
-      <c r="DD10" s="109"/>
-      <c r="DE10" s="109"/>
-      <c r="DF10" s="109"/>
-      <c r="DG10" s="109"/>
-      <c r="DH10" s="109"/>
-      <c r="DI10" s="109"/>
-      <c r="DJ10" s="109"/>
-      <c r="DK10" s="109"/>
-      <c r="DL10" s="109"/>
-      <c r="DM10" s="109"/>
-      <c r="DN10" s="109"/>
-      <c r="DO10" s="109"/>
-      <c r="DP10" s="109"/>
-      <c r="DQ10" s="109"/>
-      <c r="DR10" s="109"/>
-      <c r="DS10" s="109"/>
-      <c r="DT10" s="109"/>
-      <c r="DU10" s="109"/>
-      <c r="DV10" s="109"/>
-      <c r="DW10" s="109"/>
-      <c r="DX10" s="109"/>
-      <c r="DY10" s="109"/>
-      <c r="DZ10" s="109"/>
-      <c r="EA10" s="109"/>
-      <c r="EB10" s="109"/>
-      <c r="EC10" s="109"/>
-      <c r="ED10" s="109"/>
-      <c r="EE10" s="109"/>
-      <c r="EF10" s="109"/>
-      <c r="EG10" s="109"/>
-      <c r="EH10" s="108"/>
-      <c r="EI10" s="108"/>
-      <c r="EJ10" s="108"/>
-      <c r="EK10" s="108"/>
-      <c r="EL10" s="108"/>
-      <c r="EM10" s="108"/>
-      <c r="EN10" s="108"/>
-      <c r="EO10" s="108"/>
-      <c r="EP10" s="108"/>
-      <c r="EQ10" s="108"/>
-      <c r="ER10" s="108"/>
-      <c r="ES10" s="108"/>
-      <c r="ET10" s="108"/>
-      <c r="EU10" s="108"/>
-      <c r="EV10" s="108"/>
-      <c r="EW10" s="108"/>
-      <c r="EX10" s="108"/>
-      <c r="EY10" s="108"/>
-      <c r="EZ10" s="108"/>
-      <c r="FA10" s="108"/>
-      <c r="FB10" s="108"/>
-      <c r="FC10" s="108"/>
-      <c r="FD10" s="108"/>
-      <c r="FE10" s="108"/>
-      <c r="FF10" s="108"/>
-      <c r="FG10" s="108"/>
-      <c r="FH10" s="108"/>
-      <c r="FI10" s="108"/>
-      <c r="FJ10" s="108"/>
-      <c r="FK10" s="108"/>
-      <c r="FL10" s="108"/>
-      <c r="FM10" s="108"/>
-      <c r="FN10" s="108"/>
-      <c r="FO10" s="108"/>
-      <c r="FP10" s="108"/>
-      <c r="FQ10" s="108"/>
-      <c r="FR10" s="108"/>
-      <c r="FS10" s="108"/>
-      <c r="FT10" s="108"/>
-      <c r="FU10" s="108"/>
-      <c r="FV10" s="108"/>
-      <c r="FW10" s="108"/>
-      <c r="FX10" s="108"/>
-      <c r="FY10" s="108"/>
-      <c r="FZ10" s="108"/>
-      <c r="GA10" s="108"/>
-      <c r="GB10" s="108"/>
-      <c r="GC10" s="108"/>
-      <c r="GD10" s="108"/>
-      <c r="GE10" s="108"/>
-      <c r="GF10" s="108"/>
-      <c r="GG10" s="108"/>
-      <c r="GH10" s="108"/>
-      <c r="GI10" s="108"/>
-      <c r="GJ10" s="108"/>
-      <c r="GK10" s="108"/>
-      <c r="GL10" s="108"/>
-      <c r="GM10" s="108"/>
-      <c r="GN10" s="108"/>
-      <c r="GO10" s="108"/>
-      <c r="GP10" s="108"/>
-      <c r="GQ10" s="108"/>
-      <c r="GR10" s="108"/>
-      <c r="GS10" s="108"/>
-      <c r="GT10" s="108"/>
-      <c r="GU10" s="108"/>
-      <c r="GV10" s="108"/>
+      <c r="N10" s="67"/>
+      <c r="O10" s="66"/>
+      <c r="P10" s="100"/>
+      <c r="Q10" s="100"/>
+      <c r="R10" s="99"/>
+      <c r="S10" s="87"/>
+      <c r="T10" s="98"/>
+      <c r="U10" s="98"/>
+      <c r="V10" s="98"/>
+      <c r="W10" s="98"/>
+      <c r="X10" s="98"/>
+      <c r="Y10" s="98"/>
+      <c r="Z10" s="98"/>
+      <c r="AA10" s="98"/>
+      <c r="AB10" s="98"/>
+      <c r="AC10" s="98"/>
+      <c r="AD10" s="98"/>
+      <c r="AE10" s="98"/>
+      <c r="AF10" s="98"/>
+      <c r="AG10" s="98"/>
+      <c r="AH10" s="98"/>
+      <c r="AI10" s="98"/>
+      <c r="AJ10" s="98"/>
+      <c r="AK10" s="98"/>
+      <c r="AL10" s="98"/>
+      <c r="AM10" s="98"/>
+      <c r="AN10" s="98"/>
+      <c r="AO10" s="98"/>
+      <c r="AP10" s="98"/>
+      <c r="AQ10" s="98"/>
+      <c r="AR10" s="98"/>
+      <c r="AS10" s="98"/>
+      <c r="AT10" s="96"/>
+      <c r="AU10" s="96"/>
+      <c r="AV10" s="96"/>
+      <c r="AW10" s="96"/>
+      <c r="AX10" s="96"/>
+      <c r="AY10" s="96"/>
+      <c r="AZ10" s="96"/>
+      <c r="BA10" s="96"/>
+      <c r="BB10" s="96"/>
+      <c r="BC10" s="96"/>
+      <c r="BD10" s="96"/>
+      <c r="BE10" s="96"/>
+      <c r="BF10" s="97"/>
+      <c r="BG10" s="97"/>
+      <c r="BH10" s="97"/>
+      <c r="BI10" s="97"/>
+      <c r="BJ10" s="97"/>
+      <c r="BK10" s="97"/>
+      <c r="BL10" s="97"/>
+      <c r="BM10" s="97"/>
+      <c r="BN10" s="97"/>
+      <c r="BO10" s="97"/>
+      <c r="BP10" s="97"/>
+      <c r="BQ10" s="97"/>
+      <c r="BR10" s="97"/>
+      <c r="BS10" s="97"/>
+      <c r="BT10" s="97"/>
+      <c r="BU10" s="97"/>
+      <c r="BV10" s="97"/>
+      <c r="BW10" s="97"/>
+      <c r="BX10" s="97"/>
+      <c r="BY10" s="97"/>
+      <c r="BZ10" s="97"/>
+      <c r="CA10" s="97"/>
+      <c r="CB10" s="97"/>
+      <c r="CC10" s="97"/>
+      <c r="CD10" s="97"/>
+      <c r="CE10" s="97"/>
+      <c r="CF10" s="97"/>
+      <c r="CG10" s="97"/>
+      <c r="CH10" s="97"/>
+      <c r="CI10" s="97"/>
+      <c r="CJ10" s="97"/>
+      <c r="CK10" s="97"/>
+      <c r="CL10" s="97"/>
+      <c r="CM10" s="97"/>
+      <c r="CN10" s="97"/>
+      <c r="CO10" s="97"/>
+      <c r="CP10" s="97"/>
+      <c r="CQ10" s="97"/>
+      <c r="CR10" s="97"/>
+      <c r="CS10" s="97"/>
+      <c r="CT10" s="97"/>
+      <c r="CU10" s="97"/>
+      <c r="CV10" s="97"/>
+      <c r="CW10" s="97"/>
+      <c r="CX10" s="97"/>
+      <c r="CY10" s="97"/>
+      <c r="CZ10" s="97"/>
+      <c r="DA10" s="97"/>
+      <c r="DB10" s="97"/>
+      <c r="DC10" s="97"/>
+      <c r="DD10" s="97"/>
+      <c r="DE10" s="97"/>
+      <c r="DF10" s="97"/>
+      <c r="DG10" s="97"/>
+      <c r="DH10" s="97"/>
+      <c r="DI10" s="97"/>
+      <c r="DJ10" s="97"/>
+      <c r="DK10" s="97"/>
+      <c r="DL10" s="97"/>
+      <c r="DM10" s="97"/>
+      <c r="DN10" s="97"/>
+      <c r="DO10" s="97"/>
+      <c r="DP10" s="97"/>
+      <c r="DQ10" s="97"/>
+      <c r="DR10" s="97"/>
+      <c r="DS10" s="97"/>
+      <c r="DT10" s="97"/>
+      <c r="DU10" s="97"/>
+      <c r="DV10" s="97"/>
+      <c r="DW10" s="97"/>
+      <c r="DX10" s="97"/>
+      <c r="DY10" s="97"/>
+      <c r="DZ10" s="97"/>
+      <c r="EA10" s="97"/>
+      <c r="EB10" s="97"/>
+      <c r="EC10" s="97"/>
+      <c r="ED10" s="97"/>
+      <c r="EE10" s="97"/>
+      <c r="EF10" s="97"/>
+      <c r="EG10" s="97"/>
+      <c r="EH10" s="96"/>
+      <c r="EI10" s="96"/>
+      <c r="EJ10" s="96"/>
+      <c r="EK10" s="96"/>
+      <c r="EL10" s="96"/>
+      <c r="EM10" s="96"/>
+      <c r="EN10" s="96"/>
+      <c r="EO10" s="96"/>
+      <c r="EP10" s="96"/>
+      <c r="EQ10" s="96"/>
+      <c r="ER10" s="96"/>
+      <c r="ES10" s="96"/>
+      <c r="ET10" s="96"/>
+      <c r="EU10" s="96"/>
+      <c r="EV10" s="96"/>
+      <c r="EW10" s="96"/>
+      <c r="EX10" s="96"/>
+      <c r="EY10" s="96"/>
+      <c r="EZ10" s="96"/>
+      <c r="FA10" s="96"/>
+      <c r="FB10" s="96"/>
+      <c r="FC10" s="96"/>
+      <c r="FD10" s="96"/>
+      <c r="FE10" s="96"/>
+      <c r="FF10" s="96"/>
+      <c r="FG10" s="96"/>
+      <c r="FH10" s="96"/>
+      <c r="FI10" s="96"/>
+      <c r="FJ10" s="96"/>
+      <c r="FK10" s="96"/>
+      <c r="FL10" s="96"/>
+      <c r="FM10" s="96"/>
+      <c r="FN10" s="96"/>
+      <c r="FO10" s="96"/>
+      <c r="FP10" s="96"/>
+      <c r="FQ10" s="96"/>
+      <c r="FR10" s="96"/>
+      <c r="FS10" s="96"/>
+      <c r="FT10" s="96"/>
+      <c r="FU10" s="96"/>
+      <c r="FV10" s="96"/>
+      <c r="FW10" s="96"/>
+      <c r="FX10" s="96"/>
+      <c r="FY10" s="96"/>
+      <c r="FZ10" s="96"/>
+      <c r="GA10" s="96"/>
+      <c r="GB10" s="96"/>
+      <c r="GC10" s="96"/>
+      <c r="GD10" s="96"/>
+      <c r="GE10" s="96"/>
+      <c r="GF10" s="96"/>
+      <c r="GG10" s="96"/>
+      <c r="GH10" s="96"/>
+      <c r="GI10" s="96"/>
+      <c r="GJ10" s="96"/>
+      <c r="GK10" s="96"/>
+      <c r="GL10" s="96"/>
+      <c r="GM10" s="96"/>
+      <c r="GN10" s="96"/>
+      <c r="GO10" s="96"/>
+      <c r="GP10" s="96"/>
+      <c r="GQ10" s="96"/>
+      <c r="GR10" s="96"/>
+      <c r="GS10" s="96"/>
+      <c r="GT10" s="96"/>
+      <c r="GU10" s="96"/>
+      <c r="GV10" s="96"/>
     </row>
     <row r="11" spans="1:204" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="167"/>
-      <c r="B11" s="145" t="s">
+      <c r="A11" s="166"/>
+      <c r="B11" s="133" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="145" t="s">
+      <c r="C11" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="145">
+      <c r="D11" s="133">
         <f>C10-D10</f>
         <v>0</v>
       </c>
-      <c r="E11" s="145">
+      <c r="E11" s="133">
         <f>C10-E10</f>
         <v>0</v>
       </c>
-      <c r="F11" s="146" t="s">
+      <c r="F11" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="146">
+      <c r="G11" s="134">
         <f>F10-G10</f>
         <v>0</v>
       </c>
-      <c r="H11" s="146">
+      <c r="H11" s="134">
         <f>F10-H10</f>
         <v>0</v>
       </c>
-      <c r="I11" s="146" t="s">
+      <c r="I11" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="146">
+      <c r="J11" s="134">
         <f>I10-J10</f>
         <v>0</v>
       </c>
-      <c r="K11" s="146">
+      <c r="K11" s="134">
         <f>I10-K10</f>
         <v>0</v>
       </c>
-      <c r="L11" s="145">
+      <c r="L11" s="133">
         <f>L10-M10</f>
         <v>0</v>
       </c>
-      <c r="M11" s="94">
+      <c r="M11" s="82">
         <f>IFERROR(L10/M10, 0)</f>
         <v>1</v>
       </c>
-      <c r="N11" s="170"/>
-      <c r="O11" s="171"/>
-      <c r="P11" s="91"/>
-      <c r="Q11" s="91"/>
-      <c r="R11" s="111"/>
-      <c r="S11" s="91"/>
-      <c r="T11" s="106"/>
-      <c r="U11" s="106"/>
-      <c r="V11" s="106"/>
-      <c r="W11" s="106"/>
-      <c r="X11" s="106"/>
-      <c r="Y11" s="106"/>
-      <c r="Z11" s="106"/>
-      <c r="AA11" s="106"/>
-      <c r="AB11" s="106"/>
-      <c r="AC11" s="106"/>
-      <c r="AD11" s="106"/>
-      <c r="AE11" s="106"/>
-      <c r="AF11" s="106"/>
-      <c r="AG11" s="106"/>
-      <c r="AH11" s="106"/>
-      <c r="AI11" s="105"/>
-      <c r="AJ11" s="105"/>
-      <c r="AK11" s="105"/>
-      <c r="AL11" s="105"/>
-      <c r="AM11" s="105"/>
-      <c r="AN11" s="105"/>
-      <c r="AO11" s="105"/>
-      <c r="AP11" s="105"/>
-      <c r="AQ11" s="105"/>
-      <c r="AR11" s="105"/>
-      <c r="AS11" s="105"/>
-      <c r="AT11" s="105"/>
-      <c r="AU11" s="105"/>
-      <c r="AV11" s="105"/>
-      <c r="AW11" s="105"/>
-      <c r="AX11" s="105"/>
-      <c r="AY11" s="105"/>
-      <c r="AZ11" s="105"/>
-      <c r="BA11" s="105"/>
-      <c r="BB11" s="105"/>
-      <c r="BC11" s="105"/>
-      <c r="BD11" s="105"/>
-      <c r="BE11" s="105"/>
-      <c r="BF11" s="105"/>
-      <c r="BG11" s="105"/>
-      <c r="BH11" s="105"/>
-      <c r="BI11" s="105"/>
-      <c r="BJ11" s="105"/>
-      <c r="BK11" s="105"/>
-      <c r="BL11" s="105"/>
-      <c r="BM11" s="105"/>
-      <c r="BN11" s="105"/>
-      <c r="BO11" s="105"/>
-      <c r="BP11" s="105"/>
-      <c r="BQ11" s="105"/>
-      <c r="BR11" s="105"/>
-      <c r="BS11" s="105"/>
-      <c r="BT11" s="105"/>
-      <c r="BU11" s="105"/>
-      <c r="BV11" s="105"/>
-      <c r="BW11" s="105"/>
-      <c r="BX11" s="105"/>
-      <c r="BY11" s="105"/>
-      <c r="BZ11" s="105"/>
-      <c r="CA11" s="105"/>
-      <c r="CB11" s="105"/>
-      <c r="CC11" s="105"/>
-      <c r="CD11" s="105"/>
-      <c r="CE11" s="105"/>
-      <c r="CF11" s="105"/>
-      <c r="CG11" s="105"/>
-      <c r="CH11" s="105"/>
-      <c r="CI11" s="105"/>
-      <c r="CJ11" s="105"/>
-      <c r="CK11" s="105"/>
-      <c r="CL11" s="105"/>
-      <c r="CM11" s="105"/>
-      <c r="CN11" s="105"/>
-      <c r="CO11" s="105"/>
-      <c r="CP11" s="105"/>
-      <c r="CQ11" s="105"/>
-      <c r="CR11" s="105"/>
-      <c r="CS11" s="105"/>
-      <c r="CT11" s="105"/>
-      <c r="CU11" s="105"/>
-      <c r="CV11" s="105"/>
-      <c r="CW11" s="105"/>
-      <c r="CX11" s="105"/>
-      <c r="CY11" s="105"/>
-      <c r="CZ11" s="105"/>
-      <c r="DA11" s="105"/>
-      <c r="DB11" s="105"/>
-      <c r="DC11" s="105"/>
-      <c r="DD11" s="105"/>
-      <c r="DE11" s="105"/>
-      <c r="DF11" s="105"/>
-      <c r="DG11" s="105"/>
-      <c r="DH11" s="105"/>
-      <c r="DI11" s="105"/>
-      <c r="DJ11" s="105"/>
-      <c r="DK11" s="105"/>
-      <c r="DL11" s="105"/>
-      <c r="DM11" s="105"/>
-      <c r="DN11" s="105"/>
-      <c r="DO11" s="105"/>
-      <c r="DP11" s="105"/>
-      <c r="DQ11" s="105"/>
-      <c r="DR11" s="105"/>
-      <c r="DS11" s="105"/>
-      <c r="DT11" s="105"/>
-      <c r="DU11" s="105"/>
-      <c r="DV11" s="105"/>
-      <c r="DW11" s="105"/>
-      <c r="DX11" s="105"/>
-      <c r="DY11" s="105"/>
-      <c r="DZ11" s="105"/>
-      <c r="EA11" s="105"/>
-      <c r="EB11" s="105"/>
-      <c r="EC11" s="105"/>
-      <c r="ED11" s="105"/>
-      <c r="EE11" s="105"/>
-      <c r="EF11" s="105"/>
-      <c r="EG11" s="105"/>
-      <c r="EH11" s="104"/>
-      <c r="EI11" s="104"/>
-      <c r="EJ11" s="104"/>
-      <c r="EK11" s="104"/>
-      <c r="EL11" s="104"/>
-      <c r="EM11" s="104"/>
-      <c r="EN11" s="104"/>
-      <c r="EO11" s="104"/>
-      <c r="EP11" s="104"/>
-      <c r="EQ11" s="104"/>
-      <c r="ER11" s="104"/>
-      <c r="ES11" s="104"/>
-      <c r="ET11" s="104"/>
-      <c r="EU11" s="104"/>
-      <c r="EV11" s="104"/>
-      <c r="EW11" s="104"/>
-      <c r="EX11" s="104"/>
-      <c r="EY11" s="104"/>
-      <c r="EZ11" s="104"/>
-      <c r="FA11" s="104"/>
-      <c r="FB11" s="104"/>
-      <c r="FC11" s="104"/>
-      <c r="FD11" s="104"/>
-      <c r="FE11" s="104"/>
-      <c r="FF11" s="104"/>
-      <c r="FG11" s="104"/>
-      <c r="FH11" s="104"/>
-      <c r="FI11" s="104"/>
-      <c r="FJ11" s="104"/>
-      <c r="FK11" s="104"/>
-      <c r="FL11" s="104"/>
-      <c r="FM11" s="104"/>
-      <c r="FN11" s="104"/>
-      <c r="FO11" s="104"/>
-      <c r="FP11" s="104"/>
-      <c r="FQ11" s="104"/>
-      <c r="FR11" s="104"/>
-      <c r="FS11" s="104"/>
-      <c r="FT11" s="104"/>
-      <c r="FU11" s="104"/>
-      <c r="FV11" s="104"/>
-      <c r="FW11" s="104"/>
-      <c r="FX11" s="104"/>
-      <c r="FY11" s="104"/>
-      <c r="FZ11" s="104"/>
-      <c r="GA11" s="104"/>
-      <c r="GB11" s="104"/>
-      <c r="GC11" s="104"/>
-      <c r="GD11" s="104"/>
-      <c r="GE11" s="104"/>
-      <c r="GF11" s="104"/>
-      <c r="GG11" s="104"/>
-      <c r="GH11" s="104"/>
-      <c r="GI11" s="104"/>
-      <c r="GJ11" s="104"/>
-      <c r="GK11" s="104"/>
-      <c r="GL11" s="104"/>
-      <c r="GM11" s="104"/>
-      <c r="GN11" s="104"/>
-      <c r="GO11" s="104"/>
-      <c r="GP11" s="104"/>
-      <c r="GQ11" s="104"/>
-      <c r="GR11" s="104"/>
-      <c r="GS11" s="104"/>
-      <c r="GT11" s="104"/>
-      <c r="GU11" s="104"/>
-      <c r="GV11" s="104"/>
-    </row>
-    <row r="12" spans="1:204" s="95" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="167" t="s">
+      <c r="N11" s="168"/>
+      <c r="O11" s="169"/>
+      <c r="P11" s="79"/>
+      <c r="Q11" s="79"/>
+      <c r="R11" s="99"/>
+      <c r="S11" s="79"/>
+      <c r="T11" s="94"/>
+      <c r="U11" s="94"/>
+      <c r="V11" s="94"/>
+      <c r="W11" s="94"/>
+      <c r="X11" s="94"/>
+      <c r="Y11" s="94"/>
+      <c r="Z11" s="94"/>
+      <c r="AA11" s="94"/>
+      <c r="AB11" s="94"/>
+      <c r="AC11" s="94"/>
+      <c r="AD11" s="94"/>
+      <c r="AE11" s="94"/>
+      <c r="AF11" s="94"/>
+      <c r="AG11" s="94"/>
+      <c r="AH11" s="94"/>
+      <c r="AI11" s="93"/>
+      <c r="AJ11" s="93"/>
+      <c r="AK11" s="93"/>
+      <c r="AL11" s="93"/>
+      <c r="AM11" s="93"/>
+      <c r="AN11" s="93"/>
+      <c r="AO11" s="93"/>
+      <c r="AP11" s="93"/>
+      <c r="AQ11" s="93"/>
+      <c r="AR11" s="93"/>
+      <c r="AS11" s="93"/>
+      <c r="AT11" s="93"/>
+      <c r="AU11" s="93"/>
+      <c r="AV11" s="93"/>
+      <c r="AW11" s="93"/>
+      <c r="AX11" s="93"/>
+      <c r="AY11" s="93"/>
+      <c r="AZ11" s="93"/>
+      <c r="BA11" s="93"/>
+      <c r="BB11" s="93"/>
+      <c r="BC11" s="93"/>
+      <c r="BD11" s="93"/>
+      <c r="BE11" s="93"/>
+      <c r="BF11" s="93"/>
+      <c r="BG11" s="93"/>
+      <c r="BH11" s="93"/>
+      <c r="BI11" s="93"/>
+      <c r="BJ11" s="93"/>
+      <c r="BK11" s="93"/>
+      <c r="BL11" s="93"/>
+      <c r="BM11" s="93"/>
+      <c r="BN11" s="93"/>
+      <c r="BO11" s="93"/>
+      <c r="BP11" s="93"/>
+      <c r="BQ11" s="93"/>
+      <c r="BR11" s="93"/>
+      <c r="BS11" s="93"/>
+      <c r="BT11" s="93"/>
+      <c r="BU11" s="93"/>
+      <c r="BV11" s="93"/>
+      <c r="BW11" s="93"/>
+      <c r="BX11" s="93"/>
+      <c r="BY11" s="93"/>
+      <c r="BZ11" s="93"/>
+      <c r="CA11" s="93"/>
+      <c r="CB11" s="93"/>
+      <c r="CC11" s="93"/>
+      <c r="CD11" s="93"/>
+      <c r="CE11" s="93"/>
+      <c r="CF11" s="93"/>
+      <c r="CG11" s="93"/>
+      <c r="CH11" s="93"/>
+      <c r="CI11" s="93"/>
+      <c r="CJ11" s="93"/>
+      <c r="CK11" s="93"/>
+      <c r="CL11" s="93"/>
+      <c r="CM11" s="93"/>
+      <c r="CN11" s="93"/>
+      <c r="CO11" s="93"/>
+      <c r="CP11" s="93"/>
+      <c r="CQ11" s="93"/>
+      <c r="CR11" s="93"/>
+      <c r="CS11" s="93"/>
+      <c r="CT11" s="93"/>
+      <c r="CU11" s="93"/>
+      <c r="CV11" s="93"/>
+      <c r="CW11" s="93"/>
+      <c r="CX11" s="93"/>
+      <c r="CY11" s="93"/>
+      <c r="CZ11" s="93"/>
+      <c r="DA11" s="93"/>
+      <c r="DB11" s="93"/>
+      <c r="DC11" s="93"/>
+      <c r="DD11" s="93"/>
+      <c r="DE11" s="93"/>
+      <c r="DF11" s="93"/>
+      <c r="DG11" s="93"/>
+      <c r="DH11" s="93"/>
+      <c r="DI11" s="93"/>
+      <c r="DJ11" s="93"/>
+      <c r="DK11" s="93"/>
+      <c r="DL11" s="93"/>
+      <c r="DM11" s="93"/>
+      <c r="DN11" s="93"/>
+      <c r="DO11" s="93"/>
+      <c r="DP11" s="93"/>
+      <c r="DQ11" s="93"/>
+      <c r="DR11" s="93"/>
+      <c r="DS11" s="93"/>
+      <c r="DT11" s="93"/>
+      <c r="DU11" s="93"/>
+      <c r="DV11" s="93"/>
+      <c r="DW11" s="93"/>
+      <c r="DX11" s="93"/>
+      <c r="DY11" s="93"/>
+      <c r="DZ11" s="93"/>
+      <c r="EA11" s="93"/>
+      <c r="EB11" s="93"/>
+      <c r="EC11" s="93"/>
+      <c r="ED11" s="93"/>
+      <c r="EE11" s="93"/>
+      <c r="EF11" s="93"/>
+      <c r="EG11" s="93"/>
+      <c r="EH11" s="92"/>
+      <c r="EI11" s="92"/>
+      <c r="EJ11" s="92"/>
+      <c r="EK11" s="92"/>
+      <c r="EL11" s="92"/>
+      <c r="EM11" s="92"/>
+      <c r="EN11" s="92"/>
+      <c r="EO11" s="92"/>
+      <c r="EP11" s="92"/>
+      <c r="EQ11" s="92"/>
+      <c r="ER11" s="92"/>
+      <c r="ES11" s="92"/>
+      <c r="ET11" s="92"/>
+      <c r="EU11" s="92"/>
+      <c r="EV11" s="92"/>
+      <c r="EW11" s="92"/>
+      <c r="EX11" s="92"/>
+      <c r="EY11" s="92"/>
+      <c r="EZ11" s="92"/>
+      <c r="FA11" s="92"/>
+      <c r="FB11" s="92"/>
+      <c r="FC11" s="92"/>
+      <c r="FD11" s="92"/>
+      <c r="FE11" s="92"/>
+      <c r="FF11" s="92"/>
+      <c r="FG11" s="92"/>
+      <c r="FH11" s="92"/>
+      <c r="FI11" s="92"/>
+      <c r="FJ11" s="92"/>
+      <c r="FK11" s="92"/>
+      <c r="FL11" s="92"/>
+      <c r="FM11" s="92"/>
+      <c r="FN11" s="92"/>
+      <c r="FO11" s="92"/>
+      <c r="FP11" s="92"/>
+      <c r="FQ11" s="92"/>
+      <c r="FR11" s="92"/>
+      <c r="FS11" s="92"/>
+      <c r="FT11" s="92"/>
+      <c r="FU11" s="92"/>
+      <c r="FV11" s="92"/>
+      <c r="FW11" s="92"/>
+      <c r="FX11" s="92"/>
+      <c r="FY11" s="92"/>
+      <c r="FZ11" s="92"/>
+      <c r="GA11" s="92"/>
+      <c r="GB11" s="92"/>
+      <c r="GC11" s="92"/>
+      <c r="GD11" s="92"/>
+      <c r="GE11" s="92"/>
+      <c r="GF11" s="92"/>
+      <c r="GG11" s="92"/>
+      <c r="GH11" s="92"/>
+      <c r="GI11" s="92"/>
+      <c r="GJ11" s="92"/>
+      <c r="GK11" s="92"/>
+      <c r="GL11" s="92"/>
+      <c r="GM11" s="92"/>
+      <c r="GN11" s="92"/>
+      <c r="GO11" s="92"/>
+      <c r="GP11" s="92"/>
+      <c r="GQ11" s="92"/>
+      <c r="GR11" s="92"/>
+      <c r="GS11" s="92"/>
+      <c r="GT11" s="92"/>
+      <c r="GU11" s="92"/>
+      <c r="GV11" s="92"/>
+    </row>
+    <row r="12" spans="1:204" s="83" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="166" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="101">
+      <c r="B12" s="89">
         <v>1</v>
       </c>
-      <c r="C12" s="101">
+      <c r="C12" s="89">
         <v>1</v>
       </c>
-      <c r="D12" s="143">
+      <c r="D12" s="131">
         <v>1</v>
       </c>
-      <c r="E12" s="144">
+      <c r="E12" s="132">
         <v>1</v>
       </c>
-      <c r="F12" s="72">
+      <c r="F12" s="67">
         <v>1</v>
       </c>
-      <c r="G12" s="103">
+      <c r="G12" s="91">
         <v>1</v>
       </c>
-      <c r="H12" s="102">
+      <c r="H12" s="90">
         <v>1</v>
       </c>
-      <c r="I12" s="72">
+      <c r="I12" s="67">
         <v>1</v>
       </c>
-      <c r="J12" s="103">
+      <c r="J12" s="91">
         <v>1</v>
       </c>
-      <c r="K12" s="102">
+      <c r="K12" s="90">
         <v>1</v>
       </c>
-      <c r="L12" s="101">
+      <c r="L12" s="89">
         <v>1</v>
       </c>
-      <c r="M12" s="140">
+      <c r="M12" s="128">
         <v>1</v>
       </c>
-      <c r="N12" s="72">
+      <c r="N12" s="67">
         <v>1</v>
       </c>
-      <c r="O12" s="71">
+      <c r="O12" s="66">
         <v>1</v>
       </c>
-      <c r="P12" s="112"/>
-      <c r="Q12" s="112"/>
-      <c r="R12" s="111"/>
-      <c r="S12" s="99"/>
-      <c r="T12" s="110"/>
-      <c r="U12" s="110"/>
-      <c r="V12" s="110"/>
-      <c r="W12" s="110"/>
-      <c r="X12" s="110"/>
-      <c r="Y12" s="110"/>
-      <c r="Z12" s="110"/>
-      <c r="AA12" s="110"/>
-      <c r="AB12" s="110"/>
-      <c r="AC12" s="110"/>
-      <c r="AD12" s="110"/>
-      <c r="AE12" s="110"/>
-      <c r="AF12" s="110"/>
-      <c r="AG12" s="110"/>
-      <c r="AH12" s="110"/>
-      <c r="AI12" s="110"/>
-      <c r="AJ12" s="110"/>
-      <c r="AK12" s="110"/>
-      <c r="AL12" s="110"/>
-      <c r="AM12" s="110"/>
-      <c r="AN12" s="110"/>
-      <c r="AO12" s="110"/>
-      <c r="AP12" s="110"/>
-      <c r="AQ12" s="110"/>
-      <c r="AR12" s="110"/>
-      <c r="AS12" s="110"/>
-      <c r="AT12" s="108"/>
-      <c r="AU12" s="108"/>
-      <c r="AV12" s="108"/>
-      <c r="AW12" s="108"/>
-      <c r="AX12" s="108"/>
-      <c r="AY12" s="108"/>
-      <c r="AZ12" s="108"/>
-      <c r="BA12" s="108"/>
-      <c r="BB12" s="108"/>
-      <c r="BC12" s="108"/>
-      <c r="BD12" s="108"/>
-      <c r="BE12" s="108"/>
-      <c r="BF12" s="109"/>
-      <c r="BG12" s="109"/>
-      <c r="BH12" s="109"/>
-      <c r="BI12" s="109"/>
-      <c r="BJ12" s="109"/>
-      <c r="BK12" s="109"/>
-      <c r="BL12" s="109"/>
-      <c r="BM12" s="109"/>
-      <c r="BN12" s="109"/>
-      <c r="BO12" s="109"/>
-      <c r="BP12" s="109"/>
-      <c r="BQ12" s="109"/>
-      <c r="BR12" s="109"/>
-      <c r="BS12" s="109"/>
-      <c r="BT12" s="109"/>
-      <c r="BU12" s="109"/>
-      <c r="BV12" s="109"/>
-      <c r="BW12" s="109"/>
-      <c r="BX12" s="109"/>
-      <c r="BY12" s="109"/>
-      <c r="BZ12" s="109"/>
-      <c r="CA12" s="109"/>
-      <c r="CB12" s="109"/>
-      <c r="CC12" s="109"/>
-      <c r="CD12" s="109"/>
-      <c r="CE12" s="109"/>
-      <c r="CF12" s="109"/>
-      <c r="CG12" s="109"/>
-      <c r="CH12" s="109"/>
-      <c r="CI12" s="109"/>
-      <c r="CJ12" s="109"/>
-      <c r="CK12" s="109"/>
-      <c r="CL12" s="109"/>
-      <c r="CM12" s="109"/>
-      <c r="CN12" s="109"/>
-      <c r="CO12" s="109"/>
-      <c r="CP12" s="109"/>
-      <c r="CQ12" s="109"/>
-      <c r="CR12" s="109"/>
-      <c r="CS12" s="109"/>
-      <c r="CT12" s="109"/>
-      <c r="CU12" s="109"/>
-      <c r="CV12" s="109"/>
-      <c r="CW12" s="109"/>
-      <c r="CX12" s="109"/>
-      <c r="CY12" s="109"/>
-      <c r="CZ12" s="109"/>
-      <c r="DA12" s="109"/>
-      <c r="DB12" s="109"/>
-      <c r="DC12" s="109"/>
-      <c r="DD12" s="109"/>
-      <c r="DE12" s="109"/>
-      <c r="DF12" s="109"/>
-      <c r="DG12" s="109"/>
-      <c r="DH12" s="109"/>
-      <c r="DI12" s="109"/>
-      <c r="DJ12" s="109"/>
-      <c r="DK12" s="109"/>
-      <c r="DL12" s="109"/>
-      <c r="DM12" s="109"/>
-      <c r="DN12" s="109"/>
-      <c r="DO12" s="109"/>
-      <c r="DP12" s="109"/>
-      <c r="DQ12" s="109"/>
-      <c r="DR12" s="109"/>
-      <c r="DS12" s="109"/>
-      <c r="DT12" s="109"/>
-      <c r="DU12" s="109"/>
-      <c r="DV12" s="109"/>
-      <c r="DW12" s="109"/>
-      <c r="DX12" s="109"/>
-      <c r="DY12" s="109"/>
-      <c r="DZ12" s="109"/>
-      <c r="EA12" s="109"/>
-      <c r="EB12" s="109"/>
-      <c r="EC12" s="109"/>
-      <c r="ED12" s="109"/>
-      <c r="EE12" s="109"/>
-      <c r="EF12" s="109"/>
-      <c r="EG12" s="109"/>
-      <c r="EH12" s="108"/>
-      <c r="EI12" s="108"/>
-      <c r="EJ12" s="108"/>
-      <c r="EK12" s="108"/>
-      <c r="EL12" s="108"/>
-      <c r="EM12" s="108"/>
-      <c r="EN12" s="108"/>
-      <c r="EO12" s="108"/>
-      <c r="EP12" s="108"/>
-      <c r="EQ12" s="108"/>
-      <c r="ER12" s="108"/>
-      <c r="ES12" s="108"/>
-      <c r="ET12" s="108"/>
-      <c r="EU12" s="108"/>
-      <c r="EV12" s="108"/>
-      <c r="EW12" s="108"/>
-      <c r="EX12" s="108"/>
-      <c r="EY12" s="108"/>
-      <c r="EZ12" s="108"/>
-      <c r="FA12" s="108"/>
-      <c r="FB12" s="108"/>
-      <c r="FC12" s="108"/>
-      <c r="FD12" s="108"/>
-      <c r="FE12" s="108"/>
-      <c r="FF12" s="108"/>
-      <c r="FG12" s="108"/>
-      <c r="FH12" s="108"/>
-      <c r="FI12" s="108"/>
-      <c r="FJ12" s="108"/>
-      <c r="FK12" s="108"/>
-      <c r="FL12" s="108"/>
-      <c r="FM12" s="108"/>
-      <c r="FN12" s="108"/>
-      <c r="FO12" s="108"/>
-      <c r="FP12" s="108"/>
-      <c r="FQ12" s="108"/>
-      <c r="FR12" s="108"/>
-      <c r="FS12" s="108"/>
-      <c r="FT12" s="108"/>
-      <c r="FU12" s="108"/>
-      <c r="FV12" s="108"/>
-      <c r="FW12" s="108"/>
-      <c r="FX12" s="108"/>
-      <c r="FY12" s="108"/>
-      <c r="FZ12" s="108"/>
-      <c r="GA12" s="108"/>
-      <c r="GB12" s="108"/>
-      <c r="GC12" s="108"/>
-      <c r="GD12" s="108"/>
-      <c r="GE12" s="108"/>
-      <c r="GF12" s="108"/>
-      <c r="GG12" s="108"/>
-      <c r="GH12" s="108"/>
-      <c r="GI12" s="108"/>
-      <c r="GJ12" s="108"/>
-      <c r="GK12" s="108"/>
-      <c r="GL12" s="108"/>
-      <c r="GM12" s="108"/>
-      <c r="GN12" s="108"/>
-      <c r="GO12" s="108"/>
-      <c r="GP12" s="108"/>
-      <c r="GQ12" s="108"/>
-      <c r="GR12" s="108"/>
-      <c r="GS12" s="108"/>
-      <c r="GT12" s="108"/>
-      <c r="GU12" s="108"/>
-      <c r="GV12" s="108"/>
+      <c r="P12" s="100"/>
+      <c r="Q12" s="100"/>
+      <c r="R12" s="99"/>
+      <c r="S12" s="87"/>
+      <c r="T12" s="98"/>
+      <c r="U12" s="98"/>
+      <c r="V12" s="98"/>
+      <c r="W12" s="98"/>
+      <c r="X12" s="98"/>
+      <c r="Y12" s="98"/>
+      <c r="Z12" s="98"/>
+      <c r="AA12" s="98"/>
+      <c r="AB12" s="98"/>
+      <c r="AC12" s="98"/>
+      <c r="AD12" s="98"/>
+      <c r="AE12" s="98"/>
+      <c r="AF12" s="98"/>
+      <c r="AG12" s="98"/>
+      <c r="AH12" s="98"/>
+      <c r="AI12" s="98"/>
+      <c r="AJ12" s="98"/>
+      <c r="AK12" s="98"/>
+      <c r="AL12" s="98"/>
+      <c r="AM12" s="98"/>
+      <c r="AN12" s="98"/>
+      <c r="AO12" s="98"/>
+      <c r="AP12" s="98"/>
+      <c r="AQ12" s="98"/>
+      <c r="AR12" s="98"/>
+      <c r="AS12" s="98"/>
+      <c r="AT12" s="96"/>
+      <c r="AU12" s="96"/>
+      <c r="AV12" s="96"/>
+      <c r="AW12" s="96"/>
+      <c r="AX12" s="96"/>
+      <c r="AY12" s="96"/>
+      <c r="AZ12" s="96"/>
+      <c r="BA12" s="96"/>
+      <c r="BB12" s="96"/>
+      <c r="BC12" s="96"/>
+      <c r="BD12" s="96"/>
+      <c r="BE12" s="96"/>
+      <c r="BF12" s="97"/>
+      <c r="BG12" s="97"/>
+      <c r="BH12" s="97"/>
+      <c r="BI12" s="97"/>
+      <c r="BJ12" s="97"/>
+      <c r="BK12" s="97"/>
+      <c r="BL12" s="97"/>
+      <c r="BM12" s="97"/>
+      <c r="BN12" s="97"/>
+      <c r="BO12" s="97"/>
+      <c r="BP12" s="97"/>
+      <c r="BQ12" s="97"/>
+      <c r="BR12" s="97"/>
+      <c r="BS12" s="97"/>
+      <c r="BT12" s="97"/>
+      <c r="BU12" s="97"/>
+      <c r="BV12" s="97"/>
+      <c r="BW12" s="97"/>
+      <c r="BX12" s="97"/>
+      <c r="BY12" s="97"/>
+      <c r="BZ12" s="97"/>
+      <c r="CA12" s="97"/>
+      <c r="CB12" s="97"/>
+      <c r="CC12" s="97"/>
+      <c r="CD12" s="97"/>
+      <c r="CE12" s="97"/>
+      <c r="CF12" s="97"/>
+      <c r="CG12" s="97"/>
+      <c r="CH12" s="97"/>
+      <c r="CI12" s="97"/>
+      <c r="CJ12" s="97"/>
+      <c r="CK12" s="97"/>
+      <c r="CL12" s="97"/>
+      <c r="CM12" s="97"/>
+      <c r="CN12" s="97"/>
+      <c r="CO12" s="97"/>
+      <c r="CP12" s="97"/>
+      <c r="CQ12" s="97"/>
+      <c r="CR12" s="97"/>
+      <c r="CS12" s="97"/>
+      <c r="CT12" s="97"/>
+      <c r="CU12" s="97"/>
+      <c r="CV12" s="97"/>
+      <c r="CW12" s="97"/>
+      <c r="CX12" s="97"/>
+      <c r="CY12" s="97"/>
+      <c r="CZ12" s="97"/>
+      <c r="DA12" s="97"/>
+      <c r="DB12" s="97"/>
+      <c r="DC12" s="97"/>
+      <c r="DD12" s="97"/>
+      <c r="DE12" s="97"/>
+      <c r="DF12" s="97"/>
+      <c r="DG12" s="97"/>
+      <c r="DH12" s="97"/>
+      <c r="DI12" s="97"/>
+      <c r="DJ12" s="97"/>
+      <c r="DK12" s="97"/>
+      <c r="DL12" s="97"/>
+      <c r="DM12" s="97"/>
+      <c r="DN12" s="97"/>
+      <c r="DO12" s="97"/>
+      <c r="DP12" s="97"/>
+      <c r="DQ12" s="97"/>
+      <c r="DR12" s="97"/>
+      <c r="DS12" s="97"/>
+      <c r="DT12" s="97"/>
+      <c r="DU12" s="97"/>
+      <c r="DV12" s="97"/>
+      <c r="DW12" s="97"/>
+      <c r="DX12" s="97"/>
+      <c r="DY12" s="97"/>
+      <c r="DZ12" s="97"/>
+      <c r="EA12" s="97"/>
+      <c r="EB12" s="97"/>
+      <c r="EC12" s="97"/>
+      <c r="ED12" s="97"/>
+      <c r="EE12" s="97"/>
+      <c r="EF12" s="97"/>
+      <c r="EG12" s="97"/>
+      <c r="EH12" s="96"/>
+      <c r="EI12" s="96"/>
+      <c r="EJ12" s="96"/>
+      <c r="EK12" s="96"/>
+      <c r="EL12" s="96"/>
+      <c r="EM12" s="96"/>
+      <c r="EN12" s="96"/>
+      <c r="EO12" s="96"/>
+      <c r="EP12" s="96"/>
+      <c r="EQ12" s="96"/>
+      <c r="ER12" s="96"/>
+      <c r="ES12" s="96"/>
+      <c r="ET12" s="96"/>
+      <c r="EU12" s="96"/>
+      <c r="EV12" s="96"/>
+      <c r="EW12" s="96"/>
+      <c r="EX12" s="96"/>
+      <c r="EY12" s="96"/>
+      <c r="EZ12" s="96"/>
+      <c r="FA12" s="96"/>
+      <c r="FB12" s="96"/>
+      <c r="FC12" s="96"/>
+      <c r="FD12" s="96"/>
+      <c r="FE12" s="96"/>
+      <c r="FF12" s="96"/>
+      <c r="FG12" s="96"/>
+      <c r="FH12" s="96"/>
+      <c r="FI12" s="96"/>
+      <c r="FJ12" s="96"/>
+      <c r="FK12" s="96"/>
+      <c r="FL12" s="96"/>
+      <c r="FM12" s="96"/>
+      <c r="FN12" s="96"/>
+      <c r="FO12" s="96"/>
+      <c r="FP12" s="96"/>
+      <c r="FQ12" s="96"/>
+      <c r="FR12" s="96"/>
+      <c r="FS12" s="96"/>
+      <c r="FT12" s="96"/>
+      <c r="FU12" s="96"/>
+      <c r="FV12" s="96"/>
+      <c r="FW12" s="96"/>
+      <c r="FX12" s="96"/>
+      <c r="FY12" s="96"/>
+      <c r="FZ12" s="96"/>
+      <c r="GA12" s="96"/>
+      <c r="GB12" s="96"/>
+      <c r="GC12" s="96"/>
+      <c r="GD12" s="96"/>
+      <c r="GE12" s="96"/>
+      <c r="GF12" s="96"/>
+      <c r="GG12" s="96"/>
+      <c r="GH12" s="96"/>
+      <c r="GI12" s="96"/>
+      <c r="GJ12" s="96"/>
+      <c r="GK12" s="96"/>
+      <c r="GL12" s="96"/>
+      <c r="GM12" s="96"/>
+      <c r="GN12" s="96"/>
+      <c r="GO12" s="96"/>
+      <c r="GP12" s="96"/>
+      <c r="GQ12" s="96"/>
+      <c r="GR12" s="96"/>
+      <c r="GS12" s="96"/>
+      <c r="GT12" s="96"/>
+      <c r="GU12" s="96"/>
+      <c r="GV12" s="96"/>
     </row>
     <row r="13" spans="1:204" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="167"/>
-      <c r="B13" s="145" t="s">
+      <c r="A13" s="166"/>
+      <c r="B13" s="133" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="145" t="s">
+      <c r="C13" s="133" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="145">
+      <c r="D13" s="133">
         <f>C12-D12</f>
         <v>0</v>
       </c>
-      <c r="E13" s="145">
+      <c r="E13" s="133">
         <f>C12-E12</f>
         <v>0</v>
       </c>
-      <c r="F13" s="146" t="s">
+      <c r="F13" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="146">
+      <c r="G13" s="134">
         <f>F12-G12</f>
         <v>0</v>
       </c>
-      <c r="H13" s="146">
+      <c r="H13" s="134">
         <f>F12-H12</f>
         <v>0</v>
       </c>
-      <c r="I13" s="146" t="s">
+      <c r="I13" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="146">
+      <c r="J13" s="134">
         <f>I12-J12</f>
         <v>0</v>
       </c>
-      <c r="K13" s="146">
+      <c r="K13" s="134">
         <f>I12-K12</f>
         <v>0</v>
       </c>
-      <c r="L13" s="145">
+      <c r="L13" s="133">
         <f>L12-M12</f>
         <v>0</v>
       </c>
-      <c r="M13" s="94">
+      <c r="M13" s="82">
         <f>IFERROR(L12/M12, 0)</f>
         <v>1</v>
       </c>
-      <c r="N13" s="168">
+      <c r="N13" s="157">
         <f>N12-O12</f>
         <v>0</v>
       </c>
-      <c r="O13" s="169" t="str">
+      <c r="O13" s="158" t="str">
         <f>IF(TEXT(N12-O12,"+0,0; -0,0")="+0,0","0,0",TEXT(N12-O12,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
-      <c r="P13" s="91"/>
-      <c r="Q13" s="91"/>
-      <c r="R13" s="111"/>
-      <c r="S13" s="91"/>
-      <c r="T13" s="106"/>
-      <c r="U13" s="106"/>
-      <c r="V13" s="106"/>
-      <c r="W13" s="106"/>
-      <c r="X13" s="106"/>
-      <c r="Y13" s="106"/>
-      <c r="Z13" s="106"/>
-      <c r="AA13" s="106"/>
-      <c r="AB13" s="106"/>
-      <c r="AC13" s="106"/>
-      <c r="AD13" s="106"/>
-      <c r="AE13" s="106"/>
-      <c r="AF13" s="106"/>
-      <c r="AG13" s="106"/>
-      <c r="AH13" s="106"/>
-      <c r="AI13" s="105"/>
-      <c r="AJ13" s="105"/>
-      <c r="AK13" s="105"/>
-      <c r="AL13" s="105"/>
-      <c r="AM13" s="105"/>
-      <c r="AN13" s="105"/>
-      <c r="AO13" s="105"/>
-      <c r="AP13" s="105"/>
-      <c r="AQ13" s="105"/>
-      <c r="AR13" s="105"/>
-      <c r="AS13" s="105"/>
-      <c r="AT13" s="105"/>
-      <c r="AU13" s="105"/>
-      <c r="AV13" s="105"/>
-      <c r="AW13" s="105"/>
-      <c r="AX13" s="105"/>
-      <c r="AY13" s="105"/>
-      <c r="AZ13" s="105"/>
-      <c r="BA13" s="105"/>
-      <c r="BB13" s="105"/>
-      <c r="BC13" s="105"/>
-      <c r="BD13" s="105"/>
-      <c r="BE13" s="105"/>
-      <c r="BF13" s="105"/>
-      <c r="BG13" s="105"/>
-      <c r="BH13" s="105"/>
-      <c r="BI13" s="105"/>
-      <c r="BJ13" s="105"/>
-      <c r="BK13" s="105"/>
-      <c r="BL13" s="105"/>
-      <c r="BM13" s="105"/>
-      <c r="BN13" s="105"/>
-      <c r="BO13" s="105"/>
-      <c r="BP13" s="105"/>
-      <c r="BQ13" s="105"/>
-      <c r="BR13" s="105"/>
-      <c r="BS13" s="105"/>
-      <c r="BT13" s="105"/>
-      <c r="BU13" s="105"/>
-      <c r="BV13" s="105"/>
-      <c r="BW13" s="105"/>
-      <c r="BX13" s="105"/>
-      <c r="BY13" s="105"/>
-      <c r="BZ13" s="105"/>
-      <c r="CA13" s="105"/>
-      <c r="CB13" s="105"/>
-      <c r="CC13" s="105"/>
-      <c r="CD13" s="105"/>
-      <c r="CE13" s="105"/>
-      <c r="CF13" s="105"/>
-      <c r="CG13" s="105"/>
-      <c r="CH13" s="105"/>
-      <c r="CI13" s="105"/>
-      <c r="CJ13" s="105"/>
-      <c r="CK13" s="105"/>
-      <c r="CL13" s="105"/>
-      <c r="CM13" s="105"/>
-      <c r="CN13" s="105"/>
-      <c r="CO13" s="105"/>
-      <c r="CP13" s="105"/>
-      <c r="CQ13" s="105"/>
-      <c r="CR13" s="105"/>
-      <c r="CS13" s="105"/>
-      <c r="CT13" s="105"/>
-      <c r="CU13" s="105"/>
-      <c r="CV13" s="105"/>
-      <c r="CW13" s="105"/>
-      <c r="CX13" s="105"/>
-      <c r="CY13" s="105"/>
-      <c r="CZ13" s="105"/>
-      <c r="DA13" s="105"/>
-      <c r="DB13" s="105"/>
-      <c r="DC13" s="105"/>
-      <c r="DD13" s="105"/>
-      <c r="DE13" s="105"/>
-      <c r="DF13" s="105"/>
-      <c r="DG13" s="105"/>
-      <c r="DH13" s="105"/>
-      <c r="DI13" s="105"/>
-      <c r="DJ13" s="105"/>
-      <c r="DK13" s="105"/>
-      <c r="DL13" s="105"/>
-      <c r="DM13" s="105"/>
-      <c r="DN13" s="105"/>
-      <c r="DO13" s="105"/>
-      <c r="DP13" s="105"/>
-      <c r="DQ13" s="105"/>
-      <c r="DR13" s="105"/>
-      <c r="DS13" s="105"/>
-      <c r="DT13" s="105"/>
-      <c r="DU13" s="105"/>
-      <c r="DV13" s="105"/>
-      <c r="DW13" s="105"/>
-      <c r="DX13" s="105"/>
-      <c r="DY13" s="105"/>
-      <c r="DZ13" s="105"/>
-      <c r="EA13" s="105"/>
-      <c r="EB13" s="105"/>
-      <c r="EC13" s="105"/>
-      <c r="ED13" s="105"/>
-      <c r="EE13" s="105"/>
-      <c r="EF13" s="105"/>
-      <c r="EG13" s="105"/>
-      <c r="EH13" s="104"/>
-      <c r="EI13" s="104"/>
-      <c r="EJ13" s="104"/>
-      <c r="EK13" s="104"/>
-      <c r="EL13" s="104"/>
-      <c r="EM13" s="104"/>
-      <c r="EN13" s="104"/>
-      <c r="EO13" s="104"/>
-      <c r="EP13" s="104"/>
-      <c r="EQ13" s="104"/>
-      <c r="ER13" s="104"/>
-      <c r="ES13" s="104"/>
-      <c r="ET13" s="104"/>
-      <c r="EU13" s="104"/>
-      <c r="EV13" s="104"/>
-      <c r="EW13" s="104"/>
-      <c r="EX13" s="104"/>
-      <c r="EY13" s="104"/>
-      <c r="EZ13" s="104"/>
-      <c r="FA13" s="104"/>
-      <c r="FB13" s="104"/>
-      <c r="FC13" s="104"/>
-      <c r="FD13" s="104"/>
-      <c r="FE13" s="104"/>
-      <c r="FF13" s="104"/>
-      <c r="FG13" s="104"/>
-      <c r="FH13" s="104"/>
-      <c r="FI13" s="104"/>
-      <c r="FJ13" s="104"/>
-      <c r="FK13" s="104"/>
-      <c r="FL13" s="104"/>
-      <c r="FM13" s="104"/>
-      <c r="FN13" s="104"/>
-      <c r="FO13" s="104"/>
-      <c r="FP13" s="104"/>
-      <c r="FQ13" s="104"/>
-      <c r="FR13" s="104"/>
-      <c r="FS13" s="104"/>
-      <c r="FT13" s="104"/>
-      <c r="FU13" s="104"/>
-      <c r="FV13" s="104"/>
-      <c r="FW13" s="104"/>
-      <c r="FX13" s="104"/>
-      <c r="FY13" s="104"/>
-      <c r="FZ13" s="104"/>
-      <c r="GA13" s="104"/>
-      <c r="GB13" s="104"/>
-      <c r="GC13" s="104"/>
-      <c r="GD13" s="104"/>
-      <c r="GE13" s="104"/>
-      <c r="GF13" s="104"/>
-      <c r="GG13" s="104"/>
-      <c r="GH13" s="104"/>
-      <c r="GI13" s="104"/>
-      <c r="GJ13" s="104"/>
-      <c r="GK13" s="104"/>
-      <c r="GL13" s="104"/>
-      <c r="GM13" s="104"/>
-      <c r="GN13" s="104"/>
-      <c r="GO13" s="104"/>
-      <c r="GP13" s="104"/>
-      <c r="GQ13" s="104"/>
-      <c r="GR13" s="104"/>
-      <c r="GS13" s="104"/>
-      <c r="GT13" s="104"/>
-      <c r="GU13" s="104"/>
-      <c r="GV13" s="104"/>
-    </row>
-    <row r="14" spans="1:204" s="95" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="167" t="s">
+      <c r="P13" s="79"/>
+      <c r="Q13" s="79"/>
+      <c r="R13" s="99"/>
+      <c r="S13" s="79"/>
+      <c r="T13" s="94"/>
+      <c r="U13" s="94"/>
+      <c r="V13" s="94"/>
+      <c r="W13" s="94"/>
+      <c r="X13" s="94"/>
+      <c r="Y13" s="94"/>
+      <c r="Z13" s="94"/>
+      <c r="AA13" s="94"/>
+      <c r="AB13" s="94"/>
+      <c r="AC13" s="94"/>
+      <c r="AD13" s="94"/>
+      <c r="AE13" s="94"/>
+      <c r="AF13" s="94"/>
+      <c r="AG13" s="94"/>
+      <c r="AH13" s="94"/>
+      <c r="AI13" s="93"/>
+      <c r="AJ13" s="93"/>
+      <c r="AK13" s="93"/>
+      <c r="AL13" s="93"/>
+      <c r="AM13" s="93"/>
+      <c r="AN13" s="93"/>
+      <c r="AO13" s="93"/>
+      <c r="AP13" s="93"/>
+      <c r="AQ13" s="93"/>
+      <c r="AR13" s="93"/>
+      <c r="AS13" s="93"/>
+      <c r="AT13" s="93"/>
+      <c r="AU13" s="93"/>
+      <c r="AV13" s="93"/>
+      <c r="AW13" s="93"/>
+      <c r="AX13" s="93"/>
+      <c r="AY13" s="93"/>
+      <c r="AZ13" s="93"/>
+      <c r="BA13" s="93"/>
+      <c r="BB13" s="93"/>
+      <c r="BC13" s="93"/>
+      <c r="BD13" s="93"/>
+      <c r="BE13" s="93"/>
+      <c r="BF13" s="93"/>
+      <c r="BG13" s="93"/>
+      <c r="BH13" s="93"/>
+      <c r="BI13" s="93"/>
+      <c r="BJ13" s="93"/>
+      <c r="BK13" s="93"/>
+      <c r="BL13" s="93"/>
+      <c r="BM13" s="93"/>
+      <c r="BN13" s="93"/>
+      <c r="BO13" s="93"/>
+      <c r="BP13" s="93"/>
+      <c r="BQ13" s="93"/>
+      <c r="BR13" s="93"/>
+      <c r="BS13" s="93"/>
+      <c r="BT13" s="93"/>
+      <c r="BU13" s="93"/>
+      <c r="BV13" s="93"/>
+      <c r="BW13" s="93"/>
+      <c r="BX13" s="93"/>
+      <c r="BY13" s="93"/>
+      <c r="BZ13" s="93"/>
+      <c r="CA13" s="93"/>
+      <c r="CB13" s="93"/>
+      <c r="CC13" s="93"/>
+      <c r="CD13" s="93"/>
+      <c r="CE13" s="93"/>
+      <c r="CF13" s="93"/>
+      <c r="CG13" s="93"/>
+      <c r="CH13" s="93"/>
+      <c r="CI13" s="93"/>
+      <c r="CJ13" s="93"/>
+      <c r="CK13" s="93"/>
+      <c r="CL13" s="93"/>
+      <c r="CM13" s="93"/>
+      <c r="CN13" s="93"/>
+      <c r="CO13" s="93"/>
+      <c r="CP13" s="93"/>
+      <c r="CQ13" s="93"/>
+      <c r="CR13" s="93"/>
+      <c r="CS13" s="93"/>
+      <c r="CT13" s="93"/>
+      <c r="CU13" s="93"/>
+      <c r="CV13" s="93"/>
+      <c r="CW13" s="93"/>
+      <c r="CX13" s="93"/>
+      <c r="CY13" s="93"/>
+      <c r="CZ13" s="93"/>
+      <c r="DA13" s="93"/>
+      <c r="DB13" s="93"/>
+      <c r="DC13" s="93"/>
+      <c r="DD13" s="93"/>
+      <c r="DE13" s="93"/>
+      <c r="DF13" s="93"/>
+      <c r="DG13" s="93"/>
+      <c r="DH13" s="93"/>
+      <c r="DI13" s="93"/>
+      <c r="DJ13" s="93"/>
+      <c r="DK13" s="93"/>
+      <c r="DL13" s="93"/>
+      <c r="DM13" s="93"/>
+      <c r="DN13" s="93"/>
+      <c r="DO13" s="93"/>
+      <c r="DP13" s="93"/>
+      <c r="DQ13" s="93"/>
+      <c r="DR13" s="93"/>
+      <c r="DS13" s="93"/>
+      <c r="DT13" s="93"/>
+      <c r="DU13" s="93"/>
+      <c r="DV13" s="93"/>
+      <c r="DW13" s="93"/>
+      <c r="DX13" s="93"/>
+      <c r="DY13" s="93"/>
+      <c r="DZ13" s="93"/>
+      <c r="EA13" s="93"/>
+      <c r="EB13" s="93"/>
+      <c r="EC13" s="93"/>
+      <c r="ED13" s="93"/>
+      <c r="EE13" s="93"/>
+      <c r="EF13" s="93"/>
+      <c r="EG13" s="93"/>
+      <c r="EH13" s="92"/>
+      <c r="EI13" s="92"/>
+      <c r="EJ13" s="92"/>
+      <c r="EK13" s="92"/>
+      <c r="EL13" s="92"/>
+      <c r="EM13" s="92"/>
+      <c r="EN13" s="92"/>
+      <c r="EO13" s="92"/>
+      <c r="EP13" s="92"/>
+      <c r="EQ13" s="92"/>
+      <c r="ER13" s="92"/>
+      <c r="ES13" s="92"/>
+      <c r="ET13" s="92"/>
+      <c r="EU13" s="92"/>
+      <c r="EV13" s="92"/>
+      <c r="EW13" s="92"/>
+      <c r="EX13" s="92"/>
+      <c r="EY13" s="92"/>
+      <c r="EZ13" s="92"/>
+      <c r="FA13" s="92"/>
+      <c r="FB13" s="92"/>
+      <c r="FC13" s="92"/>
+      <c r="FD13" s="92"/>
+      <c r="FE13" s="92"/>
+      <c r="FF13" s="92"/>
+      <c r="FG13" s="92"/>
+      <c r="FH13" s="92"/>
+      <c r="FI13" s="92"/>
+      <c r="FJ13" s="92"/>
+      <c r="FK13" s="92"/>
+      <c r="FL13" s="92"/>
+      <c r="FM13" s="92"/>
+      <c r="FN13" s="92"/>
+      <c r="FO13" s="92"/>
+      <c r="FP13" s="92"/>
+      <c r="FQ13" s="92"/>
+      <c r="FR13" s="92"/>
+      <c r="FS13" s="92"/>
+      <c r="FT13" s="92"/>
+      <c r="FU13" s="92"/>
+      <c r="FV13" s="92"/>
+      <c r="FW13" s="92"/>
+      <c r="FX13" s="92"/>
+      <c r="FY13" s="92"/>
+      <c r="FZ13" s="92"/>
+      <c r="GA13" s="92"/>
+      <c r="GB13" s="92"/>
+      <c r="GC13" s="92"/>
+      <c r="GD13" s="92"/>
+      <c r="GE13" s="92"/>
+      <c r="GF13" s="92"/>
+      <c r="GG13" s="92"/>
+      <c r="GH13" s="92"/>
+      <c r="GI13" s="92"/>
+      <c r="GJ13" s="92"/>
+      <c r="GK13" s="92"/>
+      <c r="GL13" s="92"/>
+      <c r="GM13" s="92"/>
+      <c r="GN13" s="92"/>
+      <c r="GO13" s="92"/>
+      <c r="GP13" s="92"/>
+      <c r="GQ13" s="92"/>
+      <c r="GR13" s="92"/>
+      <c r="GS13" s="92"/>
+      <c r="GT13" s="92"/>
+      <c r="GU13" s="92"/>
+      <c r="GV13" s="92"/>
+    </row>
+    <row r="14" spans="1:204" s="83" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="166" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="101">
+      <c r="B14" s="89">
         <v>1</v>
       </c>
-      <c r="C14" s="101">
+      <c r="C14" s="89">
         <v>1</v>
       </c>
-      <c r="D14" s="143">
+      <c r="D14" s="131">
         <v>1</v>
       </c>
-      <c r="E14" s="144">
+      <c r="E14" s="132">
         <v>1</v>
       </c>
-      <c r="F14" s="72">
+      <c r="F14" s="67">
         <v>1</v>
       </c>
-      <c r="G14" s="103">
+      <c r="G14" s="91">
         <v>1</v>
       </c>
-      <c r="H14" s="102">
+      <c r="H14" s="90">
         <v>1</v>
       </c>
-      <c r="I14" s="72">
+      <c r="I14" s="67">
         <v>1</v>
       </c>
-      <c r="J14" s="103">
+      <c r="J14" s="91">
         <v>1</v>
       </c>
-      <c r="K14" s="102">
+      <c r="K14" s="90">
         <v>1</v>
       </c>
-      <c r="L14" s="101">
+      <c r="L14" s="89">
         <v>1</v>
       </c>
-      <c r="M14" s="140">
+      <c r="M14" s="128">
         <v>1</v>
       </c>
-      <c r="N14" s="72">
+      <c r="N14" s="67">
         <v>1</v>
       </c>
-      <c r="O14" s="71">
+      <c r="O14" s="66">
         <v>1</v>
       </c>
-      <c r="P14" s="112"/>
-      <c r="Q14" s="112"/>
-      <c r="R14" s="111"/>
-      <c r="S14" s="99"/>
-      <c r="T14" s="110"/>
-      <c r="U14" s="110"/>
-      <c r="V14" s="110"/>
-      <c r="W14" s="110"/>
-      <c r="X14" s="110"/>
-      <c r="Y14" s="110"/>
-      <c r="Z14" s="110"/>
-      <c r="AA14" s="110"/>
-      <c r="AB14" s="110"/>
-      <c r="AC14" s="110"/>
-      <c r="AD14" s="110"/>
-      <c r="AE14" s="108"/>
-      <c r="AF14" s="110"/>
-      <c r="AG14" s="110"/>
-      <c r="AH14" s="110"/>
-      <c r="AI14" s="110"/>
-      <c r="AJ14" s="110"/>
-      <c r="AK14" s="110"/>
-      <c r="AL14" s="110"/>
-      <c r="AM14" s="110"/>
-      <c r="AN14" s="110"/>
-      <c r="AO14" s="110"/>
-      <c r="AP14" s="110"/>
-      <c r="AQ14" s="110"/>
-      <c r="AR14" s="110"/>
-      <c r="AS14" s="110"/>
-      <c r="AT14" s="108"/>
-      <c r="AU14" s="108"/>
-      <c r="AV14" s="108"/>
-      <c r="AW14" s="108"/>
-      <c r="AX14" s="108"/>
-      <c r="AY14" s="108"/>
-      <c r="AZ14" s="108"/>
-      <c r="BA14" s="108"/>
-      <c r="BB14" s="108"/>
-      <c r="BC14" s="108"/>
-      <c r="BD14" s="108"/>
-      <c r="BE14" s="108"/>
-      <c r="BF14" s="109"/>
-      <c r="BG14" s="109"/>
-      <c r="BH14" s="109"/>
-      <c r="BI14" s="109"/>
-      <c r="BJ14" s="109"/>
-      <c r="BK14" s="109"/>
-      <c r="BL14" s="109"/>
-      <c r="BM14" s="109"/>
-      <c r="BN14" s="109"/>
-      <c r="BO14" s="109"/>
-      <c r="BP14" s="109"/>
-      <c r="BQ14" s="109"/>
-      <c r="BR14" s="109"/>
-      <c r="BS14" s="109"/>
-      <c r="BT14" s="109"/>
-      <c r="BU14" s="109"/>
-      <c r="BV14" s="109"/>
-      <c r="BW14" s="109"/>
-      <c r="BX14" s="109"/>
-      <c r="BY14" s="109"/>
-      <c r="BZ14" s="109"/>
-      <c r="CA14" s="109"/>
-      <c r="CB14" s="109"/>
-      <c r="CC14" s="109"/>
-      <c r="CD14" s="109"/>
-      <c r="CE14" s="109"/>
-      <c r="CF14" s="109"/>
-      <c r="CG14" s="109"/>
-      <c r="CH14" s="109"/>
-      <c r="CI14" s="109"/>
-      <c r="CJ14" s="109"/>
-      <c r="CK14" s="109"/>
-      <c r="CL14" s="109"/>
-      <c r="CM14" s="109"/>
-      <c r="CN14" s="109"/>
-      <c r="CO14" s="109"/>
-      <c r="CP14" s="109"/>
-      <c r="CQ14" s="109"/>
-      <c r="CR14" s="109"/>
-      <c r="CS14" s="109"/>
-      <c r="CT14" s="109"/>
-      <c r="CU14" s="109"/>
-      <c r="CV14" s="109"/>
-      <c r="CW14" s="109"/>
-      <c r="CX14" s="109"/>
-      <c r="CY14" s="109"/>
-      <c r="CZ14" s="109"/>
-      <c r="DA14" s="109"/>
-      <c r="DB14" s="109"/>
-      <c r="DC14" s="109"/>
-      <c r="DD14" s="109"/>
-      <c r="DE14" s="109"/>
-      <c r="DF14" s="109"/>
-      <c r="DG14" s="109"/>
-      <c r="DH14" s="109"/>
-      <c r="DI14" s="109"/>
-      <c r="DJ14" s="109"/>
-      <c r="DK14" s="109"/>
-      <c r="DL14" s="109"/>
-      <c r="DM14" s="109"/>
-      <c r="DN14" s="109"/>
-      <c r="DO14" s="109"/>
-      <c r="DP14" s="109"/>
-      <c r="DQ14" s="109"/>
-      <c r="DR14" s="109"/>
-      <c r="DS14" s="109"/>
-      <c r="DT14" s="109"/>
-      <c r="DU14" s="109"/>
-      <c r="DV14" s="109"/>
-      <c r="DW14" s="109"/>
-      <c r="DX14" s="109"/>
-      <c r="DY14" s="109"/>
-      <c r="DZ14" s="109"/>
-      <c r="EA14" s="109"/>
-      <c r="EB14" s="109"/>
-      <c r="EC14" s="109"/>
-      <c r="ED14" s="109"/>
-      <c r="EE14" s="109"/>
-      <c r="EF14" s="109"/>
-      <c r="EG14" s="109"/>
-      <c r="EH14" s="108"/>
-      <c r="EI14" s="108"/>
-      <c r="EJ14" s="108"/>
-      <c r="EK14" s="108"/>
-      <c r="EL14" s="108"/>
-      <c r="EM14" s="108"/>
-      <c r="EN14" s="108"/>
-      <c r="EO14" s="108"/>
-      <c r="EP14" s="108"/>
-      <c r="EQ14" s="108"/>
-      <c r="ER14" s="108"/>
-      <c r="ES14" s="108"/>
-      <c r="ET14" s="108"/>
-      <c r="EU14" s="108"/>
-      <c r="EV14" s="108"/>
-      <c r="EW14" s="108"/>
-      <c r="EX14" s="108"/>
-      <c r="EY14" s="108"/>
-      <c r="EZ14" s="108"/>
-      <c r="FA14" s="108"/>
-      <c r="FB14" s="108"/>
-      <c r="FC14" s="108"/>
-      <c r="FD14" s="108"/>
-      <c r="FE14" s="108"/>
-      <c r="FF14" s="108"/>
-      <c r="FG14" s="108"/>
-      <c r="FH14" s="108"/>
-      <c r="FI14" s="108"/>
-      <c r="FJ14" s="108"/>
-      <c r="FK14" s="108"/>
-      <c r="FL14" s="108"/>
-      <c r="FM14" s="108"/>
-      <c r="FN14" s="108"/>
-      <c r="FO14" s="108"/>
-      <c r="FP14" s="108"/>
-      <c r="FQ14" s="108"/>
-      <c r="FR14" s="108"/>
-      <c r="FS14" s="108"/>
-      <c r="FT14" s="108"/>
-      <c r="FU14" s="108"/>
-      <c r="FV14" s="108"/>
-      <c r="FW14" s="108"/>
-      <c r="FX14" s="108"/>
-      <c r="FY14" s="108"/>
-      <c r="FZ14" s="108"/>
-      <c r="GA14" s="108"/>
-      <c r="GB14" s="108"/>
-      <c r="GC14" s="108"/>
-      <c r="GD14" s="108"/>
-      <c r="GE14" s="108"/>
-      <c r="GF14" s="108"/>
-      <c r="GG14" s="108"/>
-      <c r="GH14" s="108"/>
-      <c r="GI14" s="108"/>
-      <c r="GJ14" s="108"/>
-      <c r="GK14" s="108"/>
-      <c r="GL14" s="108"/>
-      <c r="GM14" s="108"/>
-      <c r="GN14" s="108"/>
-      <c r="GO14" s="108"/>
-      <c r="GP14" s="108"/>
-      <c r="GQ14" s="108"/>
-      <c r="GR14" s="108"/>
-      <c r="GS14" s="108"/>
-      <c r="GT14" s="108"/>
-      <c r="GU14" s="108"/>
-      <c r="GV14" s="108"/>
+      <c r="P14" s="100"/>
+      <c r="Q14" s="100"/>
+      <c r="R14" s="99"/>
+      <c r="S14" s="87"/>
+      <c r="T14" s="98"/>
+      <c r="U14" s="98"/>
+      <c r="V14" s="98"/>
+      <c r="W14" s="98"/>
+      <c r="X14" s="98"/>
+      <c r="Y14" s="98"/>
+      <c r="Z14" s="98"/>
+      <c r="AA14" s="98"/>
+      <c r="AB14" s="98"/>
+      <c r="AC14" s="98"/>
+      <c r="AD14" s="98"/>
+      <c r="AE14" s="96"/>
+      <c r="AF14" s="98"/>
+      <c r="AG14" s="98"/>
+      <c r="AH14" s="98"/>
+      <c r="AI14" s="98"/>
+      <c r="AJ14" s="98"/>
+      <c r="AK14" s="98"/>
+      <c r="AL14" s="98"/>
+      <c r="AM14" s="98"/>
+      <c r="AN14" s="98"/>
+      <c r="AO14" s="98"/>
+      <c r="AP14" s="98"/>
+      <c r="AQ14" s="98"/>
+      <c r="AR14" s="98"/>
+      <c r="AS14" s="98"/>
+      <c r="AT14" s="96"/>
+      <c r="AU14" s="96"/>
+      <c r="AV14" s="96"/>
+      <c r="AW14" s="96"/>
+      <c r="AX14" s="96"/>
+      <c r="AY14" s="96"/>
+      <c r="AZ14" s="96"/>
+      <c r="BA14" s="96"/>
+      <c r="BB14" s="96"/>
+      <c r="BC14" s="96"/>
+      <c r="BD14" s="96"/>
+      <c r="BE14" s="96"/>
+      <c r="BF14" s="97"/>
+      <c r="BG14" s="97"/>
+      <c r="BH14" s="97"/>
+      <c r="BI14" s="97"/>
+      <c r="BJ14" s="97"/>
+      <c r="BK14" s="97"/>
+      <c r="BL14" s="97"/>
+      <c r="BM14" s="97"/>
+      <c r="BN14" s="97"/>
+      <c r="BO14" s="97"/>
+      <c r="BP14" s="97"/>
+      <c r="BQ14" s="97"/>
+      <c r="BR14" s="97"/>
+      <c r="BS14" s="97"/>
+      <c r="BT14" s="97"/>
+      <c r="BU14" s="97"/>
+      <c r="BV14" s="97"/>
+      <c r="BW14" s="97"/>
+      <c r="BX14" s="97"/>
+      <c r="BY14" s="97"/>
+      <c r="BZ14" s="97"/>
+      <c r="CA14" s="97"/>
+      <c r="CB14" s="97"/>
+      <c r="CC14" s="97"/>
+      <c r="CD14" s="97"/>
+      <c r="CE14" s="97"/>
+      <c r="CF14" s="97"/>
+      <c r="CG14" s="97"/>
+      <c r="CH14" s="97"/>
+      <c r="CI14" s="97"/>
+      <c r="CJ14" s="97"/>
+      <c r="CK14" s="97"/>
+      <c r="CL14" s="97"/>
+      <c r="CM14" s="97"/>
+      <c r="CN14" s="97"/>
+      <c r="CO14" s="97"/>
+      <c r="CP14" s="97"/>
+      <c r="CQ14" s="97"/>
+      <c r="CR14" s="97"/>
+      <c r="CS14" s="97"/>
+      <c r="CT14" s="97"/>
+      <c r="CU14" s="97"/>
+      <c r="CV14" s="97"/>
+      <c r="CW14" s="97"/>
+      <c r="CX14" s="97"/>
+      <c r="CY14" s="97"/>
+      <c r="CZ14" s="97"/>
+      <c r="DA14" s="97"/>
+      <c r="DB14" s="97"/>
+      <c r="DC14" s="97"/>
+      <c r="DD14" s="97"/>
+      <c r="DE14" s="97"/>
+      <c r="DF14" s="97"/>
+      <c r="DG14" s="97"/>
+      <c r="DH14" s="97"/>
+      <c r="DI14" s="97"/>
+      <c r="DJ14" s="97"/>
+      <c r="DK14" s="97"/>
+      <c r="DL14" s="97"/>
+      <c r="DM14" s="97"/>
+      <c r="DN14" s="97"/>
+      <c r="DO14" s="97"/>
+      <c r="DP14" s="97"/>
+      <c r="DQ14" s="97"/>
+      <c r="DR14" s="97"/>
+      <c r="DS14" s="97"/>
+      <c r="DT14" s="97"/>
+      <c r="DU14" s="97"/>
+      <c r="DV14" s="97"/>
+      <c r="DW14" s="97"/>
+      <c r="DX14" s="97"/>
+      <c r="DY14" s="97"/>
+      <c r="DZ14" s="97"/>
+      <c r="EA14" s="97"/>
+      <c r="EB14" s="97"/>
+      <c r="EC14" s="97"/>
+      <c r="ED14" s="97"/>
+      <c r="EE14" s="97"/>
+      <c r="EF14" s="97"/>
+      <c r="EG14" s="97"/>
+      <c r="EH14" s="96"/>
+      <c r="EI14" s="96"/>
+      <c r="EJ14" s="96"/>
+      <c r="EK14" s="96"/>
+      <c r="EL14" s="96"/>
+      <c r="EM14" s="96"/>
+      <c r="EN14" s="96"/>
+      <c r="EO14" s="96"/>
+      <c r="EP14" s="96"/>
+      <c r="EQ14" s="96"/>
+      <c r="ER14" s="96"/>
+      <c r="ES14" s="96"/>
+      <c r="ET14" s="96"/>
+      <c r="EU14" s="96"/>
+      <c r="EV14" s="96"/>
+      <c r="EW14" s="96"/>
+      <c r="EX14" s="96"/>
+      <c r="EY14" s="96"/>
+      <c r="EZ14" s="96"/>
+      <c r="FA14" s="96"/>
+      <c r="FB14" s="96"/>
+      <c r="FC14" s="96"/>
+      <c r="FD14" s="96"/>
+      <c r="FE14" s="96"/>
+      <c r="FF14" s="96"/>
+      <c r="FG14" s="96"/>
+      <c r="FH14" s="96"/>
+      <c r="FI14" s="96"/>
+      <c r="FJ14" s="96"/>
+      <c r="FK14" s="96"/>
+      <c r="FL14" s="96"/>
+      <c r="FM14" s="96"/>
+      <c r="FN14" s="96"/>
+      <c r="FO14" s="96"/>
+      <c r="FP14" s="96"/>
+      <c r="FQ14" s="96"/>
+      <c r="FR14" s="96"/>
+      <c r="FS14" s="96"/>
+      <c r="FT14" s="96"/>
+      <c r="FU14" s="96"/>
+      <c r="FV14" s="96"/>
+      <c r="FW14" s="96"/>
+      <c r="FX14" s="96"/>
+      <c r="FY14" s="96"/>
+      <c r="FZ14" s="96"/>
+      <c r="GA14" s="96"/>
+      <c r="GB14" s="96"/>
+      <c r="GC14" s="96"/>
+      <c r="GD14" s="96"/>
+      <c r="GE14" s="96"/>
+      <c r="GF14" s="96"/>
+      <c r="GG14" s="96"/>
+      <c r="GH14" s="96"/>
+      <c r="GI14" s="96"/>
+      <c r="GJ14" s="96"/>
+      <c r="GK14" s="96"/>
+      <c r="GL14" s="96"/>
+      <c r="GM14" s="96"/>
+      <c r="GN14" s="96"/>
+      <c r="GO14" s="96"/>
+      <c r="GP14" s="96"/>
+      <c r="GQ14" s="96"/>
+      <c r="GR14" s="96"/>
+      <c r="GS14" s="96"/>
+      <c r="GT14" s="96"/>
+      <c r="GU14" s="96"/>
+      <c r="GV14" s="96"/>
     </row>
     <row r="15" spans="1:204" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="167"/>
-      <c r="B15" s="145" t="s">
+      <c r="A15" s="166"/>
+      <c r="B15" s="133" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="145" t="s">
+      <c r="C15" s="133" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="145">
+      <c r="D15" s="133">
         <f>C14-D14</f>
         <v>0</v>
       </c>
-      <c r="E15" s="145">
+      <c r="E15" s="133">
         <f>C14-E14</f>
         <v>0</v>
       </c>
-      <c r="F15" s="146" t="s">
+      <c r="F15" s="134" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="146">
+      <c r="G15" s="134">
         <f>F14-G14</f>
         <v>0</v>
       </c>
-      <c r="H15" s="146">
+      <c r="H15" s="134">
         <f>F14-H14</f>
         <v>0</v>
       </c>
-      <c r="I15" s="146" t="s">
+      <c r="I15" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="J15" s="146">
+      <c r="J15" s="134">
         <f>I14-J14</f>
         <v>0</v>
       </c>
-      <c r="K15" s="146">
+      <c r="K15" s="134">
         <f>I14-K14</f>
         <v>0</v>
       </c>
-      <c r="L15" s="145">
+      <c r="L15" s="133">
         <f>L14-M14</f>
         <v>0</v>
       </c>
-      <c r="M15" s="94">
+      <c r="M15" s="82">
         <f>IFERROR(L14/M14, 0)</f>
         <v>1</v>
       </c>
-      <c r="N15" s="168">
+      <c r="N15" s="157">
         <f>N14-O14</f>
         <v>0</v>
       </c>
-      <c r="O15" s="169" t="str">
+      <c r="O15" s="158" t="str">
         <f>IF(TEXT(N14-O14,"+0,0; -0,0")="+0,0","0,0",TEXT(N14-O14,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
-      <c r="P15" s="91"/>
-      <c r="Q15" s="91"/>
-      <c r="R15" s="111"/>
-      <c r="S15" s="91"/>
-      <c r="T15" s="106"/>
-      <c r="U15" s="106"/>
-      <c r="V15" s="106"/>
-      <c r="W15" s="106"/>
-      <c r="X15" s="106"/>
-      <c r="Y15" s="106"/>
-      <c r="Z15" s="106"/>
-      <c r="AA15" s="106"/>
-      <c r="AB15" s="106"/>
-      <c r="AC15" s="106"/>
-      <c r="AD15" s="106"/>
-      <c r="AE15" s="106"/>
-      <c r="AF15" s="106"/>
-      <c r="AG15" s="106"/>
-      <c r="AH15" s="106"/>
-      <c r="AI15" s="105"/>
-      <c r="AJ15" s="105"/>
-      <c r="AK15" s="105"/>
-      <c r="AL15" s="105"/>
-      <c r="AM15" s="105"/>
-      <c r="AN15" s="105"/>
-      <c r="AO15" s="105"/>
-      <c r="AP15" s="105"/>
-      <c r="AQ15" s="105"/>
-      <c r="AR15" s="105"/>
-      <c r="AS15" s="105"/>
-      <c r="AT15" s="105"/>
-      <c r="AU15" s="105"/>
-      <c r="AV15" s="105"/>
-      <c r="AW15" s="105"/>
-      <c r="AX15" s="105"/>
-      <c r="AY15" s="105"/>
-      <c r="AZ15" s="105"/>
-      <c r="BA15" s="105"/>
-      <c r="BB15" s="105"/>
-      <c r="BC15" s="105"/>
-      <c r="BD15" s="105"/>
-      <c r="BE15" s="105"/>
-      <c r="BF15" s="105"/>
-      <c r="BG15" s="105"/>
-      <c r="BH15" s="105"/>
-      <c r="BI15" s="105"/>
-      <c r="BJ15" s="105"/>
-      <c r="BK15" s="105"/>
-      <c r="BL15" s="105"/>
-      <c r="BM15" s="105"/>
-      <c r="BN15" s="105"/>
-      <c r="BO15" s="105"/>
-      <c r="BP15" s="105"/>
-      <c r="BQ15" s="105"/>
-      <c r="BR15" s="105"/>
-      <c r="BS15" s="105"/>
-      <c r="BT15" s="105"/>
-      <c r="BU15" s="105"/>
-      <c r="BV15" s="105"/>
-      <c r="BW15" s="105"/>
-      <c r="BX15" s="105"/>
-      <c r="BY15" s="105"/>
-      <c r="BZ15" s="105"/>
-      <c r="CA15" s="105"/>
-      <c r="CB15" s="105"/>
-      <c r="CC15" s="105"/>
-      <c r="CD15" s="105"/>
-      <c r="CE15" s="105"/>
-      <c r="CF15" s="105"/>
-      <c r="CG15" s="105"/>
-      <c r="CH15" s="105"/>
-      <c r="CI15" s="105"/>
-      <c r="CJ15" s="105"/>
-      <c r="CK15" s="105"/>
-      <c r="CL15" s="105"/>
-      <c r="CM15" s="105"/>
-      <c r="CN15" s="105"/>
-      <c r="CO15" s="105"/>
-      <c r="CP15" s="105"/>
-      <c r="CQ15" s="105"/>
-      <c r="CR15" s="105"/>
-      <c r="CS15" s="105"/>
-      <c r="CT15" s="105"/>
-      <c r="CU15" s="105"/>
-      <c r="CV15" s="105"/>
-      <c r="CW15" s="105"/>
-      <c r="CX15" s="105"/>
-      <c r="CY15" s="105"/>
-      <c r="CZ15" s="105"/>
-      <c r="DA15" s="105"/>
-      <c r="DB15" s="105"/>
-      <c r="DC15" s="105"/>
-      <c r="DD15" s="105"/>
-      <c r="DE15" s="105"/>
-      <c r="DF15" s="105"/>
-      <c r="DG15" s="105"/>
-      <c r="DH15" s="105"/>
-      <c r="DI15" s="105"/>
-      <c r="DJ15" s="105"/>
-      <c r="DK15" s="105"/>
-      <c r="DL15" s="105"/>
-      <c r="DM15" s="105"/>
-      <c r="DN15" s="105"/>
-      <c r="DO15" s="105"/>
-      <c r="DP15" s="105"/>
-      <c r="DQ15" s="105"/>
-      <c r="DR15" s="105"/>
-      <c r="DS15" s="105"/>
-      <c r="DT15" s="105"/>
-      <c r="DU15" s="105"/>
-      <c r="DV15" s="105"/>
-      <c r="DW15" s="105"/>
-      <c r="DX15" s="105"/>
-      <c r="DY15" s="105"/>
-      <c r="DZ15" s="105"/>
-      <c r="EA15" s="105"/>
-      <c r="EB15" s="105"/>
-      <c r="EC15" s="105"/>
-      <c r="ED15" s="105"/>
-      <c r="EE15" s="105"/>
-      <c r="EF15" s="105"/>
-      <c r="EG15" s="105"/>
-      <c r="EH15" s="104"/>
-      <c r="EI15" s="104"/>
-      <c r="EJ15" s="104"/>
-      <c r="EK15" s="104"/>
-      <c r="EL15" s="104"/>
-      <c r="EM15" s="104"/>
-      <c r="EN15" s="104"/>
-      <c r="EO15" s="104"/>
-      <c r="EP15" s="104"/>
-      <c r="EQ15" s="104"/>
-      <c r="ER15" s="104"/>
-      <c r="ES15" s="104"/>
-      <c r="ET15" s="104"/>
-      <c r="EU15" s="104"/>
-      <c r="EV15" s="104"/>
-      <c r="EW15" s="104"/>
-      <c r="EX15" s="104"/>
-      <c r="EY15" s="104"/>
-      <c r="EZ15" s="104"/>
-      <c r="FA15" s="104"/>
-      <c r="FB15" s="104"/>
-      <c r="FC15" s="104"/>
-      <c r="FD15" s="104"/>
-      <c r="FE15" s="104"/>
-      <c r="FF15" s="104"/>
-      <c r="FG15" s="104"/>
-      <c r="FH15" s="104"/>
-      <c r="FI15" s="104"/>
-      <c r="FJ15" s="104"/>
-      <c r="FK15" s="104"/>
-      <c r="FL15" s="104"/>
-      <c r="FM15" s="104"/>
-      <c r="FN15" s="104"/>
-      <c r="FO15" s="104"/>
-      <c r="FP15" s="104"/>
-      <c r="FQ15" s="104"/>
-      <c r="FR15" s="104"/>
-      <c r="FS15" s="104"/>
-      <c r="FT15" s="104"/>
-      <c r="FU15" s="104"/>
-      <c r="FV15" s="104"/>
-      <c r="FW15" s="104"/>
-      <c r="FX15" s="104"/>
-      <c r="FY15" s="104"/>
-      <c r="FZ15" s="104"/>
-      <c r="GA15" s="104"/>
-      <c r="GB15" s="104"/>
-      <c r="GC15" s="104"/>
-      <c r="GD15" s="104"/>
-      <c r="GE15" s="104"/>
-      <c r="GF15" s="104"/>
-      <c r="GG15" s="104"/>
-      <c r="GH15" s="104"/>
-      <c r="GI15" s="104"/>
-      <c r="GJ15" s="104"/>
-      <c r="GK15" s="104"/>
-      <c r="GL15" s="104"/>
-      <c r="GM15" s="104"/>
-      <c r="GN15" s="104"/>
-      <c r="GO15" s="104"/>
-      <c r="GP15" s="104"/>
-      <c r="GQ15" s="104"/>
-      <c r="GR15" s="104"/>
-      <c r="GS15" s="104"/>
-      <c r="GT15" s="104"/>
-      <c r="GU15" s="104"/>
-      <c r="GV15" s="104"/>
-    </row>
-    <row r="16" spans="1:204" s="107" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="167" t="s">
+      <c r="P15" s="79"/>
+      <c r="Q15" s="79"/>
+      <c r="R15" s="99"/>
+      <c r="S15" s="79"/>
+      <c r="T15" s="94"/>
+      <c r="U15" s="94"/>
+      <c r="V15" s="94"/>
+      <c r="W15" s="94"/>
+      <c r="X15" s="94"/>
+      <c r="Y15" s="94"/>
+      <c r="Z15" s="94"/>
+      <c r="AA15" s="94"/>
+      <c r="AB15" s="94"/>
+      <c r="AC15" s="94"/>
+      <c r="AD15" s="94"/>
+      <c r="AE15" s="94"/>
+      <c r="AF15" s="94"/>
+      <c r="AG15" s="94"/>
+      <c r="AH15" s="94"/>
+      <c r="AI15" s="93"/>
+      <c r="AJ15" s="93"/>
+      <c r="AK15" s="93"/>
+      <c r="AL15" s="93"/>
+      <c r="AM15" s="93"/>
+      <c r="AN15" s="93"/>
+      <c r="AO15" s="93"/>
+      <c r="AP15" s="93"/>
+      <c r="AQ15" s="93"/>
+      <c r="AR15" s="93"/>
+      <c r="AS15" s="93"/>
+      <c r="AT15" s="93"/>
+      <c r="AU15" s="93"/>
+      <c r="AV15" s="93"/>
+      <c r="AW15" s="93"/>
+      <c r="AX15" s="93"/>
+      <c r="AY15" s="93"/>
+      <c r="AZ15" s="93"/>
+      <c r="BA15" s="93"/>
+      <c r="BB15" s="93"/>
+      <c r="BC15" s="93"/>
+      <c r="BD15" s="93"/>
+      <c r="BE15" s="93"/>
+      <c r="BF15" s="93"/>
+      <c r="BG15" s="93"/>
+      <c r="BH15" s="93"/>
+      <c r="BI15" s="93"/>
+      <c r="BJ15" s="93"/>
+      <c r="BK15" s="93"/>
+      <c r="BL15" s="93"/>
+      <c r="BM15" s="93"/>
+      <c r="BN15" s="93"/>
+      <c r="BO15" s="93"/>
+      <c r="BP15" s="93"/>
+      <c r="BQ15" s="93"/>
+      <c r="BR15" s="93"/>
+      <c r="BS15" s="93"/>
+      <c r="BT15" s="93"/>
+      <c r="BU15" s="93"/>
+      <c r="BV15" s="93"/>
+      <c r="BW15" s="93"/>
+      <c r="BX15" s="93"/>
+      <c r="BY15" s="93"/>
+      <c r="BZ15" s="93"/>
+      <c r="CA15" s="93"/>
+      <c r="CB15" s="93"/>
+      <c r="CC15" s="93"/>
+      <c r="CD15" s="93"/>
+      <c r="CE15" s="93"/>
+      <c r="CF15" s="93"/>
+      <c r="CG15" s="93"/>
+      <c r="CH15" s="93"/>
+      <c r="CI15" s="93"/>
+      <c r="CJ15" s="93"/>
+      <c r="CK15" s="93"/>
+      <c r="CL15" s="93"/>
+      <c r="CM15" s="93"/>
+      <c r="CN15" s="93"/>
+      <c r="CO15" s="93"/>
+      <c r="CP15" s="93"/>
+      <c r="CQ15" s="93"/>
+      <c r="CR15" s="93"/>
+      <c r="CS15" s="93"/>
+      <c r="CT15" s="93"/>
+      <c r="CU15" s="93"/>
+      <c r="CV15" s="93"/>
+      <c r="CW15" s="93"/>
+      <c r="CX15" s="93"/>
+      <c r="CY15" s="93"/>
+      <c r="CZ15" s="93"/>
+      <c r="DA15" s="93"/>
+      <c r="DB15" s="93"/>
+      <c r="DC15" s="93"/>
+      <c r="DD15" s="93"/>
+      <c r="DE15" s="93"/>
+      <c r="DF15" s="93"/>
+      <c r="DG15" s="93"/>
+      <c r="DH15" s="93"/>
+      <c r="DI15" s="93"/>
+      <c r="DJ15" s="93"/>
+      <c r="DK15" s="93"/>
+      <c r="DL15" s="93"/>
+      <c r="DM15" s="93"/>
+      <c r="DN15" s="93"/>
+      <c r="DO15" s="93"/>
+      <c r="DP15" s="93"/>
+      <c r="DQ15" s="93"/>
+      <c r="DR15" s="93"/>
+      <c r="DS15" s="93"/>
+      <c r="DT15" s="93"/>
+      <c r="DU15" s="93"/>
+      <c r="DV15" s="93"/>
+      <c r="DW15" s="93"/>
+      <c r="DX15" s="93"/>
+      <c r="DY15" s="93"/>
+      <c r="DZ15" s="93"/>
+      <c r="EA15" s="93"/>
+      <c r="EB15" s="93"/>
+      <c r="EC15" s="93"/>
+      <c r="ED15" s="93"/>
+      <c r="EE15" s="93"/>
+      <c r="EF15" s="93"/>
+      <c r="EG15" s="93"/>
+      <c r="EH15" s="92"/>
+      <c r="EI15" s="92"/>
+      <c r="EJ15" s="92"/>
+      <c r="EK15" s="92"/>
+      <c r="EL15" s="92"/>
+      <c r="EM15" s="92"/>
+      <c r="EN15" s="92"/>
+      <c r="EO15" s="92"/>
+      <c r="EP15" s="92"/>
+      <c r="EQ15" s="92"/>
+      <c r="ER15" s="92"/>
+      <c r="ES15" s="92"/>
+      <c r="ET15" s="92"/>
+      <c r="EU15" s="92"/>
+      <c r="EV15" s="92"/>
+      <c r="EW15" s="92"/>
+      <c r="EX15" s="92"/>
+      <c r="EY15" s="92"/>
+      <c r="EZ15" s="92"/>
+      <c r="FA15" s="92"/>
+      <c r="FB15" s="92"/>
+      <c r="FC15" s="92"/>
+      <c r="FD15" s="92"/>
+      <c r="FE15" s="92"/>
+      <c r="FF15" s="92"/>
+      <c r="FG15" s="92"/>
+      <c r="FH15" s="92"/>
+      <c r="FI15" s="92"/>
+      <c r="FJ15" s="92"/>
+      <c r="FK15" s="92"/>
+      <c r="FL15" s="92"/>
+      <c r="FM15" s="92"/>
+      <c r="FN15" s="92"/>
+      <c r="FO15" s="92"/>
+      <c r="FP15" s="92"/>
+      <c r="FQ15" s="92"/>
+      <c r="FR15" s="92"/>
+      <c r="FS15" s="92"/>
+      <c r="FT15" s="92"/>
+      <c r="FU15" s="92"/>
+      <c r="FV15" s="92"/>
+      <c r="FW15" s="92"/>
+      <c r="FX15" s="92"/>
+      <c r="FY15" s="92"/>
+      <c r="FZ15" s="92"/>
+      <c r="GA15" s="92"/>
+      <c r="GB15" s="92"/>
+      <c r="GC15" s="92"/>
+      <c r="GD15" s="92"/>
+      <c r="GE15" s="92"/>
+      <c r="GF15" s="92"/>
+      <c r="GG15" s="92"/>
+      <c r="GH15" s="92"/>
+      <c r="GI15" s="92"/>
+      <c r="GJ15" s="92"/>
+      <c r="GK15" s="92"/>
+      <c r="GL15" s="92"/>
+      <c r="GM15" s="92"/>
+      <c r="GN15" s="92"/>
+      <c r="GO15" s="92"/>
+      <c r="GP15" s="92"/>
+      <c r="GQ15" s="92"/>
+      <c r="GR15" s="92"/>
+      <c r="GS15" s="92"/>
+      <c r="GT15" s="92"/>
+      <c r="GU15" s="92"/>
+      <c r="GV15" s="92"/>
+    </row>
+    <row r="16" spans="1:204" s="95" customFormat="1" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="166" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="101">
+      <c r="B16" s="89">
         <v>1</v>
       </c>
-      <c r="C16" s="101">
+      <c r="C16" s="89">
         <v>1</v>
       </c>
-      <c r="D16" s="143">
+      <c r="D16" s="131">
         <v>1</v>
       </c>
-      <c r="E16" s="144">
+      <c r="E16" s="132">
         <v>1</v>
       </c>
-      <c r="F16" s="72">
+      <c r="F16" s="67">
         <v>1</v>
       </c>
-      <c r="G16" s="103">
+      <c r="G16" s="91">
         <v>1</v>
       </c>
-      <c r="H16" s="102">
+      <c r="H16" s="90">
         <v>1</v>
       </c>
-      <c r="I16" s="113">
+      <c r="I16" s="101">
         <v>1</v>
       </c>
-      <c r="J16" s="103">
+      <c r="J16" s="91">
         <v>1</v>
       </c>
-      <c r="K16" s="102">
+      <c r="K16" s="90">
         <v>1</v>
       </c>
-      <c r="L16" s="101">
+      <c r="L16" s="89">
         <v>1</v>
       </c>
-      <c r="M16" s="140">
+      <c r="M16" s="128">
         <v>1</v>
       </c>
-      <c r="N16" s="72">
+      <c r="N16" s="67">
         <v>1</v>
       </c>
-      <c r="O16" s="71">
+      <c r="O16" s="66">
         <v>1</v>
       </c>
-      <c r="P16" s="112"/>
-      <c r="Q16" s="112"/>
-      <c r="R16" s="111"/>
-      <c r="S16" s="99"/>
-      <c r="T16" s="110"/>
-      <c r="U16" s="110"/>
-      <c r="V16" s="110"/>
-      <c r="W16" s="110"/>
-      <c r="X16" s="110"/>
-      <c r="Y16" s="110"/>
-      <c r="Z16" s="110"/>
-      <c r="AA16" s="110"/>
-      <c r="AB16" s="110"/>
-      <c r="AC16" s="110"/>
-      <c r="AD16" s="110"/>
-      <c r="AE16" s="108"/>
-      <c r="AF16" s="110"/>
-      <c r="AG16" s="110"/>
-      <c r="AH16" s="110"/>
-      <c r="AI16" s="110"/>
-      <c r="AJ16" s="110"/>
-      <c r="AK16" s="110"/>
-      <c r="AL16" s="110"/>
-      <c r="AM16" s="110"/>
-      <c r="AN16" s="110"/>
-      <c r="AO16" s="110"/>
-      <c r="AP16" s="110"/>
-      <c r="AQ16" s="110"/>
-      <c r="AR16" s="110"/>
-      <c r="AS16" s="110"/>
-      <c r="AT16" s="108"/>
-      <c r="AU16" s="108"/>
-      <c r="AV16" s="108"/>
-      <c r="AW16" s="108"/>
-      <c r="AX16" s="108"/>
-      <c r="AY16" s="108"/>
-      <c r="AZ16" s="108"/>
-      <c r="BA16" s="108"/>
-      <c r="BB16" s="108"/>
-      <c r="BC16" s="108"/>
-      <c r="BD16" s="108"/>
-      <c r="BE16" s="108"/>
-      <c r="BF16" s="109"/>
-      <c r="BG16" s="109"/>
-      <c r="BH16" s="109"/>
-      <c r="BI16" s="109"/>
-      <c r="BJ16" s="109"/>
-      <c r="BK16" s="109"/>
-      <c r="BL16" s="109"/>
-      <c r="BM16" s="109"/>
-      <c r="BN16" s="109"/>
-      <c r="BO16" s="109"/>
-      <c r="BP16" s="109"/>
-      <c r="BQ16" s="109"/>
-      <c r="BR16" s="109"/>
-      <c r="BS16" s="109"/>
-      <c r="BT16" s="109"/>
-      <c r="BU16" s="109"/>
-      <c r="BV16" s="109"/>
-      <c r="BW16" s="109"/>
-      <c r="BX16" s="109"/>
-      <c r="BY16" s="109"/>
-      <c r="BZ16" s="109"/>
-      <c r="CA16" s="109"/>
-      <c r="CB16" s="109"/>
-      <c r="CC16" s="109"/>
-      <c r="CD16" s="109"/>
-      <c r="CE16" s="109"/>
-      <c r="CF16" s="109"/>
-      <c r="CG16" s="109"/>
-      <c r="CH16" s="109"/>
-      <c r="CI16" s="109"/>
-      <c r="CJ16" s="109"/>
-      <c r="CK16" s="109"/>
-      <c r="CL16" s="109"/>
-      <c r="CM16" s="109"/>
-      <c r="CN16" s="109"/>
-      <c r="CO16" s="109"/>
-      <c r="CP16" s="109"/>
-      <c r="CQ16" s="109"/>
-      <c r="CR16" s="109"/>
-      <c r="CS16" s="109"/>
-      <c r="CT16" s="109"/>
-      <c r="CU16" s="109"/>
-      <c r="CV16" s="109"/>
-      <c r="CW16" s="109"/>
-      <c r="CX16" s="109"/>
-      <c r="CY16" s="109"/>
-      <c r="CZ16" s="109"/>
-      <c r="DA16" s="109"/>
-      <c r="DB16" s="109"/>
-      <c r="DC16" s="109"/>
-      <c r="DD16" s="109"/>
-      <c r="DE16" s="109"/>
-      <c r="DF16" s="109"/>
-      <c r="DG16" s="109"/>
-      <c r="DH16" s="109"/>
-      <c r="DI16" s="109"/>
-      <c r="DJ16" s="109"/>
-      <c r="DK16" s="109"/>
-      <c r="DL16" s="109"/>
-      <c r="DM16" s="109"/>
-      <c r="DN16" s="109"/>
-      <c r="DO16" s="109"/>
-      <c r="DP16" s="109"/>
-      <c r="DQ16" s="109"/>
-      <c r="DR16" s="109"/>
-      <c r="DS16" s="109"/>
-      <c r="DT16" s="109"/>
-      <c r="DU16" s="109"/>
-      <c r="DV16" s="109"/>
-      <c r="DW16" s="109"/>
-      <c r="DX16" s="109"/>
-      <c r="DY16" s="109"/>
-      <c r="DZ16" s="109"/>
-      <c r="EA16" s="109"/>
-      <c r="EB16" s="109"/>
-      <c r="EC16" s="109"/>
-      <c r="ED16" s="109"/>
-      <c r="EE16" s="109"/>
-      <c r="EF16" s="109"/>
-      <c r="EG16" s="109"/>
-      <c r="EH16" s="108"/>
-      <c r="EI16" s="108"/>
-      <c r="EJ16" s="108"/>
-      <c r="EK16" s="108"/>
-      <c r="EL16" s="108"/>
-      <c r="EM16" s="108"/>
-      <c r="EN16" s="108"/>
-      <c r="EO16" s="108"/>
-      <c r="EP16" s="108"/>
-      <c r="EQ16" s="108"/>
-      <c r="ER16" s="108"/>
-      <c r="ES16" s="108"/>
-      <c r="ET16" s="108"/>
-      <c r="EU16" s="108"/>
-      <c r="EV16" s="108"/>
-      <c r="EW16" s="108"/>
-      <c r="EX16" s="108"/>
-      <c r="EY16" s="108"/>
-      <c r="EZ16" s="108"/>
-      <c r="FA16" s="108"/>
-      <c r="FB16" s="108"/>
-      <c r="FC16" s="108"/>
-      <c r="FD16" s="108"/>
-      <c r="FE16" s="108"/>
-      <c r="FF16" s="108"/>
-      <c r="FG16" s="108"/>
-      <c r="FH16" s="108"/>
-      <c r="FI16" s="108"/>
-      <c r="FJ16" s="108"/>
-      <c r="FK16" s="108"/>
-      <c r="FL16" s="108"/>
-      <c r="FM16" s="108"/>
-      <c r="FN16" s="108"/>
-      <c r="FO16" s="108"/>
-      <c r="FP16" s="108"/>
-      <c r="FQ16" s="108"/>
-      <c r="FR16" s="108"/>
-      <c r="FS16" s="108"/>
-      <c r="FT16" s="108"/>
-      <c r="FU16" s="108"/>
-      <c r="FV16" s="108"/>
-      <c r="FW16" s="108"/>
-      <c r="FX16" s="108"/>
-      <c r="FY16" s="108"/>
-      <c r="FZ16" s="108"/>
-      <c r="GA16" s="108"/>
-      <c r="GB16" s="108"/>
-      <c r="GC16" s="108"/>
-      <c r="GD16" s="108"/>
-      <c r="GE16" s="108"/>
-      <c r="GF16" s="108"/>
-      <c r="GG16" s="108"/>
-      <c r="GH16" s="108"/>
-      <c r="GI16" s="108"/>
-      <c r="GJ16" s="108"/>
-      <c r="GK16" s="108"/>
-      <c r="GL16" s="108"/>
-      <c r="GM16" s="108"/>
-      <c r="GN16" s="108"/>
-      <c r="GO16" s="108"/>
-      <c r="GP16" s="108"/>
-      <c r="GQ16" s="108"/>
-      <c r="GR16" s="108"/>
-      <c r="GS16" s="108"/>
-      <c r="GT16" s="108"/>
-      <c r="GU16" s="108"/>
-      <c r="GV16" s="108"/>
-    </row>
-    <row r="17" spans="1:211" s="87" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="167"/>
-      <c r="B17" s="145" t="s">
+      <c r="P16" s="100"/>
+      <c r="Q16" s="100"/>
+      <c r="R16" s="99"/>
+      <c r="S16" s="87"/>
+      <c r="T16" s="98"/>
+      <c r="U16" s="98"/>
+      <c r="V16" s="98"/>
+      <c r="W16" s="98"/>
+      <c r="X16" s="98"/>
+      <c r="Y16" s="98"/>
+      <c r="Z16" s="98"/>
+      <c r="AA16" s="98"/>
+      <c r="AB16" s="98"/>
+      <c r="AC16" s="98"/>
+      <c r="AD16" s="98"/>
+      <c r="AE16" s="96"/>
+      <c r="AF16" s="98"/>
+      <c r="AG16" s="98"/>
+      <c r="AH16" s="98"/>
+      <c r="AI16" s="98"/>
+      <c r="AJ16" s="98"/>
+      <c r="AK16" s="98"/>
+      <c r="AL16" s="98"/>
+      <c r="AM16" s="98"/>
+      <c r="AN16" s="98"/>
+      <c r="AO16" s="98"/>
+      <c r="AP16" s="98"/>
+      <c r="AQ16" s="98"/>
+      <c r="AR16" s="98"/>
+      <c r="AS16" s="98"/>
+      <c r="AT16" s="96"/>
+      <c r="AU16" s="96"/>
+      <c r="AV16" s="96"/>
+      <c r="AW16" s="96"/>
+      <c r="AX16" s="96"/>
+      <c r="AY16" s="96"/>
+      <c r="AZ16" s="96"/>
+      <c r="BA16" s="96"/>
+      <c r="BB16" s="96"/>
+      <c r="BC16" s="96"/>
+      <c r="BD16" s="96"/>
+      <c r="BE16" s="96"/>
+      <c r="BF16" s="97"/>
+      <c r="BG16" s="97"/>
+      <c r="BH16" s="97"/>
+      <c r="BI16" s="97"/>
+      <c r="BJ16" s="97"/>
+      <c r="BK16" s="97"/>
+      <c r="BL16" s="97"/>
+      <c r="BM16" s="97"/>
+      <c r="BN16" s="97"/>
+      <c r="BO16" s="97"/>
+      <c r="BP16" s="97"/>
+      <c r="BQ16" s="97"/>
+      <c r="BR16" s="97"/>
+      <c r="BS16" s="97"/>
+      <c r="BT16" s="97"/>
+      <c r="BU16" s="97"/>
+      <c r="BV16" s="97"/>
+      <c r="BW16" s="97"/>
+      <c r="BX16" s="97"/>
+      <c r="BY16" s="97"/>
+      <c r="BZ16" s="97"/>
+      <c r="CA16" s="97"/>
+      <c r="CB16" s="97"/>
+      <c r="CC16" s="97"/>
+      <c r="CD16" s="97"/>
+      <c r="CE16" s="97"/>
+      <c r="CF16" s="97"/>
+      <c r="CG16" s="97"/>
+      <c r="CH16" s="97"/>
+      <c r="CI16" s="97"/>
+      <c r="CJ16" s="97"/>
+      <c r="CK16" s="97"/>
+      <c r="CL16" s="97"/>
+      <c r="CM16" s="97"/>
+      <c r="CN16" s="97"/>
+      <c r="CO16" s="97"/>
+      <c r="CP16" s="97"/>
+      <c r="CQ16" s="97"/>
+      <c r="CR16" s="97"/>
+      <c r="CS16" s="97"/>
+      <c r="CT16" s="97"/>
+      <c r="CU16" s="97"/>
+      <c r="CV16" s="97"/>
+      <c r="CW16" s="97"/>
+      <c r="CX16" s="97"/>
+      <c r="CY16" s="97"/>
+      <c r="CZ16" s="97"/>
+      <c r="DA16" s="97"/>
+      <c r="DB16" s="97"/>
+      <c r="DC16" s="97"/>
+      <c r="DD16" s="97"/>
+      <c r="DE16" s="97"/>
+      <c r="DF16" s="97"/>
+      <c r="DG16" s="97"/>
+      <c r="DH16" s="97"/>
+      <c r="DI16" s="97"/>
+      <c r="DJ16" s="97"/>
+      <c r="DK16" s="97"/>
+      <c r="DL16" s="97"/>
+      <c r="DM16" s="97"/>
+      <c r="DN16" s="97"/>
+      <c r="DO16" s="97"/>
+      <c r="DP16" s="97"/>
+      <c r="DQ16" s="97"/>
+      <c r="DR16" s="97"/>
+      <c r="DS16" s="97"/>
+      <c r="DT16" s="97"/>
+      <c r="DU16" s="97"/>
+      <c r="DV16" s="97"/>
+      <c r="DW16" s="97"/>
+      <c r="DX16" s="97"/>
+      <c r="DY16" s="97"/>
+      <c r="DZ16" s="97"/>
+      <c r="EA16" s="97"/>
+      <c r="EB16" s="97"/>
+      <c r="EC16" s="97"/>
+      <c r="ED16" s="97"/>
+      <c r="EE16" s="97"/>
+      <c r="EF16" s="97"/>
+      <c r="EG16" s="97"/>
+      <c r="EH16" s="96"/>
+      <c r="EI16" s="96"/>
+      <c r="EJ16" s="96"/>
+      <c r="EK16" s="96"/>
+      <c r="EL16" s="96"/>
+      <c r="EM16" s="96"/>
+      <c r="EN16" s="96"/>
+      <c r="EO16" s="96"/>
+      <c r="EP16" s="96"/>
+      <c r="EQ16" s="96"/>
+      <c r="ER16" s="96"/>
+      <c r="ES16" s="96"/>
+      <c r="ET16" s="96"/>
+      <c r="EU16" s="96"/>
+      <c r="EV16" s="96"/>
+      <c r="EW16" s="96"/>
+      <c r="EX16" s="96"/>
+      <c r="EY16" s="96"/>
+      <c r="EZ16" s="96"/>
+      <c r="FA16" s="96"/>
+      <c r="FB16" s="96"/>
+      <c r="FC16" s="96"/>
+      <c r="FD16" s="96"/>
+      <c r="FE16" s="96"/>
+      <c r="FF16" s="96"/>
+      <c r="FG16" s="96"/>
+      <c r="FH16" s="96"/>
+      <c r="FI16" s="96"/>
+      <c r="FJ16" s="96"/>
+      <c r="FK16" s="96"/>
+      <c r="FL16" s="96"/>
+      <c r="FM16" s="96"/>
+      <c r="FN16" s="96"/>
+      <c r="FO16" s="96"/>
+      <c r="FP16" s="96"/>
+      <c r="FQ16" s="96"/>
+      <c r="FR16" s="96"/>
+      <c r="FS16" s="96"/>
+      <c r="FT16" s="96"/>
+      <c r="FU16" s="96"/>
+      <c r="FV16" s="96"/>
+      <c r="FW16" s="96"/>
+      <c r="FX16" s="96"/>
+      <c r="FY16" s="96"/>
+      <c r="FZ16" s="96"/>
+      <c r="GA16" s="96"/>
+      <c r="GB16" s="96"/>
+      <c r="GC16" s="96"/>
+      <c r="GD16" s="96"/>
+      <c r="GE16" s="96"/>
+      <c r="GF16" s="96"/>
+      <c r="GG16" s="96"/>
+      <c r="GH16" s="96"/>
+      <c r="GI16" s="96"/>
+      <c r="GJ16" s="96"/>
+      <c r="GK16" s="96"/>
+      <c r="GL16" s="96"/>
+      <c r="GM16" s="96"/>
+      <c r="GN16" s="96"/>
+      <c r="GO16" s="96"/>
+      <c r="GP16" s="96"/>
+      <c r="GQ16" s="96"/>
+      <c r="GR16" s="96"/>
+      <c r="GS16" s="96"/>
+      <c r="GT16" s="96"/>
+      <c r="GU16" s="96"/>
+      <c r="GV16" s="96"/>
+    </row>
+    <row r="17" spans="1:211" s="75" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="166"/>
+      <c r="B17" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="145" t="s">
+      <c r="C17" s="133" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="145">
+      <c r="D17" s="133">
         <f>C16-D16</f>
         <v>0</v>
       </c>
-      <c r="E17" s="145">
+      <c r="E17" s="133">
         <f>C16-E16</f>
         <v>0</v>
       </c>
-      <c r="F17" s="146" t="s">
+      <c r="F17" s="134" t="s">
         <v>31</v>
       </c>
-      <c r="G17" s="146">
+      <c r="G17" s="134">
         <f>F16-G16</f>
         <v>0</v>
       </c>
-      <c r="H17" s="146">
+      <c r="H17" s="134">
         <f>F16-H16</f>
         <v>0</v>
       </c>
-      <c r="I17" s="146" t="s">
+      <c r="I17" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="J17" s="146">
+      <c r="J17" s="134">
         <f>I16-J16</f>
         <v>0</v>
       </c>
-      <c r="K17" s="146">
+      <c r="K17" s="134">
         <f>I16-K16</f>
         <v>0</v>
       </c>
-      <c r="L17" s="145">
+      <c r="L17" s="133">
         <f>L16-M16</f>
         <v>0</v>
       </c>
-      <c r="M17" s="94">
+      <c r="M17" s="82">
         <f>IFERROR(L16/M16, 0)</f>
         <v>1</v>
       </c>
-      <c r="N17" s="168">
+      <c r="N17" s="157">
         <f>N16-O16</f>
         <v>0</v>
       </c>
-      <c r="O17" s="169" t="str">
+      <c r="O17" s="158" t="str">
         <f>IF(TEXT(N16-O16,"+0,0; -0,0")="+0,0","0,0",TEXT(N16-O16,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
-      <c r="P17" s="91"/>
-      <c r="Q17" s="91"/>
-      <c r="R17" s="91"/>
-      <c r="S17" s="91"/>
-      <c r="T17" s="106"/>
-      <c r="U17" s="106"/>
-      <c r="V17" s="106"/>
-      <c r="W17" s="106"/>
-      <c r="X17" s="106"/>
-      <c r="Y17" s="106"/>
-      <c r="Z17" s="106"/>
-      <c r="AA17" s="106"/>
-      <c r="AB17" s="106"/>
-      <c r="AC17" s="106"/>
-      <c r="AD17" s="106"/>
-      <c r="AE17" s="106"/>
-      <c r="AF17" s="106"/>
-      <c r="AG17" s="106"/>
-      <c r="AH17" s="106"/>
-      <c r="AI17" s="105"/>
-      <c r="AJ17" s="105"/>
-      <c r="AK17" s="105"/>
-      <c r="AL17" s="105"/>
-      <c r="AM17" s="105"/>
-      <c r="AN17" s="105"/>
-      <c r="AO17" s="105"/>
-      <c r="AP17" s="105"/>
-      <c r="AQ17" s="105"/>
-      <c r="AR17" s="105"/>
-      <c r="AS17" s="105"/>
-      <c r="AT17" s="105"/>
-      <c r="AU17" s="105"/>
-      <c r="AV17" s="105"/>
-      <c r="AW17" s="105"/>
-      <c r="AX17" s="105"/>
-      <c r="AY17" s="105"/>
-      <c r="AZ17" s="105"/>
-      <c r="BA17" s="105"/>
-      <c r="BB17" s="105"/>
-      <c r="BC17" s="105"/>
-      <c r="BD17" s="105"/>
-      <c r="BE17" s="105"/>
-      <c r="BF17" s="105"/>
-      <c r="BG17" s="105"/>
-      <c r="BH17" s="105"/>
-      <c r="BI17" s="105"/>
-      <c r="BJ17" s="105"/>
-      <c r="BK17" s="105"/>
-      <c r="BL17" s="105"/>
-      <c r="BM17" s="105"/>
-      <c r="BN17" s="105"/>
-      <c r="BO17" s="105"/>
-      <c r="BP17" s="105"/>
-      <c r="BQ17" s="105"/>
-      <c r="BR17" s="105"/>
-      <c r="BS17" s="105"/>
-      <c r="BT17" s="105"/>
-      <c r="BU17" s="105"/>
-      <c r="BV17" s="105"/>
-      <c r="BW17" s="105"/>
-      <c r="BX17" s="105"/>
-      <c r="BY17" s="105"/>
-      <c r="BZ17" s="105"/>
-      <c r="CA17" s="105"/>
-      <c r="CB17" s="105"/>
-      <c r="CC17" s="105"/>
-      <c r="CD17" s="105"/>
-      <c r="CE17" s="105"/>
-      <c r="CF17" s="105"/>
-      <c r="CG17" s="105"/>
-      <c r="CH17" s="105"/>
-      <c r="CI17" s="105"/>
-      <c r="CJ17" s="105"/>
-      <c r="CK17" s="105"/>
-      <c r="CL17" s="105"/>
-      <c r="CM17" s="105"/>
-      <c r="CN17" s="105"/>
-      <c r="CO17" s="105"/>
-      <c r="CP17" s="105"/>
-      <c r="CQ17" s="105"/>
-      <c r="CR17" s="105"/>
-      <c r="CS17" s="105"/>
-      <c r="CT17" s="105"/>
-      <c r="CU17" s="105"/>
-      <c r="CV17" s="105"/>
-      <c r="CW17" s="105"/>
-      <c r="CX17" s="105"/>
-      <c r="CY17" s="105"/>
-      <c r="CZ17" s="105"/>
-      <c r="DA17" s="105"/>
-      <c r="DB17" s="105"/>
-      <c r="DC17" s="105"/>
-      <c r="DD17" s="105"/>
-      <c r="DE17" s="105"/>
-      <c r="DF17" s="105"/>
-      <c r="DG17" s="105"/>
-      <c r="DH17" s="105"/>
-      <c r="DI17" s="105"/>
-      <c r="DJ17" s="105"/>
-      <c r="DK17" s="105"/>
-      <c r="DL17" s="105"/>
-      <c r="DM17" s="105"/>
-      <c r="DN17" s="105"/>
-      <c r="DO17" s="105"/>
-      <c r="DP17" s="105"/>
-      <c r="DQ17" s="105"/>
-      <c r="DR17" s="105"/>
-      <c r="DS17" s="105"/>
-      <c r="DT17" s="105"/>
-      <c r="DU17" s="105"/>
-      <c r="DV17" s="105"/>
-      <c r="DW17" s="105"/>
-      <c r="DX17" s="105"/>
-      <c r="DY17" s="105"/>
-      <c r="DZ17" s="105"/>
-      <c r="EA17" s="105"/>
-      <c r="EB17" s="105"/>
-      <c r="EC17" s="105"/>
-      <c r="ED17" s="105"/>
-      <c r="EE17" s="105"/>
-      <c r="EF17" s="105"/>
-      <c r="EG17" s="105"/>
-      <c r="EH17" s="104"/>
-      <c r="EI17" s="104"/>
-      <c r="EJ17" s="104"/>
-      <c r="EK17" s="104"/>
-      <c r="EL17" s="104"/>
-      <c r="EM17" s="104"/>
-      <c r="EN17" s="104"/>
-      <c r="EO17" s="104"/>
-      <c r="EP17" s="104"/>
-      <c r="EQ17" s="104"/>
-      <c r="ER17" s="104"/>
-      <c r="ES17" s="104"/>
-      <c r="ET17" s="104"/>
-      <c r="EU17" s="104"/>
-      <c r="EV17" s="104"/>
-      <c r="EW17" s="104"/>
-      <c r="EX17" s="104"/>
-      <c r="EY17" s="104"/>
-      <c r="EZ17" s="104"/>
-      <c r="FA17" s="104"/>
-      <c r="FB17" s="104"/>
-      <c r="FC17" s="104"/>
-      <c r="FD17" s="104"/>
-      <c r="FE17" s="104"/>
-      <c r="FF17" s="104"/>
-      <c r="FG17" s="104"/>
-      <c r="FH17" s="104"/>
-      <c r="FI17" s="104"/>
-      <c r="FJ17" s="104"/>
-      <c r="FK17" s="104"/>
-      <c r="FL17" s="104"/>
-      <c r="FM17" s="104"/>
-      <c r="FN17" s="104"/>
-      <c r="FO17" s="104"/>
-      <c r="FP17" s="104"/>
-      <c r="FQ17" s="104"/>
-      <c r="FR17" s="104"/>
-      <c r="FS17" s="104"/>
-      <c r="FT17" s="104"/>
-      <c r="FU17" s="104"/>
-      <c r="FV17" s="104"/>
-      <c r="FW17" s="104"/>
-      <c r="FX17" s="104"/>
-      <c r="FY17" s="104"/>
-      <c r="FZ17" s="104"/>
-      <c r="GA17" s="104"/>
-      <c r="GB17" s="104"/>
-      <c r="GC17" s="104"/>
-      <c r="GD17" s="104"/>
-      <c r="GE17" s="104"/>
-      <c r="GF17" s="104"/>
-      <c r="GG17" s="104"/>
-      <c r="GH17" s="104"/>
-      <c r="GI17" s="104"/>
-      <c r="GJ17" s="104"/>
-      <c r="GK17" s="104"/>
-      <c r="GL17" s="104"/>
-      <c r="GM17" s="104"/>
-      <c r="GN17" s="104"/>
-      <c r="GO17" s="104"/>
-      <c r="GP17" s="104"/>
-      <c r="GQ17" s="104"/>
-      <c r="GR17" s="104"/>
-      <c r="GS17" s="104"/>
-      <c r="GT17" s="104"/>
-      <c r="GU17" s="104"/>
-      <c r="GV17" s="104"/>
-    </row>
-    <row r="18" spans="1:211" s="95" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="172" t="s">
+      <c r="P17" s="79"/>
+      <c r="Q17" s="79"/>
+      <c r="R17" s="79"/>
+      <c r="S17" s="79"/>
+      <c r="T17" s="94"/>
+      <c r="U17" s="94"/>
+      <c r="V17" s="94"/>
+      <c r="W17" s="94"/>
+      <c r="X17" s="94"/>
+      <c r="Y17" s="94"/>
+      <c r="Z17" s="94"/>
+      <c r="AA17" s="94"/>
+      <c r="AB17" s="94"/>
+      <c r="AC17" s="94"/>
+      <c r="AD17" s="94"/>
+      <c r="AE17" s="94"/>
+      <c r="AF17" s="94"/>
+      <c r="AG17" s="94"/>
+      <c r="AH17" s="94"/>
+      <c r="AI17" s="93"/>
+      <c r="AJ17" s="93"/>
+      <c r="AK17" s="93"/>
+      <c r="AL17" s="93"/>
+      <c r="AM17" s="93"/>
+      <c r="AN17" s="93"/>
+      <c r="AO17" s="93"/>
+      <c r="AP17" s="93"/>
+      <c r="AQ17" s="93"/>
+      <c r="AR17" s="93"/>
+      <c r="AS17" s="93"/>
+      <c r="AT17" s="93"/>
+      <c r="AU17" s="93"/>
+      <c r="AV17" s="93"/>
+      <c r="AW17" s="93"/>
+      <c r="AX17" s="93"/>
+      <c r="AY17" s="93"/>
+      <c r="AZ17" s="93"/>
+      <c r="BA17" s="93"/>
+      <c r="BB17" s="93"/>
+      <c r="BC17" s="93"/>
+      <c r="BD17" s="93"/>
+      <c r="BE17" s="93"/>
+      <c r="BF17" s="93"/>
+      <c r="BG17" s="93"/>
+      <c r="BH17" s="93"/>
+      <c r="BI17" s="93"/>
+      <c r="BJ17" s="93"/>
+      <c r="BK17" s="93"/>
+      <c r="BL17" s="93"/>
+      <c r="BM17" s="93"/>
+      <c r="BN17" s="93"/>
+      <c r="BO17" s="93"/>
+      <c r="BP17" s="93"/>
+      <c r="BQ17" s="93"/>
+      <c r="BR17" s="93"/>
+      <c r="BS17" s="93"/>
+      <c r="BT17" s="93"/>
+      <c r="BU17" s="93"/>
+      <c r="BV17" s="93"/>
+      <c r="BW17" s="93"/>
+      <c r="BX17" s="93"/>
+      <c r="BY17" s="93"/>
+      <c r="BZ17" s="93"/>
+      <c r="CA17" s="93"/>
+      <c r="CB17" s="93"/>
+      <c r="CC17" s="93"/>
+      <c r="CD17" s="93"/>
+      <c r="CE17" s="93"/>
+      <c r="CF17" s="93"/>
+      <c r="CG17" s="93"/>
+      <c r="CH17" s="93"/>
+      <c r="CI17" s="93"/>
+      <c r="CJ17" s="93"/>
+      <c r="CK17" s="93"/>
+      <c r="CL17" s="93"/>
+      <c r="CM17" s="93"/>
+      <c r="CN17" s="93"/>
+      <c r="CO17" s="93"/>
+      <c r="CP17" s="93"/>
+      <c r="CQ17" s="93"/>
+      <c r="CR17" s="93"/>
+      <c r="CS17" s="93"/>
+      <c r="CT17" s="93"/>
+      <c r="CU17" s="93"/>
+      <c r="CV17" s="93"/>
+      <c r="CW17" s="93"/>
+      <c r="CX17" s="93"/>
+      <c r="CY17" s="93"/>
+      <c r="CZ17" s="93"/>
+      <c r="DA17" s="93"/>
+      <c r="DB17" s="93"/>
+      <c r="DC17" s="93"/>
+      <c r="DD17" s="93"/>
+      <c r="DE17" s="93"/>
+      <c r="DF17" s="93"/>
+      <c r="DG17" s="93"/>
+      <c r="DH17" s="93"/>
+      <c r="DI17" s="93"/>
+      <c r="DJ17" s="93"/>
+      <c r="DK17" s="93"/>
+      <c r="DL17" s="93"/>
+      <c r="DM17" s="93"/>
+      <c r="DN17" s="93"/>
+      <c r="DO17" s="93"/>
+      <c r="DP17" s="93"/>
+      <c r="DQ17" s="93"/>
+      <c r="DR17" s="93"/>
+      <c r="DS17" s="93"/>
+      <c r="DT17" s="93"/>
+      <c r="DU17" s="93"/>
+      <c r="DV17" s="93"/>
+      <c r="DW17" s="93"/>
+      <c r="DX17" s="93"/>
+      <c r="DY17" s="93"/>
+      <c r="DZ17" s="93"/>
+      <c r="EA17" s="93"/>
+      <c r="EB17" s="93"/>
+      <c r="EC17" s="93"/>
+      <c r="ED17" s="93"/>
+      <c r="EE17" s="93"/>
+      <c r="EF17" s="93"/>
+      <c r="EG17" s="93"/>
+      <c r="EH17" s="92"/>
+      <c r="EI17" s="92"/>
+      <c r="EJ17" s="92"/>
+      <c r="EK17" s="92"/>
+      <c r="EL17" s="92"/>
+      <c r="EM17" s="92"/>
+      <c r="EN17" s="92"/>
+      <c r="EO17" s="92"/>
+      <c r="EP17" s="92"/>
+      <c r="EQ17" s="92"/>
+      <c r="ER17" s="92"/>
+      <c r="ES17" s="92"/>
+      <c r="ET17" s="92"/>
+      <c r="EU17" s="92"/>
+      <c r="EV17" s="92"/>
+      <c r="EW17" s="92"/>
+      <c r="EX17" s="92"/>
+      <c r="EY17" s="92"/>
+      <c r="EZ17" s="92"/>
+      <c r="FA17" s="92"/>
+      <c r="FB17" s="92"/>
+      <c r="FC17" s="92"/>
+      <c r="FD17" s="92"/>
+      <c r="FE17" s="92"/>
+      <c r="FF17" s="92"/>
+      <c r="FG17" s="92"/>
+      <c r="FH17" s="92"/>
+      <c r="FI17" s="92"/>
+      <c r="FJ17" s="92"/>
+      <c r="FK17" s="92"/>
+      <c r="FL17" s="92"/>
+      <c r="FM17" s="92"/>
+      <c r="FN17" s="92"/>
+      <c r="FO17" s="92"/>
+      <c r="FP17" s="92"/>
+      <c r="FQ17" s="92"/>
+      <c r="FR17" s="92"/>
+      <c r="FS17" s="92"/>
+      <c r="FT17" s="92"/>
+      <c r="FU17" s="92"/>
+      <c r="FV17" s="92"/>
+      <c r="FW17" s="92"/>
+      <c r="FX17" s="92"/>
+      <c r="FY17" s="92"/>
+      <c r="FZ17" s="92"/>
+      <c r="GA17" s="92"/>
+      <c r="GB17" s="92"/>
+      <c r="GC17" s="92"/>
+      <c r="GD17" s="92"/>
+      <c r="GE17" s="92"/>
+      <c r="GF17" s="92"/>
+      <c r="GG17" s="92"/>
+      <c r="GH17" s="92"/>
+      <c r="GI17" s="92"/>
+      <c r="GJ17" s="92"/>
+      <c r="GK17" s="92"/>
+      <c r="GL17" s="92"/>
+      <c r="GM17" s="92"/>
+      <c r="GN17" s="92"/>
+      <c r="GO17" s="92"/>
+      <c r="GP17" s="92"/>
+      <c r="GQ17" s="92"/>
+      <c r="GR17" s="92"/>
+      <c r="GS17" s="92"/>
+      <c r="GT17" s="92"/>
+      <c r="GU17" s="92"/>
+      <c r="GV17" s="92"/>
+    </row>
+    <row r="18" spans="1:211" s="57" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="156" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="89">
+        <v>1</v>
+      </c>
+      <c r="C18" s="89">
+        <v>1</v>
+      </c>
+      <c r="D18" s="131">
+        <v>1</v>
+      </c>
+      <c r="E18" s="132">
+        <v>1</v>
+      </c>
+      <c r="F18" s="67">
+        <v>1</v>
+      </c>
+      <c r="G18" s="91">
+        <v>1</v>
+      </c>
+      <c r="H18" s="90">
+        <v>1</v>
+      </c>
+      <c r="I18" s="101">
+        <v>1</v>
+      </c>
+      <c r="J18" s="91">
+        <v>1</v>
+      </c>
+      <c r="K18" s="90">
+        <v>0</v>
+      </c>
+      <c r="L18" s="89">
+        <v>0</v>
+      </c>
+      <c r="M18" s="128">
+        <v>0</v>
+      </c>
+      <c r="N18" s="67">
+        <v>1</v>
+      </c>
+      <c r="O18" s="66">
+        <v>1</v>
+      </c>
+      <c r="P18" s="65"/>
+      <c r="Q18" s="64"/>
+      <c r="R18" s="64"/>
+      <c r="S18" s="59"/>
+      <c r="T18" s="59"/>
+      <c r="U18" s="59"/>
+      <c r="V18" s="59"/>
+      <c r="W18" s="59"/>
+      <c r="X18" s="59"/>
+      <c r="Y18" s="59"/>
+      <c r="Z18" s="59"/>
+      <c r="AA18" s="59"/>
+      <c r="AB18" s="59"/>
+      <c r="AC18" s="59"/>
+      <c r="AD18" s="59"/>
+      <c r="AE18" s="59"/>
+      <c r="AF18" s="59"/>
+      <c r="AG18" s="59"/>
+      <c r="AH18" s="59"/>
+      <c r="AI18" s="59"/>
+      <c r="AJ18" s="59"/>
+      <c r="AK18" s="59"/>
+      <c r="AL18" s="59"/>
+      <c r="AM18" s="59"/>
+      <c r="AN18" s="59"/>
+      <c r="AO18" s="59"/>
+      <c r="AP18" s="59"/>
+      <c r="AQ18" s="59"/>
+      <c r="AR18" s="59"/>
+      <c r="AS18" s="59"/>
+      <c r="AT18" s="59"/>
+      <c r="AU18" s="59"/>
+      <c r="AV18" s="59"/>
+      <c r="AW18" s="59"/>
+      <c r="AX18" s="59"/>
+      <c r="AY18" s="59"/>
+      <c r="AZ18" s="59"/>
+      <c r="BA18" s="59"/>
+      <c r="BB18" s="59"/>
+      <c r="BC18" s="59"/>
+      <c r="BD18" s="59"/>
+      <c r="BE18" s="59"/>
+      <c r="BF18" s="60"/>
+      <c r="BG18" s="60"/>
+      <c r="BH18" s="60"/>
+      <c r="BI18" s="60"/>
+      <c r="BJ18" s="60"/>
+      <c r="BK18" s="60"/>
+      <c r="BL18" s="60"/>
+      <c r="BM18" s="60"/>
+      <c r="BN18" s="60"/>
+      <c r="BO18" s="60"/>
+      <c r="BP18" s="60"/>
+      <c r="BQ18" s="60"/>
+      <c r="BR18" s="60"/>
+      <c r="BS18" s="60"/>
+      <c r="BT18" s="60"/>
+      <c r="BU18" s="60"/>
+      <c r="BV18" s="60"/>
+      <c r="BW18" s="60"/>
+      <c r="BX18" s="60"/>
+      <c r="BY18" s="60"/>
+      <c r="BZ18" s="60"/>
+      <c r="CA18" s="60"/>
+      <c r="CB18" s="60"/>
+      <c r="CC18" s="60"/>
+      <c r="CD18" s="60"/>
+      <c r="CE18" s="59"/>
+      <c r="CF18" s="59"/>
+      <c r="CG18" s="59"/>
+      <c r="CH18" s="59"/>
+      <c r="CI18" s="59"/>
+      <c r="CJ18" s="59"/>
+      <c r="CK18" s="59"/>
+      <c r="CL18" s="59"/>
+      <c r="CM18" s="59"/>
+      <c r="CN18" s="59"/>
+      <c r="CO18" s="59"/>
+      <c r="CP18" s="59"/>
+      <c r="CQ18" s="59"/>
+      <c r="CR18" s="59"/>
+      <c r="CS18" s="59"/>
+      <c r="CT18" s="59"/>
+      <c r="CU18" s="59"/>
+      <c r="CV18" s="59"/>
+      <c r="CW18" s="59"/>
+      <c r="CX18" s="59"/>
+      <c r="CY18" s="59"/>
+      <c r="CZ18" s="59"/>
+      <c r="DA18" s="59"/>
+      <c r="DB18" s="59"/>
+      <c r="DC18" s="59"/>
+      <c r="DD18" s="59"/>
+      <c r="DE18" s="59"/>
+      <c r="DF18" s="58"/>
+      <c r="DI18" s="49"/>
+      <c r="DJ18" s="49"/>
+      <c r="DK18" s="49"/>
+      <c r="DL18" s="49"/>
+      <c r="DM18" s="49"/>
+      <c r="DN18" s="49"/>
+      <c r="DO18" s="49"/>
+      <c r="DP18" s="49"/>
+      <c r="DQ18" s="49"/>
+      <c r="DR18" s="49"/>
+      <c r="DS18" s="49"/>
+      <c r="DT18" s="49"/>
+      <c r="DU18" s="49"/>
+      <c r="DV18" s="49"/>
+      <c r="DW18" s="49"/>
+    </row>
+    <row r="19" spans="1:211" s="49" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="156"/>
+      <c r="B19" s="133" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="133" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="133">
+        <f>C18-D18</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="133">
+        <f>C18-E18</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="134" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" s="134">
+        <f>F18-G18</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="134">
+        <f>F18-H18</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="134" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" s="134">
+        <f>I18-J18</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="134">
+        <f>I18-K18</f>
+        <v>1</v>
+      </c>
+      <c r="L19" s="133">
+        <f>L18-M18</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="82">
+        <f>IFERROR(L18/M18, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="157">
+        <f>N18-O18</f>
+        <v>0</v>
+      </c>
+      <c r="O19" s="158" t="str">
+        <f>IF(TEXT(N18-O18,"+0,0; -0,0")="+0,0","0,0",TEXT(N18-O18,"+0,0; -0,0"))</f>
+        <v>0,0</v>
+      </c>
+      <c r="P19" s="51"/>
+      <c r="Q19" s="50"/>
+      <c r="R19" s="50"/>
+      <c r="S19" s="50"/>
+      <c r="T19" s="51"/>
+      <c r="U19" s="51"/>
+      <c r="V19" s="51"/>
+      <c r="W19" s="51"/>
+      <c r="X19" s="51"/>
+      <c r="Y19" s="51"/>
+      <c r="Z19" s="51"/>
+      <c r="AA19" s="51"/>
+      <c r="AB19" s="51"/>
+      <c r="AC19" s="51"/>
+      <c r="AD19" s="51"/>
+      <c r="AE19" s="51"/>
+      <c r="AF19" s="51"/>
+      <c r="AG19" s="51"/>
+      <c r="AH19" s="51"/>
+      <c r="AI19" s="51"/>
+      <c r="AJ19" s="51"/>
+      <c r="AK19" s="51"/>
+      <c r="AL19" s="51"/>
+      <c r="AM19" s="51"/>
+      <c r="AN19" s="51"/>
+      <c r="AO19" s="51"/>
+      <c r="AP19" s="51"/>
+      <c r="AQ19" s="51"/>
+      <c r="AR19" s="51"/>
+      <c r="AS19" s="51"/>
+      <c r="AT19" s="51"/>
+      <c r="AU19" s="51"/>
+      <c r="AV19" s="51"/>
+      <c r="AW19" s="51"/>
+      <c r="AX19" s="51"/>
+      <c r="AY19" s="51"/>
+      <c r="AZ19" s="51"/>
+      <c r="BA19" s="51"/>
+      <c r="BB19" s="51"/>
+      <c r="BC19" s="51"/>
+      <c r="BD19" s="51"/>
+      <c r="BE19" s="51"/>
+      <c r="BF19" s="6"/>
+      <c r="BG19" s="6"/>
+      <c r="BH19" s="6"/>
+      <c r="BI19" s="6"/>
+      <c r="BJ19" s="6"/>
+      <c r="BK19" s="6"/>
+      <c r="BL19" s="6"/>
+      <c r="BM19" s="6"/>
+      <c r="BN19" s="6"/>
+      <c r="BO19" s="6"/>
+      <c r="BP19" s="6"/>
+      <c r="BQ19" s="6"/>
+      <c r="BR19" s="6"/>
+      <c r="BS19" s="6"/>
+      <c r="BT19" s="6"/>
+      <c r="BU19" s="6"/>
+      <c r="BV19" s="6"/>
+      <c r="BW19" s="6"/>
+      <c r="BX19" s="6"/>
+      <c r="BY19" s="6"/>
+      <c r="BZ19" s="6"/>
+      <c r="CA19" s="6"/>
+      <c r="CB19" s="6"/>
+      <c r="CC19" s="6"/>
+      <c r="CD19" s="6"/>
+      <c r="CE19" s="51"/>
+      <c r="CF19" s="51"/>
+      <c r="CG19" s="51"/>
+      <c r="CH19" s="51"/>
+      <c r="CI19" s="51"/>
+      <c r="CJ19" s="51"/>
+      <c r="CK19" s="51"/>
+      <c r="CL19" s="51"/>
+      <c r="CM19" s="51"/>
+      <c r="CN19" s="51"/>
+      <c r="CO19" s="51"/>
+      <c r="CP19" s="51"/>
+      <c r="CQ19" s="51"/>
+      <c r="CR19" s="51"/>
+      <c r="CS19" s="51"/>
+      <c r="CT19" s="51"/>
+      <c r="CU19" s="51"/>
+      <c r="CV19" s="51"/>
+      <c r="CW19" s="51"/>
+      <c r="CX19" s="51"/>
+      <c r="CY19" s="51"/>
+      <c r="CZ19" s="51"/>
+      <c r="DA19" s="51"/>
+      <c r="DB19" s="51"/>
+      <c r="DC19" s="51"/>
+      <c r="DD19" s="51"/>
+      <c r="DE19" s="51"/>
+      <c r="DF19" s="50"/>
+    </row>
+    <row r="20" spans="1:211" s="83" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="167" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="101"/>
-      <c r="C18" s="101">
-        <f t="shared" ref="C18:M18" si="0">C16+C14+C12+C10+C8+C6</f>
-        <v>6</v>
+      <c r="B20" s="89"/>
+      <c r="C20" s="89">
+        <f>C16+C14+C12+C10+C8+C6+C18</f>
+        <v>7</v>
       </c>
-      <c r="D18" s="143">
+      <c r="D20" s="89">
+        <f t="shared" ref="D20:M20" si="0">D16+D14+D12+D10+D8+D6+D18</f>
+        <v>7</v>
+      </c>
+      <c r="E20" s="89">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="F20" s="89">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="G20" s="89">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="H20" s="89">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="I20" s="89">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="J20" s="89">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="K20" s="89">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="E18" s="144">
+      <c r="L20" s="89">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F18" s="72">
+      <c r="M20" s="89">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="G18" s="103">
-        <f t="shared" si="0"/>
+      <c r="N20" s="67"/>
+      <c r="O20" s="67"/>
+      <c r="P20" s="88"/>
+      <c r="Q20" s="88"/>
+      <c r="R20" s="88"/>
+      <c r="S20" s="87"/>
+      <c r="T20" s="86"/>
+      <c r="U20" s="86"/>
+      <c r="V20" s="86"/>
+      <c r="W20" s="86"/>
+      <c r="X20" s="86"/>
+      <c r="Y20" s="86"/>
+      <c r="Z20" s="86"/>
+      <c r="AA20" s="86"/>
+      <c r="AB20" s="85"/>
+      <c r="AC20" s="85"/>
+      <c r="AD20" s="85"/>
+      <c r="AE20" s="85"/>
+      <c r="AF20" s="85"/>
+      <c r="AG20" s="85"/>
+      <c r="AH20" s="85"/>
+      <c r="AI20" s="85"/>
+      <c r="AJ20" s="85"/>
+      <c r="AK20" s="85"/>
+      <c r="AL20" s="85"/>
+      <c r="AM20" s="85"/>
+      <c r="AN20" s="85"/>
+      <c r="AO20" s="85"/>
+      <c r="AP20" s="85"/>
+      <c r="AQ20" s="85"/>
+      <c r="AR20" s="85"/>
+      <c r="AS20" s="85"/>
+      <c r="AT20" s="84"/>
+      <c r="AU20" s="84"/>
+      <c r="AV20" s="84"/>
+      <c r="AW20" s="84"/>
+      <c r="AX20" s="84"/>
+      <c r="AY20" s="84"/>
+      <c r="AZ20" s="84"/>
+      <c r="BA20" s="84"/>
+      <c r="BB20" s="84"/>
+      <c r="BC20" s="84"/>
+      <c r="BD20" s="84"/>
+      <c r="BE20" s="84"/>
+      <c r="BF20" s="85"/>
+      <c r="BG20" s="85"/>
+      <c r="BH20" s="85"/>
+      <c r="BI20" s="85"/>
+      <c r="BJ20" s="85"/>
+      <c r="BK20" s="85"/>
+      <c r="BL20" s="85"/>
+      <c r="BM20" s="85"/>
+      <c r="BN20" s="85"/>
+      <c r="BO20" s="85"/>
+      <c r="BP20" s="85"/>
+      <c r="BQ20" s="85"/>
+      <c r="BR20" s="85"/>
+      <c r="BS20" s="85"/>
+      <c r="BT20" s="85"/>
+      <c r="BU20" s="85"/>
+      <c r="BV20" s="85"/>
+      <c r="BW20" s="85"/>
+      <c r="BX20" s="85"/>
+      <c r="BY20" s="85"/>
+      <c r="BZ20" s="85"/>
+      <c r="CA20" s="85"/>
+      <c r="CB20" s="85"/>
+      <c r="CC20" s="85"/>
+      <c r="CD20" s="85"/>
+      <c r="CE20" s="85"/>
+      <c r="CF20" s="85"/>
+      <c r="CG20" s="85"/>
+      <c r="CH20" s="85"/>
+      <c r="CI20" s="85"/>
+      <c r="CJ20" s="85"/>
+      <c r="CK20" s="85"/>
+      <c r="CL20" s="85"/>
+      <c r="CM20" s="85"/>
+      <c r="CN20" s="85"/>
+      <c r="CO20" s="85"/>
+      <c r="CP20" s="85"/>
+      <c r="CQ20" s="85"/>
+      <c r="CR20" s="85"/>
+      <c r="CS20" s="85"/>
+      <c r="CT20" s="85"/>
+      <c r="CU20" s="85"/>
+      <c r="CV20" s="85"/>
+      <c r="CW20" s="85"/>
+      <c r="CX20" s="85"/>
+      <c r="CY20" s="85"/>
+      <c r="CZ20" s="85"/>
+      <c r="DA20" s="85"/>
+      <c r="DB20" s="85"/>
+      <c r="DC20" s="85"/>
+      <c r="DD20" s="85"/>
+      <c r="DE20" s="85"/>
+      <c r="DF20" s="85"/>
+      <c r="DG20" s="85"/>
+      <c r="DH20" s="85"/>
+      <c r="DI20" s="85"/>
+      <c r="DJ20" s="85"/>
+      <c r="DK20" s="85"/>
+      <c r="DL20" s="85"/>
+      <c r="DM20" s="85"/>
+      <c r="DN20" s="85"/>
+      <c r="DO20" s="85"/>
+      <c r="DP20" s="85"/>
+      <c r="DQ20" s="85"/>
+      <c r="DR20" s="85"/>
+      <c r="DS20" s="85"/>
+      <c r="DT20" s="85"/>
+      <c r="DU20" s="85"/>
+      <c r="DV20" s="85"/>
+      <c r="DW20" s="85"/>
+      <c r="DX20" s="85"/>
+      <c r="DY20" s="85"/>
+      <c r="DZ20" s="85"/>
+      <c r="EA20" s="85"/>
+      <c r="EB20" s="85"/>
+      <c r="EC20" s="85"/>
+      <c r="ED20" s="85"/>
+      <c r="EE20" s="85"/>
+      <c r="EF20" s="85"/>
+      <c r="EG20" s="85"/>
+      <c r="EH20" s="84"/>
+      <c r="EI20" s="84"/>
+      <c r="EJ20" s="84"/>
+      <c r="EK20" s="84"/>
+      <c r="EL20" s="84"/>
+      <c r="EM20" s="84"/>
+      <c r="EN20" s="84"/>
+      <c r="EO20" s="84"/>
+      <c r="EP20" s="84"/>
+      <c r="EQ20" s="84"/>
+      <c r="ER20" s="84"/>
+      <c r="ES20" s="84"/>
+      <c r="ET20" s="84"/>
+      <c r="EU20" s="84"/>
+      <c r="EV20" s="84"/>
+      <c r="EW20" s="84"/>
+      <c r="EX20" s="84"/>
+      <c r="EY20" s="84"/>
+      <c r="EZ20" s="84"/>
+      <c r="FA20" s="84"/>
+      <c r="FB20" s="84"/>
+      <c r="FC20" s="84"/>
+      <c r="FD20" s="84"/>
+      <c r="FE20" s="84"/>
+      <c r="FF20" s="84"/>
+      <c r="FG20" s="84"/>
+      <c r="FH20" s="84"/>
+      <c r="FI20" s="84"/>
+      <c r="FJ20" s="84"/>
+      <c r="FK20" s="84"/>
+      <c r="FL20" s="84"/>
+      <c r="FM20" s="84"/>
+      <c r="FN20" s="84"/>
+      <c r="FO20" s="84"/>
+      <c r="FP20" s="84"/>
+      <c r="FQ20" s="84"/>
+      <c r="FR20" s="84"/>
+      <c r="FS20" s="84"/>
+      <c r="FT20" s="84"/>
+      <c r="FU20" s="84"/>
+      <c r="FV20" s="84"/>
+      <c r="FW20" s="84"/>
+      <c r="FX20" s="84"/>
+      <c r="FY20" s="84"/>
+      <c r="FZ20" s="84"/>
+      <c r="GA20" s="84"/>
+      <c r="GB20" s="84"/>
+      <c r="GC20" s="84"/>
+      <c r="GD20" s="84"/>
+      <c r="GE20" s="84"/>
+      <c r="GF20" s="84"/>
+      <c r="GG20" s="84"/>
+      <c r="GH20" s="84"/>
+      <c r="GI20" s="84"/>
+      <c r="GJ20" s="84"/>
+      <c r="GK20" s="84"/>
+      <c r="GL20" s="84"/>
+      <c r="GM20" s="84"/>
+      <c r="GN20" s="84"/>
+      <c r="GO20" s="84"/>
+      <c r="GP20" s="84"/>
+      <c r="GQ20" s="84"/>
+      <c r="GR20" s="84"/>
+      <c r="GS20" s="84"/>
+      <c r="GT20" s="84"/>
+      <c r="GU20" s="84"/>
+      <c r="GV20" s="84"/>
+    </row>
+    <row r="21" spans="1:211" s="75" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="167"/>
+      <c r="B21" s="133"/>
+      <c r="C21" s="133">
+        <f>C7+C9+C11+C13+C15+C17+C19</f>
+        <v>-6.5299999999999994</v>
+      </c>
+      <c r="D21" s="133">
+        <f t="shared" ref="D21:M21" si="1">D7+D9+D11+D13+D15+D17+D19</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="133">
+        <f t="shared" si="1"/>
+        <v>-27.14</v>
+      </c>
+      <c r="G21" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="133">
+        <f t="shared" si="1"/>
+        <v>166</v>
+      </c>
+      <c r="J21" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="133">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L21" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="133">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="H18" s="102">
-        <f t="shared" si="0"/>
-        <v>6</v>
+      <c r="N21" s="81"/>
+      <c r="O21" s="80"/>
+      <c r="P21" s="79"/>
+      <c r="Q21" s="79"/>
+      <c r="R21" s="79"/>
+      <c r="S21" s="79"/>
+      <c r="T21" s="78"/>
+      <c r="U21" s="78"/>
+      <c r="V21" s="78"/>
+      <c r="W21" s="78"/>
+      <c r="X21" s="78"/>
+      <c r="Y21" s="78"/>
+      <c r="Z21" s="76"/>
+      <c r="AA21" s="76"/>
+      <c r="AB21" s="76"/>
+      <c r="AC21" s="76"/>
+      <c r="AD21" s="76"/>
+      <c r="AE21" s="76"/>
+      <c r="AF21" s="76"/>
+      <c r="AG21" s="76"/>
+      <c r="AH21" s="76"/>
+      <c r="AI21" s="76"/>
+      <c r="AJ21" s="76"/>
+      <c r="AK21" s="76"/>
+      <c r="AL21" s="76"/>
+      <c r="AM21" s="76"/>
+      <c r="AN21" s="76"/>
+      <c r="AO21" s="76"/>
+      <c r="AP21" s="76"/>
+      <c r="AQ21" s="76"/>
+      <c r="AR21" s="76"/>
+      <c r="AS21" s="76"/>
+      <c r="AT21" s="76"/>
+      <c r="AU21" s="76"/>
+      <c r="AV21" s="76"/>
+      <c r="AW21" s="76"/>
+      <c r="AX21" s="76"/>
+      <c r="AY21" s="76"/>
+      <c r="AZ21" s="76"/>
+      <c r="BA21" s="76"/>
+      <c r="BB21" s="76"/>
+      <c r="BC21" s="76"/>
+      <c r="BD21" s="76"/>
+      <c r="BE21" s="76"/>
+      <c r="BF21" s="77"/>
+      <c r="BG21" s="77"/>
+      <c r="BH21" s="77"/>
+      <c r="BI21" s="77"/>
+      <c r="BJ21" s="77"/>
+      <c r="BK21" s="77"/>
+      <c r="BL21" s="77"/>
+      <c r="BM21" s="77"/>
+      <c r="BN21" s="77"/>
+      <c r="BO21" s="77"/>
+      <c r="BP21" s="77"/>
+      <c r="BQ21" s="77"/>
+      <c r="BR21" s="77"/>
+      <c r="BS21" s="77"/>
+      <c r="BT21" s="77"/>
+      <c r="BU21" s="77"/>
+      <c r="BV21" s="77"/>
+      <c r="BW21" s="77"/>
+      <c r="BX21" s="77"/>
+      <c r="BY21" s="77"/>
+      <c r="BZ21" s="77"/>
+      <c r="CA21" s="77"/>
+      <c r="CB21" s="77"/>
+      <c r="CC21" s="77"/>
+      <c r="CD21" s="77"/>
+      <c r="CE21" s="76"/>
+      <c r="CF21" s="76"/>
+      <c r="CG21" s="76"/>
+      <c r="CH21" s="76"/>
+      <c r="CI21" s="76"/>
+      <c r="CJ21" s="76"/>
+      <c r="CK21" s="76"/>
+      <c r="CL21" s="76"/>
+      <c r="CM21" s="76"/>
+      <c r="CN21" s="76"/>
+      <c r="CO21" s="76"/>
+      <c r="CP21" s="76"/>
+      <c r="CQ21" s="76"/>
+      <c r="CR21" s="76"/>
+      <c r="CS21" s="76"/>
+      <c r="CT21" s="76"/>
+      <c r="CU21" s="76"/>
+      <c r="CV21" s="76"/>
+      <c r="CW21" s="76"/>
+      <c r="CX21" s="76"/>
+      <c r="CY21" s="76"/>
+      <c r="CZ21" s="76"/>
+      <c r="DA21" s="76"/>
+      <c r="DB21" s="76"/>
+      <c r="DC21" s="76"/>
+      <c r="DD21" s="76"/>
+      <c r="DE21" s="76"/>
+    </row>
+    <row r="22" spans="1:211" s="70" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="156" t="s">
+        <v>34</v>
       </c>
-      <c r="I18" s="72">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="J18" s="103">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="K18" s="102">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="L18" s="101">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="M18" s="140">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="N18" s="72"/>
-      <c r="O18" s="72"/>
-      <c r="P18" s="100"/>
-      <c r="Q18" s="100"/>
-      <c r="R18" s="100"/>
-      <c r="S18" s="99"/>
-      <c r="T18" s="98"/>
-      <c r="U18" s="98"/>
-      <c r="V18" s="98"/>
-      <c r="W18" s="98"/>
-      <c r="X18" s="98"/>
-      <c r="Y18" s="98"/>
-      <c r="Z18" s="98"/>
-      <c r="AA18" s="98"/>
-      <c r="AB18" s="97"/>
-      <c r="AC18" s="97"/>
-      <c r="AD18" s="97"/>
-      <c r="AE18" s="97"/>
-      <c r="AF18" s="97"/>
-      <c r="AG18" s="97"/>
-      <c r="AH18" s="97"/>
-      <c r="AI18" s="97"/>
-      <c r="AJ18" s="97"/>
-      <c r="AK18" s="97"/>
-      <c r="AL18" s="97"/>
-      <c r="AM18" s="97"/>
-      <c r="AN18" s="97"/>
-      <c r="AO18" s="97"/>
-      <c r="AP18" s="97"/>
-      <c r="AQ18" s="97"/>
-      <c r="AR18" s="97"/>
-      <c r="AS18" s="97"/>
-      <c r="AT18" s="96"/>
-      <c r="AU18" s="96"/>
-      <c r="AV18" s="96"/>
-      <c r="AW18" s="96"/>
-      <c r="AX18" s="96"/>
-      <c r="AY18" s="96"/>
-      <c r="AZ18" s="96"/>
-      <c r="BA18" s="96"/>
-      <c r="BB18" s="96"/>
-      <c r="BC18" s="96"/>
-      <c r="BD18" s="96"/>
-      <c r="BE18" s="96"/>
-      <c r="BF18" s="97"/>
-      <c r="BG18" s="97"/>
-      <c r="BH18" s="97"/>
-      <c r="BI18" s="97"/>
-      <c r="BJ18" s="97"/>
-      <c r="BK18" s="97"/>
-      <c r="BL18" s="97"/>
-      <c r="BM18" s="97"/>
-      <c r="BN18" s="97"/>
-      <c r="BO18" s="97"/>
-      <c r="BP18" s="97"/>
-      <c r="BQ18" s="97"/>
-      <c r="BR18" s="97"/>
-      <c r="BS18" s="97"/>
-      <c r="BT18" s="97"/>
-      <c r="BU18" s="97"/>
-      <c r="BV18" s="97"/>
-      <c r="BW18" s="97"/>
-      <c r="BX18" s="97"/>
-      <c r="BY18" s="97"/>
-      <c r="BZ18" s="97"/>
-      <c r="CA18" s="97"/>
-      <c r="CB18" s="97"/>
-      <c r="CC18" s="97"/>
-      <c r="CD18" s="97"/>
-      <c r="CE18" s="97"/>
-      <c r="CF18" s="97"/>
-      <c r="CG18" s="97"/>
-      <c r="CH18" s="97"/>
-      <c r="CI18" s="97"/>
-      <c r="CJ18" s="97"/>
-      <c r="CK18" s="97"/>
-      <c r="CL18" s="97"/>
-      <c r="CM18" s="97"/>
-      <c r="CN18" s="97"/>
-      <c r="CO18" s="97"/>
-      <c r="CP18" s="97"/>
-      <c r="CQ18" s="97"/>
-      <c r="CR18" s="97"/>
-      <c r="CS18" s="97"/>
-      <c r="CT18" s="97"/>
-      <c r="CU18" s="97"/>
-      <c r="CV18" s="97"/>
-      <c r="CW18" s="97"/>
-      <c r="CX18" s="97"/>
-      <c r="CY18" s="97"/>
-      <c r="CZ18" s="97"/>
-      <c r="DA18" s="97"/>
-      <c r="DB18" s="97"/>
-      <c r="DC18" s="97"/>
-      <c r="DD18" s="97"/>
-      <c r="DE18" s="97"/>
-      <c r="DF18" s="97"/>
-      <c r="DG18" s="97"/>
-      <c r="DH18" s="97"/>
-      <c r="DI18" s="97"/>
-      <c r="DJ18" s="97"/>
-      <c r="DK18" s="97"/>
-      <c r="DL18" s="97"/>
-      <c r="DM18" s="97"/>
-      <c r="DN18" s="97"/>
-      <c r="DO18" s="97"/>
-      <c r="DP18" s="97"/>
-      <c r="DQ18" s="97"/>
-      <c r="DR18" s="97"/>
-      <c r="DS18" s="97"/>
-      <c r="DT18" s="97"/>
-      <c r="DU18" s="97"/>
-      <c r="DV18" s="97"/>
-      <c r="DW18" s="97"/>
-      <c r="DX18" s="97"/>
-      <c r="DY18" s="97"/>
-      <c r="DZ18" s="97"/>
-      <c r="EA18" s="97"/>
-      <c r="EB18" s="97"/>
-      <c r="EC18" s="97"/>
-      <c r="ED18" s="97"/>
-      <c r="EE18" s="97"/>
-      <c r="EF18" s="97"/>
-      <c r="EG18" s="97"/>
-      <c r="EH18" s="96"/>
-      <c r="EI18" s="96"/>
-      <c r="EJ18" s="96"/>
-      <c r="EK18" s="96"/>
-      <c r="EL18" s="96"/>
-      <c r="EM18" s="96"/>
-      <c r="EN18" s="96"/>
-      <c r="EO18" s="96"/>
-      <c r="EP18" s="96"/>
-      <c r="EQ18" s="96"/>
-      <c r="ER18" s="96"/>
-      <c r="ES18" s="96"/>
-      <c r="ET18" s="96"/>
-      <c r="EU18" s="96"/>
-      <c r="EV18" s="96"/>
-      <c r="EW18" s="96"/>
-      <c r="EX18" s="96"/>
-      <c r="EY18" s="96"/>
-      <c r="EZ18" s="96"/>
-      <c r="FA18" s="96"/>
-      <c r="FB18" s="96"/>
-      <c r="FC18" s="96"/>
-      <c r="FD18" s="96"/>
-      <c r="FE18" s="96"/>
-      <c r="FF18" s="96"/>
-      <c r="FG18" s="96"/>
-      <c r="FH18" s="96"/>
-      <c r="FI18" s="96"/>
-      <c r="FJ18" s="96"/>
-      <c r="FK18" s="96"/>
-      <c r="FL18" s="96"/>
-      <c r="FM18" s="96"/>
-      <c r="FN18" s="96"/>
-      <c r="FO18" s="96"/>
-      <c r="FP18" s="96"/>
-      <c r="FQ18" s="96"/>
-      <c r="FR18" s="96"/>
-      <c r="FS18" s="96"/>
-      <c r="FT18" s="96"/>
-      <c r="FU18" s="96"/>
-      <c r="FV18" s="96"/>
-      <c r="FW18" s="96"/>
-      <c r="FX18" s="96"/>
-      <c r="FY18" s="96"/>
-      <c r="FZ18" s="96"/>
-      <c r="GA18" s="96"/>
-      <c r="GB18" s="96"/>
-      <c r="GC18" s="96"/>
-      <c r="GD18" s="96"/>
-      <c r="GE18" s="96"/>
-      <c r="GF18" s="96"/>
-      <c r="GG18" s="96"/>
-      <c r="GH18" s="96"/>
-      <c r="GI18" s="96"/>
-      <c r="GJ18" s="96"/>
-      <c r="GK18" s="96"/>
-      <c r="GL18" s="96"/>
-      <c r="GM18" s="96"/>
-      <c r="GN18" s="96"/>
-      <c r="GO18" s="96"/>
-      <c r="GP18" s="96"/>
-      <c r="GQ18" s="96"/>
-      <c r="GR18" s="96"/>
-      <c r="GS18" s="96"/>
-      <c r="GT18" s="96"/>
-      <c r="GU18" s="96"/>
-      <c r="GV18" s="96"/>
-    </row>
-    <row r="19" spans="1:211" s="87" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="172"/>
-      <c r="B19" s="145"/>
-      <c r="C19" s="145">
-        <f>C7+C9+C11+C13+C15+C17</f>
-        <v>1.870000000000001</v>
-      </c>
-      <c r="D19" s="145">
-        <f>C18-D18</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="145">
-        <f>C18-E18</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="146">
-        <f>F7+F9+F11+F13+F15+F17</f>
-        <v>-13.14</v>
-      </c>
-      <c r="G19" s="146">
-        <f>F18-G18</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="146">
-        <f>F18-H18</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="146">
-        <f>I7+I9+I11+I13+I15+I17</f>
-        <v>83</v>
-      </c>
-      <c r="J19" s="146">
-        <f>I18-J18</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="146">
-        <f>I18-K18</f>
-        <v>0</v>
-      </c>
-      <c r="L19" s="145">
-        <f>L18-M18</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="94">
-        <f>IFERROR(L18/M18, 0)</f>
+      <c r="B22" s="89">
         <v>1</v>
       </c>
-      <c r="N19" s="93"/>
-      <c r="O19" s="92"/>
-      <c r="P19" s="91"/>
-      <c r="Q19" s="91"/>
-      <c r="R19" s="91"/>
-      <c r="S19" s="91"/>
-      <c r="T19" s="90"/>
-      <c r="U19" s="90"/>
-      <c r="V19" s="90"/>
-      <c r="W19" s="90"/>
-      <c r="X19" s="90"/>
-      <c r="Y19" s="90"/>
-      <c r="Z19" s="88"/>
-      <c r="AA19" s="88"/>
-      <c r="AB19" s="88"/>
-      <c r="AC19" s="88"/>
-      <c r="AD19" s="88"/>
-      <c r="AE19" s="88"/>
-      <c r="AF19" s="88"/>
-      <c r="AG19" s="88"/>
-      <c r="AH19" s="88"/>
-      <c r="AI19" s="88"/>
-      <c r="AJ19" s="88"/>
-      <c r="AK19" s="88"/>
-      <c r="AL19" s="88"/>
-      <c r="AM19" s="88"/>
-      <c r="AN19" s="88"/>
-      <c r="AO19" s="88"/>
-      <c r="AP19" s="88"/>
-      <c r="AQ19" s="88"/>
-      <c r="AR19" s="88"/>
-      <c r="AS19" s="88"/>
-      <c r="AT19" s="88"/>
-      <c r="AU19" s="88"/>
-      <c r="AV19" s="88"/>
-      <c r="AW19" s="88"/>
-      <c r="AX19" s="88"/>
-      <c r="AY19" s="88"/>
-      <c r="AZ19" s="88"/>
-      <c r="BA19" s="88"/>
-      <c r="BB19" s="88"/>
-      <c r="BC19" s="88"/>
-      <c r="BD19" s="88"/>
-      <c r="BE19" s="88"/>
-      <c r="BF19" s="89"/>
-      <c r="BG19" s="89"/>
-      <c r="BH19" s="89"/>
-      <c r="BI19" s="89"/>
-      <c r="BJ19" s="89"/>
-      <c r="BK19" s="89"/>
-      <c r="BL19" s="89"/>
-      <c r="BM19" s="89"/>
-      <c r="BN19" s="89"/>
-      <c r="BO19" s="89"/>
-      <c r="BP19" s="89"/>
-      <c r="BQ19" s="89"/>
-      <c r="BR19" s="89"/>
-      <c r="BS19" s="89"/>
-      <c r="BT19" s="89"/>
-      <c r="BU19" s="89"/>
-      <c r="BV19" s="89"/>
-      <c r="BW19" s="89"/>
-      <c r="BX19" s="89"/>
-      <c r="BY19" s="89"/>
-      <c r="BZ19" s="89"/>
-      <c r="CA19" s="89"/>
-      <c r="CB19" s="89"/>
-      <c r="CC19" s="89"/>
-      <c r="CD19" s="89"/>
-      <c r="CE19" s="88"/>
-      <c r="CF19" s="88"/>
-      <c r="CG19" s="88"/>
-      <c r="CH19" s="88"/>
-      <c r="CI19" s="88"/>
-      <c r="CJ19" s="88"/>
-      <c r="CK19" s="88"/>
-      <c r="CL19" s="88"/>
-      <c r="CM19" s="88"/>
-      <c r="CN19" s="88"/>
-      <c r="CO19" s="88"/>
-      <c r="CP19" s="88"/>
-      <c r="CQ19" s="88"/>
-      <c r="CR19" s="88"/>
-      <c r="CS19" s="88"/>
-      <c r="CT19" s="88"/>
-      <c r="CU19" s="88"/>
-      <c r="CV19" s="88"/>
-      <c r="CW19" s="88"/>
-      <c r="CX19" s="88"/>
-      <c r="CY19" s="88"/>
-      <c r="CZ19" s="88"/>
-      <c r="DA19" s="88"/>
-      <c r="DB19" s="88"/>
-      <c r="DC19" s="88"/>
-      <c r="DD19" s="88"/>
-      <c r="DE19" s="88"/>
-    </row>
-    <row r="20" spans="1:211" s="81" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="173" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" s="101">
+      <c r="C22" s="89">
         <v>1</v>
       </c>
-      <c r="C20" s="73"/>
-      <c r="D20" s="75"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="72">
+      <c r="D22" s="89">
         <v>1</v>
       </c>
-      <c r="G20" s="86"/>
-      <c r="H20" s="76"/>
-      <c r="I20" s="72">
+      <c r="E22" s="89">
         <v>1</v>
       </c>
-      <c r="J20" s="75"/>
-      <c r="K20" s="74"/>
-      <c r="L20" s="73"/>
-      <c r="M20" s="73"/>
-      <c r="N20" s="72">
+      <c r="F22" s="89">
         <v>1</v>
       </c>
-      <c r="O20" s="71">
+      <c r="G22" s="89">
         <v>1</v>
       </c>
-      <c r="P20" s="85"/>
-      <c r="Q20" s="85"/>
-      <c r="R20" s="85"/>
-      <c r="S20" s="85"/>
-      <c r="T20" s="83"/>
-      <c r="U20" s="83"/>
-      <c r="V20" s="83"/>
-      <c r="W20" s="83"/>
-      <c r="X20" s="83"/>
-      <c r="Y20" s="83"/>
-      <c r="Z20" s="83"/>
-      <c r="AA20" s="83"/>
-      <c r="AB20" s="83"/>
-      <c r="AC20" s="83"/>
-      <c r="AD20" s="83"/>
-      <c r="AE20" s="83"/>
-      <c r="AF20" s="83"/>
-      <c r="AG20" s="83"/>
-      <c r="AH20" s="83"/>
-      <c r="AI20" s="83"/>
-      <c r="AJ20" s="83"/>
-      <c r="AK20" s="83"/>
-      <c r="AL20" s="83"/>
-      <c r="AM20" s="83"/>
-      <c r="AN20" s="83"/>
-      <c r="AO20" s="83"/>
-      <c r="AP20" s="83"/>
-      <c r="AQ20" s="83"/>
-      <c r="AR20" s="83"/>
-      <c r="AS20" s="83"/>
-      <c r="AT20" s="83"/>
-      <c r="AU20" s="83"/>
-      <c r="AV20" s="83"/>
-      <c r="AW20" s="83"/>
-      <c r="AX20" s="83"/>
-      <c r="AY20" s="83"/>
-      <c r="AZ20" s="83"/>
-      <c r="BA20" s="83"/>
-      <c r="BB20" s="83"/>
-      <c r="BC20" s="83"/>
-      <c r="BD20" s="83"/>
-      <c r="BE20" s="83"/>
-      <c r="BF20" s="84"/>
-      <c r="BG20" s="84"/>
-      <c r="BH20" s="84"/>
-      <c r="BI20" s="84"/>
-      <c r="BJ20" s="84"/>
-      <c r="BK20" s="84"/>
-      <c r="BL20" s="84"/>
-      <c r="BM20" s="84"/>
-      <c r="BN20" s="84"/>
-      <c r="BO20" s="84"/>
-      <c r="BP20" s="84"/>
-      <c r="BQ20" s="84"/>
-      <c r="BR20" s="84"/>
-      <c r="BS20" s="84"/>
-      <c r="BT20" s="84"/>
-      <c r="BU20" s="84"/>
-      <c r="BV20" s="84"/>
-      <c r="BW20" s="84"/>
-      <c r="BX20" s="84"/>
-      <c r="BY20" s="84"/>
-      <c r="BZ20" s="84"/>
-      <c r="CA20" s="84"/>
-      <c r="CB20" s="84"/>
-      <c r="CC20" s="84"/>
-      <c r="CD20" s="84"/>
-      <c r="CE20" s="83"/>
-      <c r="CF20" s="83"/>
-      <c r="CG20" s="83"/>
-      <c r="CH20" s="83"/>
-      <c r="CI20" s="83"/>
-      <c r="CJ20" s="83"/>
-      <c r="CK20" s="83"/>
-      <c r="CL20" s="83"/>
-      <c r="CM20" s="83"/>
-      <c r="CN20" s="83"/>
-      <c r="CO20" s="83"/>
-      <c r="CP20" s="83"/>
-      <c r="CQ20" s="83"/>
-      <c r="CR20" s="83"/>
-      <c r="CS20" s="83"/>
-      <c r="CT20" s="83"/>
-      <c r="CU20" s="83"/>
-      <c r="CV20" s="83"/>
-      <c r="CW20" s="83"/>
-      <c r="CX20" s="83"/>
-      <c r="CY20" s="83"/>
-      <c r="CZ20" s="83"/>
-      <c r="DA20" s="83"/>
-      <c r="DB20" s="83"/>
-      <c r="DC20" s="83"/>
-      <c r="DD20" s="83"/>
-      <c r="DE20" s="83"/>
-      <c r="FQ20" s="82"/>
-    </row>
-    <row r="21" spans="1:211" s="49" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="173"/>
-      <c r="B21" s="145" t="s">
+      <c r="H22" s="89">
+        <v>1</v>
+      </c>
+      <c r="I22" s="89">
+        <v>1</v>
+      </c>
+      <c r="J22" s="89">
+        <v>1</v>
+      </c>
+      <c r="K22" s="89">
+        <v>1</v>
+      </c>
+      <c r="L22" s="89">
+        <v>1</v>
+      </c>
+      <c r="M22" s="89">
+        <v>1</v>
+      </c>
+      <c r="N22" s="67">
+        <v>1</v>
+      </c>
+      <c r="O22" s="66">
+        <v>1</v>
+      </c>
+      <c r="P22" s="74"/>
+      <c r="Q22" s="74"/>
+      <c r="R22" s="74"/>
+      <c r="S22" s="74"/>
+      <c r="T22" s="72"/>
+      <c r="U22" s="72"/>
+      <c r="V22" s="72"/>
+      <c r="W22" s="72"/>
+      <c r="X22" s="72"/>
+      <c r="Y22" s="72"/>
+      <c r="Z22" s="72"/>
+      <c r="AA22" s="72"/>
+      <c r="AB22" s="72"/>
+      <c r="AC22" s="72"/>
+      <c r="AD22" s="72"/>
+      <c r="AE22" s="72"/>
+      <c r="AF22" s="72"/>
+      <c r="AG22" s="72"/>
+      <c r="AH22" s="72"/>
+      <c r="AI22" s="72"/>
+      <c r="AJ22" s="72"/>
+      <c r="AK22" s="72"/>
+      <c r="AL22" s="72"/>
+      <c r="AM22" s="72"/>
+      <c r="AN22" s="72"/>
+      <c r="AO22" s="72"/>
+      <c r="AP22" s="72"/>
+      <c r="AQ22" s="72"/>
+      <c r="AR22" s="72"/>
+      <c r="AS22" s="72"/>
+      <c r="AT22" s="72"/>
+      <c r="AU22" s="72"/>
+      <c r="AV22" s="72"/>
+      <c r="AW22" s="72"/>
+      <c r="AX22" s="72"/>
+      <c r="AY22" s="72"/>
+      <c r="AZ22" s="72"/>
+      <c r="BA22" s="72"/>
+      <c r="BB22" s="72"/>
+      <c r="BC22" s="72"/>
+      <c r="BD22" s="72"/>
+      <c r="BE22" s="72"/>
+      <c r="BF22" s="73"/>
+      <c r="BG22" s="73"/>
+      <c r="BH22" s="73"/>
+      <c r="BI22" s="73"/>
+      <c r="BJ22" s="73"/>
+      <c r="BK22" s="73"/>
+      <c r="BL22" s="73"/>
+      <c r="BM22" s="73"/>
+      <c r="BN22" s="73"/>
+      <c r="BO22" s="73"/>
+      <c r="BP22" s="73"/>
+      <c r="BQ22" s="73"/>
+      <c r="BR22" s="73"/>
+      <c r="BS22" s="73"/>
+      <c r="BT22" s="73"/>
+      <c r="BU22" s="73"/>
+      <c r="BV22" s="73"/>
+      <c r="BW22" s="73"/>
+      <c r="BX22" s="73"/>
+      <c r="BY22" s="73"/>
+      <c r="BZ22" s="73"/>
+      <c r="CA22" s="73"/>
+      <c r="CB22" s="73"/>
+      <c r="CC22" s="73"/>
+      <c r="CD22" s="73"/>
+      <c r="CE22" s="72"/>
+      <c r="CF22" s="72"/>
+      <c r="CG22" s="72"/>
+      <c r="CH22" s="72"/>
+      <c r="CI22" s="72"/>
+      <c r="CJ22" s="72"/>
+      <c r="CK22" s="72"/>
+      <c r="CL22" s="72"/>
+      <c r="CM22" s="72"/>
+      <c r="CN22" s="72"/>
+      <c r="CO22" s="72"/>
+      <c r="CP22" s="72"/>
+      <c r="CQ22" s="72"/>
+      <c r="CR22" s="72"/>
+      <c r="CS22" s="72"/>
+      <c r="CT22" s="72"/>
+      <c r="CU22" s="72"/>
+      <c r="CV22" s="72"/>
+      <c r="CW22" s="72"/>
+      <c r="CX22" s="72"/>
+      <c r="CY22" s="72"/>
+      <c r="CZ22" s="72"/>
+      <c r="DA22" s="72"/>
+      <c r="DB22" s="72"/>
+      <c r="DC22" s="72"/>
+      <c r="DD22" s="72"/>
+      <c r="DE22" s="72"/>
+      <c r="FQ22" s="71"/>
+    </row>
+    <row r="23" spans="1:211" s="49" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="156"/>
+      <c r="B23" s="133" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="80"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="146" t="s">
-        <v>36</v>
+      <c r="C23" s="133" t="s">
+        <v>26</v>
       </c>
-      <c r="G21" s="80"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="146" t="s">
-        <v>36</v>
-      </c>
-      <c r="J21" s="66"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="64"/>
-      <c r="M21" s="79"/>
-      <c r="N21" s="168">
-        <f>N20-O20</f>
-        <v>0</v>
-      </c>
-      <c r="O21" s="169" t="str">
-        <f>IF(TEXT(N20-O20,"+0,0; -0,0")="+0,0","0,0",TEXT(N20-O20,"+0,0; -0,0"))</f>
-        <v>0,0</v>
-      </c>
-      <c r="P21" s="78"/>
-      <c r="Q21" s="78"/>
-      <c r="R21" s="78"/>
-      <c r="S21" s="78"/>
-      <c r="T21" s="51"/>
-      <c r="U21" s="51"/>
-      <c r="V21" s="51"/>
-      <c r="W21" s="51"/>
-      <c r="X21" s="51"/>
-      <c r="Y21" s="51"/>
-      <c r="Z21" s="51"/>
-      <c r="AA21" s="51"/>
-      <c r="AB21" s="51"/>
-      <c r="AC21" s="51"/>
-      <c r="AD21" s="51"/>
-      <c r="AE21" s="51"/>
-      <c r="AF21" s="51"/>
-      <c r="AG21" s="51"/>
-      <c r="AH21" s="51"/>
-      <c r="AI21" s="51"/>
-      <c r="AJ21" s="51"/>
-      <c r="AK21" s="51"/>
-      <c r="AL21" s="51"/>
-      <c r="AM21" s="51"/>
-      <c r="AN21" s="51"/>
-      <c r="AO21" s="51"/>
-      <c r="AP21" s="51"/>
-      <c r="AQ21" s="51"/>
-      <c r="AR21" s="51"/>
-      <c r="AS21" s="51"/>
-      <c r="AT21" s="51"/>
-      <c r="AU21" s="51"/>
-      <c r="AV21" s="51"/>
-      <c r="AW21" s="51"/>
-      <c r="AX21" s="51"/>
-      <c r="AY21" s="51"/>
-      <c r="AZ21" s="51"/>
-      <c r="BA21" s="51"/>
-      <c r="BB21" s="51"/>
-      <c r="BC21" s="51"/>
-      <c r="BD21" s="51"/>
-      <c r="BE21" s="51"/>
-      <c r="BF21" s="6"/>
-      <c r="BG21" s="6"/>
-      <c r="BH21" s="6"/>
-      <c r="BI21" s="6"/>
-      <c r="BJ21" s="6"/>
-      <c r="BK21" s="6"/>
-      <c r="BL21" s="6"/>
-      <c r="BM21" s="6"/>
-      <c r="BN21" s="6"/>
-      <c r="BO21" s="6"/>
-      <c r="BP21" s="6"/>
-      <c r="BQ21" s="6"/>
-      <c r="BR21" s="6"/>
-      <c r="BS21" s="6"/>
-      <c r="BT21" s="6"/>
-      <c r="BU21" s="6"/>
-      <c r="BV21" s="6"/>
-      <c r="BW21" s="6"/>
-      <c r="BX21" s="6"/>
-      <c r="BY21" s="6"/>
-      <c r="BZ21" s="6"/>
-      <c r="CA21" s="6"/>
-      <c r="CB21" s="6"/>
-      <c r="CC21" s="6"/>
-      <c r="CD21" s="6"/>
-      <c r="CE21" s="51"/>
-      <c r="CF21" s="51"/>
-      <c r="CG21" s="51"/>
-      <c r="CH21" s="51"/>
-      <c r="CI21" s="51"/>
-      <c r="CJ21" s="51"/>
-      <c r="CK21" s="51"/>
-      <c r="CL21" s="51"/>
-      <c r="CM21" s="51"/>
-      <c r="CN21" s="51"/>
-      <c r="CO21" s="51"/>
-      <c r="CP21" s="51"/>
-      <c r="CQ21" s="51"/>
-      <c r="CR21" s="51"/>
-      <c r="CS21" s="51"/>
-      <c r="CT21" s="51"/>
-      <c r="CU21" s="51"/>
-      <c r="CV21" s="51"/>
-      <c r="CW21" s="51"/>
-      <c r="CX21" s="51"/>
-      <c r="CY21" s="51"/>
-      <c r="CZ21" s="51"/>
-      <c r="DA21" s="51"/>
-      <c r="DB21" s="51"/>
-      <c r="DC21" s="51"/>
-      <c r="DD21" s="51"/>
-      <c r="DE21" s="51"/>
-      <c r="DF21" s="77"/>
-    </row>
-    <row r="22" spans="1:211" s="57" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="173" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="101">
-        <v>1</v>
-      </c>
-      <c r="C22" s="101">
-        <v>1</v>
-      </c>
-      <c r="D22" s="143">
-        <v>1</v>
-      </c>
-      <c r="E22" s="144">
-        <v>1</v>
-      </c>
-      <c r="F22" s="72">
-        <v>1</v>
-      </c>
-      <c r="G22" s="103">
-        <v>1</v>
-      </c>
-      <c r="H22" s="102">
-        <v>1</v>
-      </c>
-      <c r="I22" s="113">
-        <v>1</v>
-      </c>
-      <c r="J22" s="103">
-        <v>1</v>
-      </c>
-      <c r="K22" s="102">
-        <v>0</v>
-      </c>
-      <c r="L22" s="101">
-        <v>0</v>
-      </c>
-      <c r="M22" s="140">
-        <v>0</v>
-      </c>
-      <c r="N22" s="72">
-        <v>1</v>
-      </c>
-      <c r="O22" s="71">
-        <v>1</v>
-      </c>
-      <c r="P22" s="70"/>
-      <c r="Q22" s="69"/>
-      <c r="R22" s="69"/>
-      <c r="S22" s="59"/>
-      <c r="T22" s="59"/>
-      <c r="U22" s="59"/>
-      <c r="V22" s="59"/>
-      <c r="W22" s="59"/>
-      <c r="X22" s="59"/>
-      <c r="Y22" s="59"/>
-      <c r="Z22" s="59"/>
-      <c r="AA22" s="59"/>
-      <c r="AB22" s="59"/>
-      <c r="AC22" s="59"/>
-      <c r="AD22" s="59"/>
-      <c r="AE22" s="59"/>
-      <c r="AF22" s="59"/>
-      <c r="AG22" s="59"/>
-      <c r="AH22" s="59"/>
-      <c r="AI22" s="59"/>
-      <c r="AJ22" s="59"/>
-      <c r="AK22" s="59"/>
-      <c r="AL22" s="59"/>
-      <c r="AM22" s="59"/>
-      <c r="AN22" s="59"/>
-      <c r="AO22" s="59"/>
-      <c r="AP22" s="59"/>
-      <c r="AQ22" s="59"/>
-      <c r="AR22" s="59"/>
-      <c r="AS22" s="59"/>
-      <c r="AT22" s="59"/>
-      <c r="AU22" s="59"/>
-      <c r="AV22" s="59"/>
-      <c r="AW22" s="59"/>
-      <c r="AX22" s="59"/>
-      <c r="AY22" s="59"/>
-      <c r="AZ22" s="59"/>
-      <c r="BA22" s="59"/>
-      <c r="BB22" s="59"/>
-      <c r="BC22" s="59"/>
-      <c r="BD22" s="59"/>
-      <c r="BE22" s="59"/>
-      <c r="BF22" s="60"/>
-      <c r="BG22" s="60"/>
-      <c r="BH22" s="60"/>
-      <c r="BI22" s="60"/>
-      <c r="BJ22" s="60"/>
-      <c r="BK22" s="60"/>
-      <c r="BL22" s="60"/>
-      <c r="BM22" s="60"/>
-      <c r="BN22" s="60"/>
-      <c r="BO22" s="60"/>
-      <c r="BP22" s="60"/>
-      <c r="BQ22" s="60"/>
-      <c r="BR22" s="60"/>
-      <c r="BS22" s="60"/>
-      <c r="BT22" s="60"/>
-      <c r="BU22" s="60"/>
-      <c r="BV22" s="60"/>
-      <c r="BW22" s="60"/>
-      <c r="BX22" s="60"/>
-      <c r="BY22" s="60"/>
-      <c r="BZ22" s="60"/>
-      <c r="CA22" s="60"/>
-      <c r="CB22" s="60"/>
-      <c r="CC22" s="60"/>
-      <c r="CD22" s="60"/>
-      <c r="CE22" s="59"/>
-      <c r="CF22" s="59"/>
-      <c r="CG22" s="59"/>
-      <c r="CH22" s="59"/>
-      <c r="CI22" s="59"/>
-      <c r="CJ22" s="59"/>
-      <c r="CK22" s="59"/>
-      <c r="CL22" s="59"/>
-      <c r="CM22" s="59"/>
-      <c r="CN22" s="59"/>
-      <c r="CO22" s="59"/>
-      <c r="CP22" s="59"/>
-      <c r="CQ22" s="59"/>
-      <c r="CR22" s="59"/>
-      <c r="CS22" s="59"/>
-      <c r="CT22" s="59"/>
-      <c r="CU22" s="59"/>
-      <c r="CV22" s="59"/>
-      <c r="CW22" s="59"/>
-      <c r="CX22" s="59"/>
-      <c r="CY22" s="59"/>
-      <c r="CZ22" s="59"/>
-      <c r="DA22" s="59"/>
-      <c r="DB22" s="59"/>
-      <c r="DC22" s="59"/>
-      <c r="DD22" s="59"/>
-      <c r="DE22" s="59"/>
-      <c r="DF22" s="58"/>
-      <c r="DI22" s="49"/>
-      <c r="DJ22" s="49"/>
-      <c r="DK22" s="49"/>
-      <c r="DL22" s="49"/>
-      <c r="DM22" s="49"/>
-      <c r="DN22" s="49"/>
-      <c r="DO22" s="49"/>
-      <c r="DP22" s="49"/>
-      <c r="DQ22" s="49"/>
-      <c r="DR22" s="49"/>
-      <c r="DS22" s="49"/>
-      <c r="DT22" s="49"/>
-      <c r="DU22" s="49"/>
-      <c r="DV22" s="49"/>
-      <c r="DW22" s="49"/>
-    </row>
-    <row r="23" spans="1:211" s="49" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="173"/>
-      <c r="B23" s="145" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="145" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="145">
+      <c r="D23" s="133">
         <f>C22-D22</f>
         <v>0</v>
       </c>
-      <c r="E23" s="145">
+      <c r="E23" s="133">
         <f>C22-E22</f>
         <v>0</v>
       </c>
-      <c r="F23" s="146" t="s">
-        <v>31</v>
+      <c r="F23" s="134" t="s">
+        <v>27</v>
       </c>
-      <c r="G23" s="146">
+      <c r="G23" s="134">
         <f>F22-G22</f>
         <v>0</v>
       </c>
-      <c r="H23" s="146">
+      <c r="H23" s="134">
         <f>F22-H22</f>
         <v>0</v>
       </c>
-      <c r="I23" s="146" t="s">
-        <v>32</v>
+      <c r="I23" s="134" t="s">
+        <v>14</v>
       </c>
-      <c r="J23" s="146">
+      <c r="J23" s="134">
         <f>I22-J22</f>
         <v>0</v>
       </c>
-      <c r="K23" s="146">
+      <c r="K23" s="134">
         <f>I22-K22</f>
-        <v>1</v>
+        <v>0</v>
       </c>
-      <c r="L23" s="145">
+      <c r="L23" s="133">
         <f>L22-M22</f>
         <v>0</v>
       </c>
-      <c r="M23" s="94">
+      <c r="M23" s="82">
         <f>IFERROR(L22/M22, 0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
-      <c r="N23" s="168">
+      <c r="N23" s="157">
         <f>N22-O22</f>
         <v>0</v>
       </c>
-      <c r="O23" s="169" t="str">
+      <c r="O23" s="158" t="str">
         <f>IF(TEXT(N22-O22,"+0,0; -0,0")="+0,0","0,0",TEXT(N22-O22,"+0,0; -0,0"))</f>
         <v>0,0</v>
       </c>
-      <c r="P23" s="51"/>
-      <c r="Q23" s="50"/>
-      <c r="R23" s="50"/>
-      <c r="S23" s="50"/>
+      <c r="P23" s="69"/>
+      <c r="Q23" s="69"/>
+      <c r="R23" s="69"/>
+      <c r="S23" s="69"/>
       <c r="T23" s="51"/>
       <c r="U23" s="51"/>
       <c r="V23" s="51"/>
@@ -8951,24 +8830,24 @@
       <c r="DC23" s="51"/>
       <c r="DD23" s="51"/>
       <c r="DE23" s="51"/>
-      <c r="DF23" s="50"/>
+      <c r="DF23" s="68"/>
     </row>
     <row r="24" spans="1:211" s="49" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="174"/>
-      <c r="B24" s="174"/>
-      <c r="C24" s="174"/>
-      <c r="D24" s="174"/>
-      <c r="E24" s="174"/>
-      <c r="F24" s="174"/>
-      <c r="G24" s="174"/>
-      <c r="H24" s="174"/>
-      <c r="I24" s="174"/>
-      <c r="J24" s="174"/>
-      <c r="K24" s="174"/>
-      <c r="L24" s="174"/>
-      <c r="M24" s="174"/>
-      <c r="N24" s="174"/>
-      <c r="O24" s="174"/>
+      <c r="A24" s="135"/>
+      <c r="B24" s="135"/>
+      <c r="C24" s="135"/>
+      <c r="D24" s="135"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="135"/>
+      <c r="H24" s="135"/>
+      <c r="I24" s="135"/>
+      <c r="J24" s="135"/>
+      <c r="K24" s="135"/>
+      <c r="L24" s="135"/>
+      <c r="M24" s="135"/>
+      <c r="N24" s="135"/>
+      <c r="O24" s="135"/>
       <c r="P24" s="62"/>
       <c r="Q24" s="62"/>
       <c r="R24" s="55"/>
@@ -9073,38 +8952,38 @@
       <c r="DM24" s="50"/>
     </row>
     <row r="25" spans="1:211" s="49" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="175"/>
-      <c r="B25" s="175"/>
-      <c r="C25" s="175"/>
-      <c r="D25" s="175"/>
-      <c r="E25" s="175"/>
-      <c r="F25" s="175"/>
-      <c r="G25" s="175"/>
-      <c r="H25" s="175"/>
-      <c r="I25" s="175"/>
-      <c r="J25" s="175"/>
-      <c r="K25" s="175"/>
-      <c r="L25" s="175"/>
-      <c r="M25" s="175"/>
-      <c r="N25" s="175"/>
-      <c r="O25" s="175"/>
+      <c r="A25" s="136"/>
+      <c r="B25" s="136"/>
+      <c r="C25" s="136"/>
+      <c r="D25" s="136"/>
+      <c r="E25" s="136"/>
+      <c r="F25" s="136"/>
+      <c r="G25" s="136"/>
+      <c r="H25" s="136"/>
+      <c r="I25" s="136"/>
+      <c r="J25" s="136"/>
+      <c r="K25" s="136"/>
+      <c r="L25" s="136"/>
+      <c r="M25" s="136"/>
+      <c r="N25" s="136"/>
+      <c r="O25" s="136"/>
       <c r="P25" s="61"/>
       <c r="Q25" s="61"/>
       <c r="R25" s="61"/>
       <c r="S25" s="61"/>
-      <c r="T25" s="148" t="s">
-        <v>38</v>
+      <c r="T25" s="153" t="s">
+        <v>37</v>
       </c>
-      <c r="U25" s="149"/>
-      <c r="V25" s="149"/>
-      <c r="W25" s="149"/>
+      <c r="U25" s="154"/>
+      <c r="V25" s="154"/>
+      <c r="W25" s="154"/>
       <c r="X25" s="61"/>
       <c r="Y25" s="61"/>
       <c r="Z25" s="61"/>
       <c r="AA25" s="61"/>
-      <c r="AB25" s="147"/>
-      <c r="AC25" s="147"/>
-      <c r="AD25" s="147"/>
+      <c r="AB25" s="155"/>
+      <c r="AC25" s="155"/>
+      <c r="AD25" s="155"/>
       <c r="AE25" s="61"/>
       <c r="AF25" s="61"/>
       <c r="AG25" s="59"/>
@@ -9288,23 +9167,23 @@
       <c r="HC25" s="56"/>
     </row>
     <row r="26" spans="1:211" s="49" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="176" t="s">
-        <v>49</v>
+      <c r="A26" s="171" t="s">
+        <v>48</v>
       </c>
-      <c r="B26" s="177"/>
-      <c r="C26" s="177"/>
-      <c r="D26" s="177"/>
-      <c r="E26" s="177"/>
-      <c r="F26" s="177"/>
-      <c r="G26" s="177"/>
-      <c r="H26" s="177"/>
-      <c r="I26" s="177"/>
-      <c r="J26" s="177"/>
-      <c r="K26" s="177"/>
-      <c r="L26" s="177"/>
-      <c r="M26" s="177"/>
-      <c r="N26" s="177"/>
-      <c r="O26" s="177"/>
+      <c r="B26" s="172"/>
+      <c r="C26" s="172"/>
+      <c r="D26" s="172"/>
+      <c r="E26" s="172"/>
+      <c r="F26" s="172"/>
+      <c r="G26" s="172"/>
+      <c r="H26" s="172"/>
+      <c r="I26" s="172"/>
+      <c r="J26" s="172"/>
+      <c r="K26" s="172"/>
+      <c r="L26" s="172"/>
+      <c r="M26" s="172"/>
+      <c r="N26" s="172"/>
+      <c r="O26" s="172"/>
       <c r="P26" s="52"/>
       <c r="Q26" s="52"/>
       <c r="R26" s="52"/>
@@ -9696,46 +9575,46 @@
       <c r="HC27" s="39"/>
     </row>
     <row r="28" spans="1:211" ht="32.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="199" t="s">
+      <c r="A28" s="159" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="150" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="196" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="196">
+      <c r="C28" s="150">
         <f>L2</f>
         <v>46007</v>
       </c>
-      <c r="D28" s="197" t="s">
+      <c r="D28" s="151" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="151" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="197" t="s">
-        <v>42</v>
-      </c>
-      <c r="F28" s="197" t="s">
-        <v>41</v>
-      </c>
-      <c r="G28" s="194"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="189" t="s">
-        <v>50</v>
-      </c>
-      <c r="J28" s="189"/>
-      <c r="K28" s="178" t="s">
+      <c r="F28" s="151" t="s">
         <v>40</v>
       </c>
-      <c r="L28" s="198">
+      <c r="G28" s="148"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="162" t="s">
+        <v>49</v>
+      </c>
+      <c r="J28" s="162"/>
+      <c r="K28" s="137" t="s">
+        <v>39</v>
+      </c>
+      <c r="L28" s="152">
         <f>L2</f>
         <v>46007</v>
       </c>
-      <c r="M28" s="178" t="s">
-        <v>41</v>
+      <c r="M28" s="137" t="s">
+        <v>40</v>
       </c>
-      <c r="N28" s="178" t="s">
-        <v>43</v>
+      <c r="N28" s="137" t="s">
+        <v>42</v>
       </c>
-      <c r="O28" s="178" t="s">
-        <v>41</v>
+      <c r="O28" s="137" t="s">
+        <v>40</v>
       </c>
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
@@ -9933,40 +9812,40 @@
       <c r="HC28" s="36"/>
     </row>
     <row r="29" spans="1:211" ht="21" x14ac:dyDescent="0.4">
-      <c r="A29" s="200"/>
-      <c r="B29" s="179">
+      <c r="A29" s="160"/>
+      <c r="B29" s="138">
         <v>21.65</v>
       </c>
-      <c r="C29" s="179">
+      <c r="C29" s="138">
         <v>17.490000000000002</v>
       </c>
-      <c r="D29" s="180">
+      <c r="D29" s="139">
         <v>-4.1599999999999966</v>
       </c>
-      <c r="E29" s="179">
+      <c r="E29" s="138">
         <v>411</v>
       </c>
-      <c r="F29" s="180">
+      <c r="F29" s="139">
         <v>-393.51</v>
       </c>
-      <c r="G29" s="194"/>
+      <c r="G29" s="148"/>
       <c r="H29" s="49"/>
-      <c r="I29" s="190"/>
-      <c r="J29" s="190"/>
-      <c r="K29" s="181">
+      <c r="I29" s="163"/>
+      <c r="J29" s="163"/>
+      <c r="K29" s="140">
         <v>861.76</v>
       </c>
-      <c r="L29" s="181">
+      <c r="L29" s="140">
         <v>858.71</v>
       </c>
-      <c r="M29" s="182">
+      <c r="M29" s="141">
         <f>L29-K29</f>
         <v>-3.0499999999999545</v>
       </c>
-      <c r="N29" s="183">
+      <c r="N29" s="142">
         <v>878.2</v>
       </c>
-      <c r="O29" s="182">
+      <c r="O29" s="141">
         <f>L29-N29</f>
         <v>-19.490000000000009</v>
       </c>
@@ -10165,39 +10044,39 @@
       <c r="HC29" s="39"/>
     </row>
     <row r="30" spans="1:211" ht="21" x14ac:dyDescent="0.4">
-      <c r="A30" s="187"/>
-      <c r="B30" s="181">
+      <c r="A30" s="146"/>
+      <c r="B30" s="140">
         <v>0.82</v>
       </c>
-      <c r="C30" s="181">
+      <c r="C30" s="140">
         <v>0.82</v>
       </c>
-      <c r="D30" s="184">
+      <c r="D30" s="143">
         <f>C30-B30</f>
         <v>0</v>
       </c>
-      <c r="E30" s="181">
+      <c r="E30" s="140">
         <v>11</v>
       </c>
-      <c r="F30" s="182">
+      <c r="F30" s="141">
         <f>C30-E30</f>
         <v>-10.18</v>
       </c>
-      <c r="G30" s="194"/>
+      <c r="G30" s="148"/>
       <c r="H30" s="49"/>
-      <c r="I30" s="191" t="s">
+      <c r="I30" s="164" t="s">
+        <v>43</v>
+      </c>
+      <c r="J30" s="164"/>
+      <c r="K30" s="144">
+        <v>242</v>
+      </c>
+      <c r="L30" s="161" t="s">
         <v>44</v>
       </c>
-      <c r="J30" s="191"/>
-      <c r="K30" s="185">
-        <v>242</v>
-      </c>
-      <c r="L30" s="193" t="s">
-        <v>45</v>
-      </c>
-      <c r="M30" s="193"/>
-      <c r="N30" s="193"/>
-      <c r="O30" s="193"/>
+      <c r="M30" s="161"/>
+      <c r="N30" s="161"/>
+      <c r="O30" s="161"/>
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
       <c r="R30" s="4"/>
@@ -10393,25 +10272,25 @@
       <c r="HC30" s="39"/>
     </row>
     <row r="31" spans="1:211" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="195"/>
-      <c r="B31" s="195"/>
-      <c r="C31" s="195"/>
-      <c r="D31" s="195"/>
-      <c r="E31" s="195"/>
-      <c r="F31" s="195"/>
-      <c r="G31" s="194"/>
+      <c r="A31" s="149"/>
+      <c r="B31" s="149"/>
+      <c r="C31" s="149"/>
+      <c r="D31" s="149"/>
+      <c r="E31" s="149"/>
+      <c r="F31" s="149"/>
+      <c r="G31" s="148"/>
       <c r="H31" s="49"/>
-      <c r="I31" s="192" t="s">
-        <v>46</v>
+      <c r="I31" s="165" t="s">
+        <v>45</v>
       </c>
-      <c r="J31" s="192"/>
-      <c r="K31" s="188">
+      <c r="J31" s="165"/>
+      <c r="K31" s="147">
         <v>122</v>
       </c>
-      <c r="L31" s="193"/>
-      <c r="M31" s="193"/>
-      <c r="N31" s="193"/>
-      <c r="O31" s="193"/>
+      <c r="L31" s="161"/>
+      <c r="M31" s="161"/>
+      <c r="N31" s="161"/>
+      <c r="O31" s="161"/>
       <c r="P31" s="31"/>
       <c r="Q31" s="31"/>
       <c r="R31" s="31"/>
@@ -10607,25 +10486,25 @@
       <c r="HC31" s="39"/>
     </row>
     <row r="32" spans="1:211" s="25" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A32" s="195"/>
-      <c r="B32" s="195"/>
-      <c r="C32" s="195"/>
-      <c r="D32" s="195"/>
-      <c r="E32" s="195"/>
-      <c r="F32" s="195"/>
-      <c r="G32" s="194"/>
-      <c r="H32" s="186"/>
-      <c r="I32" s="192" t="s">
-        <v>47</v>
+      <c r="A32" s="149"/>
+      <c r="B32" s="149"/>
+      <c r="C32" s="149"/>
+      <c r="D32" s="149"/>
+      <c r="E32" s="149"/>
+      <c r="F32" s="149"/>
+      <c r="G32" s="148"/>
+      <c r="H32" s="145"/>
+      <c r="I32" s="165" t="s">
+        <v>46</v>
       </c>
-      <c r="J32" s="192"/>
-      <c r="K32" s="188">
+      <c r="J32" s="165"/>
+      <c r="K32" s="147">
         <v>120</v>
       </c>
-      <c r="L32" s="193"/>
-      <c r="M32" s="193"/>
-      <c r="N32" s="193"/>
-      <c r="O32" s="193"/>
+      <c r="L32" s="161"/>
+      <c r="M32" s="161"/>
+      <c r="N32" s="161"/>
+      <c r="O32" s="161"/>
       <c r="P32" s="32"/>
       <c r="Q32" s="32"/>
       <c r="R32" s="32"/>
@@ -10822,21 +10701,21 @@
       <c r="HC32" s="36"/>
     </row>
     <row r="33" spans="1:211" ht="21" x14ac:dyDescent="0.4">
-      <c r="A33" s="195"/>
-      <c r="B33" s="195"/>
-      <c r="C33" s="195"/>
-      <c r="D33" s="195"/>
-      <c r="E33" s="195"/>
-      <c r="F33" s="195"/>
-      <c r="G33" s="175"/>
-      <c r="H33" s="175"/>
-      <c r="I33" s="175"/>
-      <c r="J33" s="175"/>
-      <c r="K33" s="175"/>
-      <c r="L33" s="175"/>
-      <c r="M33" s="175"/>
-      <c r="N33" s="175"/>
-      <c r="O33" s="175"/>
+      <c r="A33" s="149"/>
+      <c r="B33" s="149"/>
+      <c r="C33" s="149"/>
+      <c r="D33" s="149"/>
+      <c r="E33" s="149"/>
+      <c r="F33" s="149"/>
+      <c r="G33" s="136"/>
+      <c r="H33" s="136"/>
+      <c r="I33" s="136"/>
+      <c r="J33" s="136"/>
+      <c r="K33" s="136"/>
+      <c r="L33" s="136"/>
+      <c r="M33" s="136"/>
+      <c r="N33" s="136"/>
+      <c r="O33" s="136"/>
       <c r="P33" s="31"/>
       <c r="Q33" s="31"/>
       <c r="R33" s="31"/>
@@ -11034,19 +10913,19 @@
     <row r="34" spans="1:211" s="25" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="61"/>
       <c r="B34" s="61"/>
-      <c r="C34" s="148" t="s">
-        <v>48</v>
+      <c r="C34" s="153" t="s">
+        <v>47</v>
       </c>
-      <c r="D34" s="149"/>
-      <c r="E34" s="149"/>
-      <c r="F34" s="149"/>
+      <c r="D34" s="154"/>
+      <c r="E34" s="154"/>
+      <c r="F34" s="154"/>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
       <c r="J34" s="61"/>
       <c r="K34" s="61"/>
-      <c r="L34" s="147"/>
-      <c r="M34" s="147"/>
-      <c r="N34" s="147"/>
+      <c r="L34" s="155"/>
+      <c r="M34" s="155"/>
+      <c r="N34" s="155"/>
       <c r="O34" s="61"/>
       <c r="P34" s="61"/>
       <c r="Q34" s="59"/>
@@ -12026,21 +11905,21 @@
       <c r="HC38" s="36"/>
     </row>
     <row r="39" spans="1:211" ht="21" x14ac:dyDescent="0.4">
-      <c r="A39" s="175"/>
-      <c r="B39" s="175"/>
-      <c r="C39" s="175"/>
-      <c r="D39" s="175"/>
-      <c r="E39" s="175"/>
-      <c r="F39" s="175"/>
-      <c r="G39" s="175"/>
-      <c r="H39" s="175"/>
-      <c r="I39" s="175"/>
-      <c r="J39" s="175"/>
-      <c r="K39" s="175"/>
-      <c r="L39" s="175"/>
-      <c r="M39" s="175"/>
-      <c r="N39" s="175"/>
-      <c r="O39" s="175"/>
+      <c r="A39" s="136"/>
+      <c r="B39" s="136"/>
+      <c r="C39" s="136"/>
+      <c r="D39" s="136"/>
+      <c r="E39" s="136"/>
+      <c r="F39" s="136"/>
+      <c r="G39" s="136"/>
+      <c r="H39" s="136"/>
+      <c r="I39" s="136"/>
+      <c r="J39" s="136"/>
+      <c r="K39" s="136"/>
+      <c r="L39" s="136"/>
+      <c r="M39" s="136"/>
+      <c r="N39" s="136"/>
+      <c r="O39" s="136"/>
       <c r="P39" s="31"/>
       <c r="Q39" s="31"/>
       <c r="R39" s="31"/>
@@ -12236,14 +12115,14 @@
       <c r="HC39" s="39"/>
     </row>
     <row r="40" spans="1:211" s="25" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A40" s="175"/>
-      <c r="B40" s="175"/>
-      <c r="C40" s="175"/>
-      <c r="D40" s="175"/>
-      <c r="E40" s="175"/>
-      <c r="F40" s="175"/>
-      <c r="G40" s="175"/>
-      <c r="H40" s="175"/>
+      <c r="A40" s="136"/>
+      <c r="B40" s="136"/>
+      <c r="C40" s="136"/>
+      <c r="D40" s="136"/>
+      <c r="E40" s="136"/>
+      <c r="F40" s="136"/>
+      <c r="G40" s="136"/>
+      <c r="H40" s="136"/>
       <c r="I40" s="31"/>
       <c r="J40" s="32"/>
       <c r="K40" s="30"/>
@@ -12446,7 +12325,7 @@
       <c r="HC40" s="36"/>
     </row>
     <row r="41" spans="1:211" ht="21" x14ac:dyDescent="0.25">
-      <c r="A41" s="137"/>
+      <c r="A41" s="125"/>
       <c r="B41" s="34"/>
       <c r="C41" s="33"/>
       <c r="D41" s="35"/>
@@ -12561,7 +12440,7 @@
       <c r="DJ41" s="4"/>
     </row>
     <row r="42" spans="1:211" s="25" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A42" s="137"/>
+      <c r="A42" s="125"/>
       <c r="B42" s="35"/>
       <c r="C42" s="31"/>
       <c r="D42" s="31"/>
@@ -12676,7 +12555,7 @@
       <c r="DJ42" s="26"/>
     </row>
     <row r="43" spans="1:211" ht="23.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="137"/>
+      <c r="A43" s="125"/>
       <c r="B43" s="34"/>
       <c r="C43" s="33"/>
       <c r="D43" s="33"/>
@@ -15172,7 +15051,7 @@
       <c r="V62" s="4"/>
       <c r="W62" s="4"/>
       <c r="X62" s="4"/>
-      <c r="Y62" s="136"/>
+      <c r="Y62" s="124"/>
       <c r="Z62" s="9"/>
       <c r="AA62" s="9"/>
       <c r="AB62" s="9"/>
@@ -15342,7 +15221,7 @@
       <c r="V63" s="4"/>
       <c r="W63" s="4"/>
       <c r="X63" s="4"/>
-      <c r="Y63" s="136"/>
+      <c r="Y63" s="124"/>
       <c r="Z63" s="9"/>
       <c r="AA63" s="9"/>
       <c r="AB63" s="9"/>
@@ -15512,7 +15391,7 @@
       <c r="V64" s="4"/>
       <c r="W64" s="4"/>
       <c r="X64" s="4"/>
-      <c r="Y64" s="136"/>
+      <c r="Y64" s="124"/>
       <c r="Z64" s="9"/>
       <c r="AA64" s="9"/>
       <c r="AB64" s="9"/>
@@ -15682,7 +15561,7 @@
       <c r="V65" s="4"/>
       <c r="W65" s="4"/>
       <c r="X65" s="4"/>
-      <c r="Y65" s="136"/>
+      <c r="Y65" s="124"/>
       <c r="Z65" s="9"/>
       <c r="AA65" s="9"/>
       <c r="AB65" s="9"/>
@@ -15837,7 +15716,7 @@
       <c r="V66" s="4"/>
       <c r="W66" s="4"/>
       <c r="X66" s="4"/>
-      <c r="Y66" s="136"/>
+      <c r="Y66" s="124"/>
       <c r="Z66" s="9"/>
       <c r="AA66" s="9"/>
       <c r="AB66" s="9"/>
@@ -16007,7 +15886,7 @@
       <c r="V67" s="4"/>
       <c r="W67" s="4"/>
       <c r="X67" s="4"/>
-      <c r="Y67" s="136"/>
+      <c r="Y67" s="124"/>
       <c r="Z67" s="9"/>
       <c r="AA67" s="9"/>
       <c r="AB67" s="9"/>
@@ -16177,7 +16056,7 @@
       <c r="V68" s="4"/>
       <c r="W68" s="4"/>
       <c r="X68" s="4"/>
-      <c r="Y68" s="136"/>
+      <c r="Y68" s="124"/>
       <c r="Z68" s="9"/>
       <c r="AA68" s="9"/>
       <c r="AB68" s="9"/>
@@ -16347,7 +16226,7 @@
       <c r="V69" s="4"/>
       <c r="W69" s="4"/>
       <c r="X69" s="4"/>
-      <c r="Y69" s="136"/>
+      <c r="Y69" s="124"/>
       <c r="Z69" s="9"/>
       <c r="AA69" s="9"/>
       <c r="AB69" s="9"/>
@@ -16517,7 +16396,7 @@
       <c r="V70" s="4"/>
       <c r="W70" s="4"/>
       <c r="X70" s="4"/>
-      <c r="Y70" s="136"/>
+      <c r="Y70" s="124"/>
       <c r="Z70" s="9"/>
       <c r="AA70" s="9"/>
       <c r="AB70" s="9"/>
@@ -16687,7 +16566,7 @@
       <c r="V71" s="4"/>
       <c r="W71" s="4"/>
       <c r="X71" s="4"/>
-      <c r="Y71" s="136"/>
+      <c r="Y71" s="124"/>
       <c r="Z71" s="9"/>
       <c r="AA71" s="9"/>
       <c r="AB71" s="9"/>
@@ -16857,7 +16736,7 @@
       <c r="V72" s="4"/>
       <c r="W72" s="4"/>
       <c r="X72" s="4"/>
-      <c r="Y72" s="136"/>
+      <c r="Y72" s="124"/>
       <c r="Z72" s="9"/>
       <c r="AA72" s="9"/>
       <c r="AB72" s="9"/>
@@ -17027,7 +16906,7 @@
       <c r="V73" s="4"/>
       <c r="W73" s="4"/>
       <c r="X73" s="4"/>
-      <c r="Y73" s="136"/>
+      <c r="Y73" s="124"/>
       <c r="Z73" s="9"/>
       <c r="AA73" s="9"/>
       <c r="AB73" s="9"/>
@@ -17197,7 +17076,7 @@
       <c r="V74" s="4"/>
       <c r="W74" s="4"/>
       <c r="X74" s="4"/>
-      <c r="Y74" s="136"/>
+      <c r="Y74" s="124"/>
       <c r="Z74" s="9"/>
       <c r="AA74" s="9"/>
       <c r="AB74" s="9"/>
@@ -17367,7 +17246,7 @@
       <c r="V75" s="4"/>
       <c r="W75" s="4"/>
       <c r="X75" s="4"/>
-      <c r="Y75" s="136"/>
+      <c r="Y75" s="124"/>
       <c r="Z75" s="9"/>
       <c r="AA75" s="9"/>
       <c r="AB75" s="9"/>
@@ -17537,7 +17416,7 @@
       <c r="V76" s="4"/>
       <c r="W76" s="4"/>
       <c r="X76" s="4"/>
-      <c r="Y76" s="136"/>
+      <c r="Y76" s="124"/>
       <c r="Z76" s="9"/>
       <c r="AA76" s="9"/>
       <c r="AB76" s="9"/>
@@ -17707,7 +17586,7 @@
       <c r="V77" s="4"/>
       <c r="W77" s="4"/>
       <c r="X77" s="4"/>
-      <c r="Y77" s="136"/>
+      <c r="Y77" s="124"/>
       <c r="Z77" s="9"/>
       <c r="AA77" s="9"/>
       <c r="AB77" s="9"/>
@@ -17877,7 +17756,7 @@
       <c r="V78" s="4"/>
       <c r="W78" s="4"/>
       <c r="X78" s="4"/>
-      <c r="Y78" s="136"/>
+      <c r="Y78" s="124"/>
       <c r="Z78" s="16"/>
       <c r="AA78" s="9"/>
       <c r="AB78" s="9"/>
@@ -18047,7 +17926,7 @@
       <c r="V79" s="4"/>
       <c r="W79" s="4"/>
       <c r="X79" s="4"/>
-      <c r="Y79" s="136"/>
+      <c r="Y79" s="124"/>
       <c r="Z79" s="16"/>
       <c r="AA79" s="9"/>
       <c r="AB79" s="9"/>
@@ -18217,7 +18096,7 @@
       <c r="V80" s="4"/>
       <c r="W80" s="4"/>
       <c r="X80" s="4"/>
-      <c r="Y80" s="136"/>
+      <c r="Y80" s="124"/>
       <c r="Z80" s="16"/>
       <c r="AA80" s="9"/>
       <c r="AB80" s="9"/>
@@ -18387,7 +18266,7 @@
       <c r="V81" s="4"/>
       <c r="W81" s="4"/>
       <c r="X81" s="4"/>
-      <c r="Y81" s="136"/>
+      <c r="Y81" s="124"/>
       <c r="Z81" s="16"/>
       <c r="AA81" s="9"/>
       <c r="AB81" s="9"/>
@@ -19703,7 +19582,7 @@
       <c r="V89" s="4"/>
       <c r="W89" s="4"/>
       <c r="X89" s="4"/>
-      <c r="Y89" s="136"/>
+      <c r="Y89" s="124"/>
       <c r="Z89" s="9"/>
       <c r="AA89" s="9"/>
       <c r="AB89" s="9"/>
@@ -19873,7 +19752,7 @@
       <c r="V90" s="4"/>
       <c r="W90" s="4"/>
       <c r="X90" s="4"/>
-      <c r="Y90" s="136"/>
+      <c r="Y90" s="124"/>
       <c r="Z90" s="9"/>
       <c r="AA90" s="9"/>
       <c r="AB90" s="9"/>
@@ -20043,7 +19922,7 @@
       <c r="V91" s="4"/>
       <c r="W91" s="4"/>
       <c r="X91" s="4"/>
-      <c r="Y91" s="136"/>
+      <c r="Y91" s="124"/>
       <c r="Z91" s="9"/>
       <c r="AA91" s="9"/>
       <c r="AB91" s="9"/>
@@ -20213,7 +20092,7 @@
       <c r="V92" s="4"/>
       <c r="W92" s="4"/>
       <c r="X92" s="4"/>
-      <c r="Y92" s="136"/>
+      <c r="Y92" s="124"/>
       <c r="Z92" s="9"/>
       <c r="AA92" s="9"/>
       <c r="AB92" s="9"/>
@@ -20383,7 +20262,7 @@
       <c r="V93" s="4"/>
       <c r="W93" s="4"/>
       <c r="X93" s="4"/>
-      <c r="Y93" s="136"/>
+      <c r="Y93" s="124"/>
       <c r="Z93" s="9"/>
       <c r="AA93" s="9"/>
       <c r="AB93" s="9"/>
@@ -20553,7 +20432,7 @@
       <c r="V94" s="4"/>
       <c r="W94" s="4"/>
       <c r="X94" s="4"/>
-      <c r="Y94" s="136"/>
+      <c r="Y94" s="124"/>
       <c r="Z94" s="9"/>
       <c r="AA94" s="9"/>
       <c r="AB94" s="9"/>
@@ -20723,7 +20602,7 @@
       <c r="V95" s="4"/>
       <c r="W95" s="4"/>
       <c r="X95" s="4"/>
-      <c r="Y95" s="136"/>
+      <c r="Y95" s="124"/>
       <c r="Z95" s="9"/>
       <c r="AA95" s="9"/>
       <c r="AB95" s="9"/>
@@ -20893,7 +20772,7 @@
       <c r="V96" s="4"/>
       <c r="W96" s="4"/>
       <c r="X96" s="4"/>
-      <c r="Y96" s="136"/>
+      <c r="Y96" s="124"/>
       <c r="Z96" s="9"/>
       <c r="AA96" s="9"/>
       <c r="AB96" s="9"/>
@@ -21063,7 +20942,7 @@
       <c r="V97" s="4"/>
       <c r="W97" s="4"/>
       <c r="X97" s="4"/>
-      <c r="Y97" s="136"/>
+      <c r="Y97" s="124"/>
       <c r="Z97" s="9"/>
       <c r="AA97" s="9"/>
       <c r="AB97" s="9"/>
@@ -21233,7 +21112,7 @@
       <c r="V98" s="4"/>
       <c r="W98" s="4"/>
       <c r="X98" s="4"/>
-      <c r="Y98" s="136"/>
+      <c r="Y98" s="124"/>
       <c r="Z98" s="9"/>
       <c r="AA98" s="9"/>
       <c r="AB98" s="9"/>
@@ -21403,7 +21282,7 @@
       <c r="V99" s="4"/>
       <c r="W99" s="4"/>
       <c r="X99" s="4"/>
-      <c r="Y99" s="136"/>
+      <c r="Y99" s="124"/>
       <c r="Z99" s="9"/>
       <c r="AA99" s="9"/>
       <c r="AB99" s="9"/>
@@ -21573,7 +21452,7 @@
       <c r="V100" s="4"/>
       <c r="W100" s="4"/>
       <c r="X100" s="4"/>
-      <c r="Y100" s="136"/>
+      <c r="Y100" s="124"/>
       <c r="Z100" s="9"/>
       <c r="AA100" s="9"/>
       <c r="AB100" s="9"/>
@@ -21743,7 +21622,7 @@
       <c r="V101" s="4"/>
       <c r="W101" s="4"/>
       <c r="X101" s="4"/>
-      <c r="Y101" s="136"/>
+      <c r="Y101" s="124"/>
       <c r="Z101" s="9"/>
       <c r="AA101" s="9"/>
       <c r="AB101" s="9"/>
@@ -21913,7 +21792,7 @@
       <c r="V102" s="4"/>
       <c r="W102" s="4"/>
       <c r="X102" s="4"/>
-      <c r="Y102" s="136"/>
+      <c r="Y102" s="124"/>
       <c r="Z102" s="9"/>
       <c r="AA102" s="9"/>
       <c r="AB102" s="9"/>
@@ -22083,7 +21962,7 @@
       <c r="V103" s="4"/>
       <c r="W103" s="4"/>
       <c r="X103" s="4"/>
-      <c r="Y103" s="136"/>
+      <c r="Y103" s="124"/>
       <c r="Z103" s="9"/>
       <c r="AA103" s="9"/>
       <c r="AB103" s="9"/>
@@ -22253,7 +22132,7 @@
       <c r="V104" s="4"/>
       <c r="W104" s="4"/>
       <c r="X104" s="4"/>
-      <c r="Y104" s="136"/>
+      <c r="Y104" s="124"/>
       <c r="Z104" s="9"/>
       <c r="AA104" s="9"/>
       <c r="AB104" s="9"/>
@@ -22423,7 +22302,7 @@
       <c r="V105" s="4"/>
       <c r="W105" s="4"/>
       <c r="X105" s="4"/>
-      <c r="Y105" s="136"/>
+      <c r="Y105" s="124"/>
       <c r="Z105" s="9"/>
       <c r="AA105" s="9"/>
       <c r="AB105" s="9"/>
@@ -22593,7 +22472,7 @@
       <c r="V106" s="4"/>
       <c r="W106" s="4"/>
       <c r="X106" s="4"/>
-      <c r="Y106" s="136"/>
+      <c r="Y106" s="124"/>
       <c r="Z106" s="9"/>
       <c r="AA106" s="9"/>
       <c r="AB106" s="9"/>
@@ -22763,7 +22642,7 @@
       <c r="V107" s="4"/>
       <c r="W107" s="4"/>
       <c r="X107" s="4"/>
-      <c r="Y107" s="136"/>
+      <c r="Y107" s="124"/>
       <c r="Z107" s="9"/>
       <c r="AA107" s="9"/>
       <c r="AB107" s="9"/>
@@ -22933,7 +22812,7 @@
       <c r="V108" s="4"/>
       <c r="W108" s="4"/>
       <c r="X108" s="4"/>
-      <c r="Y108" s="136"/>
+      <c r="Y108" s="124"/>
       <c r="Z108" s="9"/>
       <c r="AA108" s="9"/>
       <c r="AB108" s="9"/>
@@ -57872,34 +57751,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="L30:O32"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="A26:O26"/>
     <mergeCell ref="T25:W25"/>
     <mergeCell ref="AB25:AD25"/>
     <mergeCell ref="A1:O1"/>
@@ -57915,7 +57766,36 @@
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="L30:O32"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="A26:O26"/>
   </mergeCells>
+  <phoneticPr fontId="69" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.39374999999999999" bottom="0" header="0.11805599999999999" footer="0.11805599999999999"/>
   <pageSetup paperSize="8" fitToWidth="0" orientation="landscape"/>
